--- a/compareOP.xlsx
+++ b/compareOP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DUT\Ki 2\Edge AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43AB01B8-2417-449C-BF5D-DFEE8E2BC276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E64CC8D-0935-4854-B2C3-17FA4CC13C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{56603411-7B59-498E-88B9-7E9448248F05}"/>
   </bookViews>
@@ -39,9 +39,6 @@
     <t>Pct</t>
   </si>
   <si>
-    <t>Gemini.1</t>
-  </si>
-  <si>
     <t>V</t>
   </si>
   <si>
@@ -49,10 +46,14 @@
   </si>
   <si>
     <t>Gem1
-25% val</t>
+Custom</t>
   </si>
   <si>
-    <t>Gem1
+    <t>Gem2
+Custom</t>
+  </si>
+  <si>
+    <t>Gemini.1
 Custom</t>
   </si>
 </sst>
@@ -139,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -158,10 +159,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1023,8 +1027,8 @@
       <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>8</v>
+      <c r="C1" s="8" t="s">
+        <v>6</v>
       </c>
       <c r="F1" t="s">
         <v>0</v>
@@ -1032,7 +1036,7 @@
       <c r="G1" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1044,7 +1048,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" s="6"/>
       <c r="F2">
@@ -1062,7 +1066,7 @@
       </c>
       <c r="L2" s="4">
         <f>COUNTIF(I2:I1001, "T")</f>
-        <v>1000</v>
+        <v>936</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -1073,7 +1077,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="6"/>
       <c r="F3">
@@ -1091,7 +1095,7 @@
       </c>
       <c r="L3" s="4">
         <f>L2/1000*100</f>
-        <v>100</v>
+        <v>93.600000000000009</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -1102,7 +1106,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="6"/>
       <c r="F4">
@@ -1124,18 +1128,18 @@
         <v>2</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" s="6"/>
       <c r="F5">
         <v>14</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I5" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
@@ -1146,7 +1150,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" s="6"/>
       <c r="F6">
@@ -1168,7 +1172,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" s="6"/>
       <c r="F7">
@@ -1190,7 +1194,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" s="6"/>
       <c r="F8">
@@ -1212,7 +1216,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" s="6"/>
       <c r="F9">
@@ -1249,7 +1253,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" s="6"/>
       <c r="F10">
@@ -1271,7 +1275,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" s="6"/>
       <c r="F11">
@@ -1293,7 +1297,7 @@
         <v>7</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" s="6"/>
       <c r="F12">
@@ -1315,7 +1319,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" s="6"/>
       <c r="F13">
@@ -1337,7 +1341,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" s="6"/>
       <c r="F14">
@@ -1359,7 +1363,7 @@
         <v>7</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D15" s="6"/>
       <c r="F15">
@@ -1381,7 +1385,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" s="6"/>
       <c r="F16">
@@ -1418,7 +1422,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17" s="6"/>
       <c r="F17">
@@ -1441,7 +1445,7 @@
         <v>2</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18" s="6"/>
       <c r="F18">
@@ -1463,24 +1467,24 @@
         <v>1</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D19" s="6"/>
       <c r="F19">
         <v>59</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I19" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
-      </c>
-      <c r="O19" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="8"/>
+        <v>F</v>
+      </c>
+      <c r="O19" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
@@ -1492,16 +1496,18 @@
       <c r="C20" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="6"/>
+      <c r="D20" s="6">
+        <v>6</v>
+      </c>
       <c r="F20">
         <v>63</v>
       </c>
       <c r="G20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I20" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
@@ -1512,7 +1518,7 @@
         <v>2</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D21" s="6">
         <v>1</v>
@@ -1521,11 +1527,11 @@
         <v>67</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
@@ -1536,7 +1542,7 @@
         <v>5</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D22" s="6"/>
       <c r="F22">
@@ -1558,18 +1564,18 @@
         <v>6</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23" s="6"/>
       <c r="F23">
         <v>70</v>
       </c>
       <c r="G23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I23" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
@@ -1580,7 +1586,7 @@
         <v>2</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D24" s="6"/>
       <c r="F24">
@@ -1602,7 +1608,7 @@
         <v>6</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D25" s="6"/>
       <c r="F25">
@@ -1624,7 +1630,7 @@
         <v>9</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26" s="6"/>
       <c r="F26">
@@ -1646,7 +1652,7 @@
         <v>6</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D27" s="6"/>
       <c r="F27">
@@ -1668,7 +1674,7 @@
         <v>2</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D28" s="6"/>
       <c r="F28">
@@ -1690,7 +1696,7 @@
         <v>6</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D29" s="6"/>
       <c r="F29">
@@ -1712,7 +1718,7 @@
         <v>4</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D30" s="6"/>
       <c r="F30">
@@ -1734,7 +1740,7 @@
         <v>3</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D31" s="6"/>
       <c r="F31">
@@ -1756,7 +1762,7 @@
         <v>2</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D32" s="6"/>
       <c r="F32">
@@ -1778,7 +1784,7 @@
         <v>5</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D33" s="6"/>
       <c r="F33">
@@ -1800,7 +1806,7 @@
         <v>5</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D34" s="6"/>
       <c r="F34">
@@ -1822,7 +1828,7 @@
         <v>1</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D35" s="6"/>
       <c r="F35">
@@ -1844,7 +1850,7 @@
         <v>3</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D36" s="6"/>
       <c r="F36">
@@ -1866,7 +1872,7 @@
         <v>2</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D37" s="6"/>
       <c r="F37">
@@ -1888,7 +1894,7 @@
         <v>1</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D38" s="6"/>
       <c r="F38">
@@ -1910,7 +1916,7 @@
         <v>3</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D39" s="6"/>
       <c r="F39">
@@ -1932,7 +1938,7 @@
         <v>1</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D40" s="6"/>
       <c r="F40">
@@ -1954,7 +1960,7 @@
         <v>1</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D41" s="6"/>
       <c r="F41">
@@ -1976,7 +1982,7 @@
         <v>1</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D42" s="6"/>
       <c r="F42">
@@ -1998,7 +2004,7 @@
         <v>4</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D43" s="6"/>
       <c r="F43">
@@ -2020,7 +2026,7 @@
         <v>6</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D44" s="6"/>
       <c r="F44">
@@ -2042,7 +2048,7 @@
         <v>3</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D45" s="6"/>
       <c r="F45">
@@ -2064,7 +2070,7 @@
         <v>6</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D46" s="6"/>
       <c r="F46">
@@ -2086,7 +2092,7 @@
         <v>1</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D47" s="6"/>
       <c r="F47">
@@ -2108,7 +2114,7 @@
         <v>2</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D48" s="6"/>
       <c r="F48">
@@ -2130,7 +2136,7 @@
         <v>3</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D49" s="6"/>
       <c r="F49">
@@ -2152,7 +2158,7 @@
         <v>7</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D50" s="6"/>
       <c r="F50">
@@ -2174,7 +2180,7 @@
         <v>2</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D51" s="6"/>
       <c r="F51">
@@ -2196,7 +2202,7 @@
         <v>6</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D52" s="6"/>
       <c r="F52">
@@ -2218,7 +2224,7 @@
         <v>6</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D53" s="6"/>
       <c r="F53">
@@ -2240,7 +2246,7 @@
         <v>3</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D54" s="6"/>
       <c r="F54">
@@ -2262,7 +2268,7 @@
         <v>5</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D55" s="6"/>
       <c r="F55">
@@ -2284,7 +2290,7 @@
         <v>2</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D56" s="6"/>
       <c r="F56">
@@ -2306,7 +2312,7 @@
         <v>1</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D57" s="6"/>
       <c r="F57">
@@ -2328,7 +2334,7 @@
         <v>1</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D58" s="6"/>
       <c r="F58">
@@ -2350,7 +2356,7 @@
         <v>1</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D59" s="6"/>
       <c r="F59">
@@ -2372,7 +2378,7 @@
         <v>2</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D60" s="6"/>
       <c r="F60">
@@ -2394,7 +2400,7 @@
         <v>2</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D61" s="6"/>
       <c r="F61">
@@ -2416,7 +2422,7 @@
         <v>6</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D62" s="6"/>
       <c r="F62">
@@ -2438,7 +2444,7 @@
         <v>2</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D63" s="6"/>
       <c r="F63">
@@ -2460,7 +2466,7 @@
         <v>2</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D64" s="6"/>
       <c r="F64">
@@ -2482,7 +2488,7 @@
         <v>4</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D65" s="6"/>
       <c r="F65">
@@ -2504,7 +2510,7 @@
         <v>1</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D66" s="6"/>
       <c r="F66">
@@ -2526,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D67" s="6"/>
       <c r="F67">
@@ -2548,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D68" s="6"/>
       <c r="F68">
@@ -2570,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D69" s="6"/>
       <c r="F69">
@@ -2592,7 +2598,7 @@
         <v>6</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D70" s="6"/>
       <c r="F70">
@@ -2614,7 +2620,7 @@
         <v>6</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D71" s="6"/>
       <c r="F71">
@@ -2636,7 +2642,7 @@
         <v>4</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D72" s="6"/>
       <c r="F72">
@@ -2658,7 +2664,7 @@
         <v>4</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D73" s="6"/>
       <c r="F73">
@@ -2680,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D74" s="6"/>
       <c r="F74">
@@ -2702,7 +2708,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D75" s="6"/>
       <c r="F75">
@@ -2724,7 +2730,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D76" s="6"/>
       <c r="F76">
@@ -2746,7 +2752,7 @@
         <v>1</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D77" s="6"/>
       <c r="F77">
@@ -2768,7 +2774,7 @@
         <v>0</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D78" s="6"/>
       <c r="F78">
@@ -2790,7 +2796,7 @@
         <v>2</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D79" s="6">
         <v>6</v>
@@ -2799,11 +2805,11 @@
         <v>229</v>
       </c>
       <c r="G79">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I79" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
@@ -2814,7 +2820,7 @@
         <v>5</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D80" s="6"/>
       <c r="F80">
@@ -2836,7 +2842,7 @@
         <v>2</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D81" s="6"/>
       <c r="F81">
@@ -2858,7 +2864,7 @@
         <v>2</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D82" s="6"/>
       <c r="F82">
@@ -2880,7 +2886,7 @@
         <v>1</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D83" s="6"/>
       <c r="F83">
@@ -2902,7 +2908,7 @@
         <v>2</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D84" s="6"/>
       <c r="F84">
@@ -2924,7 +2930,7 @@
         <v>2</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D85" s="6"/>
       <c r="F85">
@@ -2946,7 +2952,7 @@
         <v>1</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D86" s="6"/>
       <c r="F86">
@@ -2968,7 +2974,7 @@
         <v>1</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D87" s="6"/>
       <c r="F87">
@@ -2990,7 +2996,7 @@
         <v>6</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D88" s="6"/>
       <c r="F88">
@@ -3012,7 +3018,7 @@
         <v>6</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D89" s="6"/>
       <c r="F89">
@@ -3034,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D90" s="6"/>
       <c r="F90">
@@ -3056,7 +3062,7 @@
         <v>0</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D91" s="6"/>
       <c r="F91">
@@ -3078,7 +3084,7 @@
         <v>2</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D92" s="6"/>
       <c r="F92">
@@ -3100,7 +3106,7 @@
         <v>1</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D93" s="6"/>
       <c r="F93">
@@ -3122,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D94" s="6"/>
       <c r="F94">
@@ -3144,7 +3150,7 @@
         <v>5</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D95" s="6"/>
       <c r="F95">
@@ -3166,7 +3172,7 @@
         <v>0</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D96" s="6"/>
       <c r="F96">
@@ -3188,7 +3194,7 @@
         <v>2</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D97" s="6"/>
       <c r="F97">
@@ -3210,7 +3216,7 @@
         <v>1</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D98" s="6"/>
       <c r="F98">
@@ -3232,7 +3238,7 @@
         <v>0</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D99" s="6"/>
       <c r="F99">
@@ -3254,7 +3260,7 @@
         <v>6</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D100" s="6"/>
       <c r="F100">
@@ -3276,7 +3282,7 @@
         <v>6</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D101" s="6"/>
       <c r="F101">
@@ -3298,7 +3304,7 @@
         <v>0</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D102" s="6"/>
       <c r="F102">
@@ -3320,18 +3326,18 @@
         <v>6</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D103" s="6"/>
       <c r="F103">
         <v>282</v>
       </c>
       <c r="G103">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I103" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
@@ -3342,7 +3348,7 @@
         <v>9</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D104" s="6"/>
       <c r="F104">
@@ -3364,7 +3370,7 @@
         <v>9</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D105" s="6"/>
       <c r="F105">
@@ -3386,7 +3392,7 @@
         <v>1</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D106" s="6"/>
       <c r="F106">
@@ -3408,7 +3414,7 @@
         <v>4</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D107" s="6"/>
       <c r="F107">
@@ -3430,7 +3436,7 @@
         <v>2</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D108" s="6"/>
       <c r="F108">
@@ -3452,7 +3458,7 @@
         <v>5</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D109" s="6"/>
       <c r="F109">
@@ -3474,7 +3480,7 @@
         <v>8</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D110" s="6"/>
       <c r="F110">
@@ -3496,7 +3502,7 @@
         <v>1</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D111" s="6"/>
       <c r="F111">
@@ -3518,7 +3524,7 @@
         <v>3</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D112" s="6"/>
       <c r="F112">
@@ -3540,7 +3546,7 @@
         <v>2</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D113" s="6"/>
       <c r="F113">
@@ -3562,7 +3568,7 @@
         <v>0</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D114" s="6"/>
       <c r="F114">
@@ -3584,7 +3590,7 @@
         <v>1</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D115" s="6"/>
       <c r="F115">
@@ -3606,7 +3612,7 @@
         <v>1</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D116" s="6"/>
       <c r="F116">
@@ -3628,7 +3634,7 @@
         <v>1</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D117" s="6"/>
       <c r="F117">
@@ -3650,7 +3656,7 @@
         <v>1</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D118" s="6"/>
       <c r="F118">
@@ -3672,7 +3678,7 @@
         <v>0</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D119" s="6"/>
       <c r="F119">
@@ -3694,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D120" s="6"/>
       <c r="F120">
@@ -3716,7 +3722,7 @@
         <v>2</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D121" s="6"/>
       <c r="F121">
@@ -3738,7 +3744,7 @@
         <v>6</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D122" s="6"/>
       <c r="F122">
@@ -3760,7 +3766,7 @@
         <v>3</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D123" s="6"/>
       <c r="F123">
@@ -3782,7 +3788,7 @@
         <v>2</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D124" s="6"/>
       <c r="F124">
@@ -3804,7 +3810,7 @@
         <v>2</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D125" s="6"/>
       <c r="F125">
@@ -3826,7 +3832,7 @@
         <v>1</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D126" s="6"/>
       <c r="F126">
@@ -3848,7 +3854,7 @@
         <v>1</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D127" s="6"/>
       <c r="F127">
@@ -3870,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D128" s="6"/>
       <c r="F128">
@@ -3892,7 +3898,7 @@
         <v>1</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D129" s="6"/>
       <c r="F129">
@@ -3914,7 +3920,7 @@
         <v>2</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D130" s="6"/>
       <c r="F130">
@@ -3936,7 +3942,7 @@
         <v>2</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D131" s="6"/>
       <c r="F131">
@@ -3958,7 +3964,7 @@
         <v>2</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D132" s="6"/>
       <c r="F132">
@@ -3980,7 +3986,7 @@
         <v>2</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D133" s="6"/>
       <c r="F133">
@@ -4002,7 +4008,7 @@
         <v>1</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D134" s="6"/>
       <c r="F134">
@@ -4024,7 +4030,7 @@
         <v>5</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D135" s="6"/>
       <c r="F135">
@@ -4046,7 +4052,7 @@
         <v>1</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D136" s="6"/>
       <c r="F136">
@@ -4068,7 +4074,7 @@
         <v>0</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D137" s="6"/>
       <c r="F137">
@@ -4090,18 +4096,18 @@
         <v>1</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D138" s="6"/>
       <c r="F138">
         <v>387</v>
       </c>
       <c r="G138">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I138" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
@@ -4112,7 +4118,7 @@
         <v>2</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D139" s="6"/>
       <c r="F139">
@@ -4134,7 +4140,7 @@
         <v>3</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D140" s="6"/>
       <c r="F140">
@@ -4156,7 +4162,7 @@
         <v>1</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D141" s="6"/>
       <c r="F141">
@@ -4178,7 +4184,7 @@
         <v>1</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D142" s="6"/>
       <c r="F142">
@@ -4200,7 +4206,7 @@
         <v>1</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D143" s="6"/>
       <c r="F143">
@@ -4222,7 +4228,7 @@
         <v>4</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D144" s="6"/>
       <c r="F144">
@@ -4244,7 +4250,7 @@
         <v>5</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D145" s="6"/>
       <c r="F145">
@@ -4451,11 +4457,11 @@
         <v>435</v>
       </c>
       <c r="G155">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I155" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
@@ -4531,11 +4537,11 @@
         <v>443</v>
       </c>
       <c r="G159">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I159" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
@@ -4891,11 +4897,11 @@
         <v>495</v>
       </c>
       <c r="G177">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I177" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.3">
@@ -4931,11 +4937,11 @@
         <v>506</v>
       </c>
       <c r="G179">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I179" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
@@ -4991,11 +4997,11 @@
         <v>509</v>
       </c>
       <c r="G182">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I182" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.3">
@@ -5231,11 +5237,11 @@
         <v>544</v>
       </c>
       <c r="G194">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I194" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.3">
@@ -5331,11 +5337,11 @@
         <v>555</v>
       </c>
       <c r="G199">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I199" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.3">
@@ -5611,11 +5617,11 @@
         <v>598</v>
       </c>
       <c r="G213">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I213" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.3">
@@ -5831,11 +5837,11 @@
         <v>621</v>
       </c>
       <c r="G224">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I224" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.3">
@@ -5971,11 +5977,11 @@
         <v>650</v>
       </c>
       <c r="G231">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I231" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.3">
@@ -6291,11 +6297,11 @@
         <v>700</v>
       </c>
       <c r="G247">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I247" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.3">
@@ -6311,11 +6317,11 @@
         <v>705</v>
       </c>
       <c r="G248">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I248" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.3">
@@ -7431,11 +7437,11 @@
         <v>874</v>
       </c>
       <c r="G304">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I304" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.3">
@@ -7971,11 +7977,11 @@
         <v>978</v>
       </c>
       <c r="G331">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I331" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.3">
@@ -8251,11 +8257,11 @@
         <v>1027</v>
       </c>
       <c r="G345">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I345" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.3">
@@ -8351,11 +8357,11 @@
         <v>1037</v>
       </c>
       <c r="G350">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I350" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.3">
@@ -9371,11 +9377,11 @@
         <v>1195</v>
       </c>
       <c r="G401">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I401" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="402" spans="1:9" x14ac:dyDescent="0.3">
@@ -9391,11 +9397,11 @@
         <v>1196</v>
       </c>
       <c r="G402">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I402" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.3">
@@ -9411,11 +9417,11 @@
         <v>1200</v>
       </c>
       <c r="G403">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I403" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.3">
@@ -10571,11 +10577,11 @@
         <v>1381</v>
       </c>
       <c r="G461">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I461" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="462" spans="1:9" x14ac:dyDescent="0.3">
@@ -10591,11 +10597,11 @@
         <v>1391</v>
       </c>
       <c r="G462">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I462" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="463" spans="1:9" x14ac:dyDescent="0.3">
@@ -10831,11 +10837,11 @@
         <v>1426</v>
       </c>
       <c r="G474">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I474" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="475" spans="1:9" x14ac:dyDescent="0.3">
@@ -11091,11 +11097,11 @@
         <v>1472</v>
       </c>
       <c r="G487">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I487" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="488" spans="1:9" x14ac:dyDescent="0.3">
@@ -11331,11 +11337,11 @@
         <v>1507</v>
       </c>
       <c r="G499">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I499" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="500" spans="1:9" x14ac:dyDescent="0.3">
@@ -11711,11 +11717,11 @@
         <v>1566</v>
       </c>
       <c r="G518">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I518" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="519" spans="1:9" x14ac:dyDescent="0.3">
@@ -12131,11 +12137,11 @@
         <v>1653</v>
       </c>
       <c r="G539">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I539" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="540" spans="1:9" x14ac:dyDescent="0.3">
@@ -12251,11 +12257,11 @@
         <v>1672</v>
       </c>
       <c r="G545">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I545" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="546" spans="1:9" x14ac:dyDescent="0.3">
@@ -12471,11 +12477,11 @@
         <v>1710</v>
       </c>
       <c r="G556">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I556" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="557" spans="1:9" x14ac:dyDescent="0.3">
@@ -13111,11 +13117,11 @@
         <v>1809</v>
       </c>
       <c r="G588">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I588" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="589" spans="1:9" x14ac:dyDescent="0.3">
@@ -13231,11 +13237,11 @@
         <v>1829</v>
       </c>
       <c r="G594">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I594" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="595" spans="1:9" x14ac:dyDescent="0.3">
@@ -13611,11 +13617,11 @@
         <v>1883</v>
       </c>
       <c r="G613">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I613" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="614" spans="1:9" x14ac:dyDescent="0.3">
@@ -13731,11 +13737,11 @@
         <v>1911</v>
       </c>
       <c r="G619">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I619" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="620" spans="1:9" x14ac:dyDescent="0.3">
@@ -13751,11 +13757,11 @@
         <v>1912</v>
       </c>
       <c r="G620">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I620" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="621" spans="1:9" x14ac:dyDescent="0.3">
@@ -14531,11 +14537,11 @@
         <v>2028</v>
       </c>
       <c r="G659">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I659" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="660" spans="1:9" x14ac:dyDescent="0.3">
@@ -15091,11 +15097,11 @@
         <v>2153</v>
       </c>
       <c r="G687">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I687" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="688" spans="1:9" x14ac:dyDescent="0.3">
@@ -15211,11 +15217,11 @@
         <v>2164</v>
       </c>
       <c r="G693">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I693" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="694" spans="1:9" x14ac:dyDescent="0.3">
@@ -15511,11 +15517,11 @@
         <v>2216</v>
       </c>
       <c r="G708">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I708" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="709" spans="1:9" x14ac:dyDescent="0.3">
@@ -16011,11 +16017,11 @@
         <v>2293</v>
       </c>
       <c r="G733">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I733" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="734" spans="1:9" x14ac:dyDescent="0.3">
@@ -16411,11 +16417,11 @@
         <v>2354</v>
       </c>
       <c r="G753">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I753" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="754" spans="1:9" x14ac:dyDescent="0.3">
@@ -17051,11 +17057,11 @@
         <v>2448</v>
       </c>
       <c r="G785">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I785" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="786" spans="1:9" x14ac:dyDescent="0.3">
@@ -17251,11 +17257,11 @@
         <v>2484</v>
       </c>
       <c r="G795">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I795" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="796" spans="1:9" x14ac:dyDescent="0.3">
@@ -17391,11 +17397,11 @@
         <v>2498</v>
       </c>
       <c r="G802">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I802" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="803" spans="1:9" x14ac:dyDescent="0.3">
@@ -18731,11 +18737,11 @@
         <v>2702</v>
       </c>
       <c r="G869">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I869" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="870" spans="1:9" x14ac:dyDescent="0.3">
@@ -18831,11 +18837,11 @@
         <v>2714</v>
       </c>
       <c r="G874">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I874" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="875" spans="1:9" x14ac:dyDescent="0.3">
@@ -19251,11 +19257,11 @@
         <v>2783</v>
       </c>
       <c r="G895">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I895" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="896" spans="1:9" x14ac:dyDescent="0.3">
@@ -19411,11 +19417,11 @@
         <v>2802</v>
       </c>
       <c r="G903">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I903" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="904" spans="1:9" x14ac:dyDescent="0.3">
@@ -19711,11 +19717,11 @@
         <v>2830</v>
       </c>
       <c r="G918">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I918" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="919" spans="1:9" x14ac:dyDescent="0.3">
@@ -19871,11 +19877,11 @@
         <v>2852</v>
       </c>
       <c r="G926">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I926" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="927" spans="1:9" x14ac:dyDescent="0.3">
@@ -20231,11 +20237,11 @@
         <v>2907</v>
       </c>
       <c r="G944">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I944" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="945" spans="1:9" x14ac:dyDescent="0.3">
@@ -20811,11 +20817,11 @@
         <v>2975</v>
       </c>
       <c r="G973">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I973" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="974" spans="1:9" x14ac:dyDescent="0.3">
@@ -20891,11 +20897,11 @@
         <v>2994</v>
       </c>
       <c r="G977">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I977" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="978" spans="1:9" x14ac:dyDescent="0.3">
@@ -20931,11 +20937,11 @@
         <v>3008</v>
       </c>
       <c r="G979">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I979" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="980" spans="1:9" x14ac:dyDescent="0.3">
@@ -21111,11 +21117,11 @@
         <v>3044</v>
       </c>
       <c r="G988">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I988" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="989" spans="1:9" x14ac:dyDescent="0.3">
@@ -21191,11 +21197,11 @@
         <v>3057</v>
       </c>
       <c r="G992">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I992" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="993" spans="1:9" x14ac:dyDescent="0.3">
@@ -21251,11 +21257,11 @@
         <v>3075</v>
       </c>
       <c r="G995">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I995" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="996" spans="1:9" x14ac:dyDescent="0.3">
@@ -21291,11 +21297,11 @@
         <v>3079</v>
       </c>
       <c r="G997">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I997" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="998" spans="1:9" x14ac:dyDescent="0.3">

--- a/compareOP.xlsx
+++ b/compareOP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DUT\Ki 2\Edge AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E64CC8D-0935-4854-B2C3-17FA4CC13C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40BD07DF-5F38-49F9-B4FA-FDBB0027BC0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{56603411-7B59-498E-88B9-7E9448248F05}"/>
   </bookViews>
@@ -163,10 +163,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1480,11 +1480,11 @@
         <f t="shared" si="0"/>
         <v>F</v>
       </c>
-      <c r="O19" s="10" t="s">
+      <c r="O19" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="P19" s="9"/>
-      <c r="Q19" s="9"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="6">

--- a/compareOP.xlsx
+++ b/compareOP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DUT\Ki 2\Edge AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40BD07DF-5F38-49F9-B4FA-FDBB0027BC0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D52865-C367-4247-99B8-A454AE73D3BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{56603411-7B59-498E-88B9-7E9448248F05}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="9">
   <si>
     <t>Id</t>
   </si>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="L2" s="4">
         <f>COUNTIF(I2:I1001, "T")</f>
-        <v>936</v>
+        <v>966</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="L3" s="4">
         <f>L2/1000*100</f>
-        <v>93.600000000000009</v>
+        <v>96.6</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -1474,11 +1474,11 @@
         <v>59</v>
       </c>
       <c r="G19">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I19" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>T</v>
       </c>
       <c r="O19" s="9" t="s">
         <v>8</v>
@@ -1527,7 +1527,7 @@
         <v>67</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I21" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1571,11 +1571,11 @@
         <v>70</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I23" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
@@ -2805,7 +2805,7 @@
         <v>229</v>
       </c>
       <c r="G79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I79" s="6" t="str">
         <f t="shared" si="1"/>
@@ -4103,11 +4103,11 @@
         <v>387</v>
       </c>
       <c r="G138">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I138" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
@@ -4271,7 +4271,9 @@
       <c r="B146" s="6">
         <v>6</v>
       </c>
-      <c r="C146" s="6"/>
+      <c r="C146" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D146" s="6"/>
       <c r="F146">
         <v>415</v>
@@ -4291,7 +4293,9 @@
       <c r="B147" s="6">
         <v>2</v>
       </c>
-      <c r="C147" s="6"/>
+      <c r="C147" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D147" s="6"/>
       <c r="F147">
         <v>416</v>
@@ -4311,7 +4315,9 @@
       <c r="B148" s="6">
         <v>1</v>
       </c>
-      <c r="C148" s="6"/>
+      <c r="C148" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D148" s="6"/>
       <c r="F148">
         <v>420</v>
@@ -4331,7 +4337,9 @@
       <c r="B149" s="6">
         <v>2</v>
       </c>
-      <c r="C149" s="6"/>
+      <c r="C149" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D149" s="6"/>
       <c r="F149">
         <v>422</v>
@@ -4351,7 +4359,9 @@
       <c r="B150" s="6">
         <v>5</v>
       </c>
-      <c r="C150" s="6"/>
+      <c r="C150" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D150" s="6"/>
       <c r="F150">
         <v>423</v>
@@ -4371,7 +4381,9 @@
       <c r="B151" s="6">
         <v>6</v>
       </c>
-      <c r="C151" s="6"/>
+      <c r="C151" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D151" s="6"/>
       <c r="F151">
         <v>424</v>
@@ -4391,7 +4403,9 @@
       <c r="B152" s="6">
         <v>9</v>
       </c>
-      <c r="C152" s="6"/>
+      <c r="C152" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D152" s="6"/>
       <c r="F152">
         <v>430</v>
@@ -4411,7 +4425,9 @@
       <c r="B153" s="6">
         <v>1</v>
       </c>
-      <c r="C153" s="6"/>
+      <c r="C153" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D153" s="6"/>
       <c r="F153">
         <v>432</v>
@@ -4431,7 +4447,9 @@
       <c r="B154" s="6">
         <v>2</v>
       </c>
-      <c r="C154" s="6"/>
+      <c r="C154" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D154" s="6"/>
       <c r="F154">
         <v>433</v>
@@ -4451,17 +4469,19 @@
       <c r="B155" s="6">
         <v>1</v>
       </c>
-      <c r="C155" s="6"/>
+      <c r="C155" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D155" s="6"/>
       <c r="F155">
         <v>435</v>
       </c>
       <c r="G155">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I155" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
@@ -4471,7 +4491,9 @@
       <c r="B156" s="6">
         <v>7</v>
       </c>
-      <c r="C156" s="6"/>
+      <c r="C156" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D156" s="6"/>
       <c r="F156">
         <v>436</v>
@@ -4491,7 +4513,9 @@
       <c r="B157" s="6">
         <v>3</v>
       </c>
-      <c r="C157" s="6"/>
+      <c r="C157" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D157" s="6"/>
       <c r="F157">
         <v>439</v>
@@ -4511,7 +4535,9 @@
       <c r="B158" s="6">
         <v>1</v>
       </c>
-      <c r="C158" s="6"/>
+      <c r="C158" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D158" s="6"/>
       <c r="F158">
         <v>440</v>
@@ -4531,17 +4557,19 @@
       <c r="B159" s="6">
         <v>6</v>
       </c>
-      <c r="C159" s="6"/>
+      <c r="C159" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D159" s="6"/>
       <c r="F159">
         <v>443</v>
       </c>
       <c r="G159">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I159" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
@@ -4551,7 +4579,9 @@
       <c r="B160" s="6">
         <v>6</v>
       </c>
-      <c r="C160" s="6"/>
+      <c r="C160" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D160" s="6"/>
       <c r="F160">
         <v>445</v>
@@ -4571,7 +4601,9 @@
       <c r="B161" s="6">
         <v>3</v>
       </c>
-      <c r="C161" s="6"/>
+      <c r="C161" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D161" s="6"/>
       <c r="F161">
         <v>449</v>
@@ -4591,7 +4623,9 @@
       <c r="B162" s="6">
         <v>2</v>
       </c>
-      <c r="C162" s="6"/>
+      <c r="C162" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D162" s="6"/>
       <c r="F162">
         <v>450</v>
@@ -4611,7 +4645,9 @@
       <c r="B163" s="6">
         <v>2</v>
       </c>
-      <c r="C163" s="6"/>
+      <c r="C163" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D163" s="6"/>
       <c r="F163">
         <v>456</v>
@@ -4631,7 +4667,9 @@
       <c r="B164" s="6">
         <v>2</v>
       </c>
-      <c r="C164" s="6"/>
+      <c r="C164" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D164" s="6"/>
       <c r="F164">
         <v>457</v>
@@ -4651,7 +4689,9 @@
       <c r="B165" s="6">
         <v>6</v>
       </c>
-      <c r="C165" s="6"/>
+      <c r="C165" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D165" s="6"/>
       <c r="F165">
         <v>460</v>
@@ -4671,7 +4711,9 @@
       <c r="B166" s="6">
         <v>6</v>
       </c>
-      <c r="C166" s="6"/>
+      <c r="C166" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D166" s="6"/>
       <c r="F166">
         <v>461</v>
@@ -4691,7 +4733,9 @@
       <c r="B167" s="6">
         <v>4</v>
       </c>
-      <c r="C167" s="6"/>
+      <c r="C167" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D167" s="6"/>
       <c r="F167">
         <v>462</v>
@@ -4711,7 +4755,9 @@
       <c r="B168" s="6">
         <v>0</v>
       </c>
-      <c r="C168" s="6"/>
+      <c r="C168" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D168" s="6"/>
       <c r="F168">
         <v>463</v>
@@ -4731,7 +4777,9 @@
       <c r="B169" s="6">
         <v>3</v>
       </c>
-      <c r="C169" s="6"/>
+      <c r="C169" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D169" s="6"/>
       <c r="F169">
         <v>464</v>
@@ -4751,7 +4799,9 @@
       <c r="B170" s="6">
         <v>4</v>
       </c>
-      <c r="C170" s="6"/>
+      <c r="C170" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D170" s="6"/>
       <c r="F170">
         <v>471</v>
@@ -4771,7 +4821,9 @@
       <c r="B171" s="6">
         <v>1</v>
       </c>
-      <c r="C171" s="6"/>
+      <c r="C171" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D171" s="6"/>
       <c r="F171">
         <v>472</v>
@@ -4791,7 +4843,9 @@
       <c r="B172" s="6">
         <v>6</v>
       </c>
-      <c r="C172" s="6"/>
+      <c r="C172" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D172" s="6"/>
       <c r="F172">
         <v>478</v>
@@ -4811,7 +4865,9 @@
       <c r="B173" s="6">
         <v>2</v>
       </c>
-      <c r="C173" s="6"/>
+      <c r="C173" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D173" s="6"/>
       <c r="F173">
         <v>479</v>
@@ -4831,7 +4887,9 @@
       <c r="B174" s="6">
         <v>0</v>
       </c>
-      <c r="C174" s="6"/>
+      <c r="C174" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D174" s="6"/>
       <c r="F174">
         <v>480</v>
@@ -4851,7 +4909,9 @@
       <c r="B175" s="6">
         <v>9</v>
       </c>
-      <c r="C175" s="6"/>
+      <c r="C175" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D175" s="6"/>
       <c r="F175">
         <v>485</v>
@@ -4871,7 +4931,9 @@
       <c r="B176" s="6">
         <v>0</v>
       </c>
-      <c r="C176" s="6"/>
+      <c r="C176" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D176" s="6"/>
       <c r="F176">
         <v>486</v>
@@ -4891,17 +4953,19 @@
       <c r="B177" s="6">
         <v>5</v>
       </c>
-      <c r="C177" s="6"/>
+      <c r="C177" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D177" s="6"/>
       <c r="F177">
         <v>495</v>
       </c>
       <c r="G177">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I177" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.3">
@@ -4911,7 +4975,9 @@
       <c r="B178" s="6">
         <v>0</v>
       </c>
-      <c r="C178" s="6"/>
+      <c r="C178" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D178" s="6"/>
       <c r="F178">
         <v>498</v>
@@ -4931,17 +4997,19 @@
       <c r="B179" s="6">
         <v>1</v>
       </c>
-      <c r="C179" s="6"/>
+      <c r="C179" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D179" s="6"/>
       <c r="F179">
         <v>506</v>
       </c>
       <c r="G179">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I179" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
@@ -4951,7 +5019,9 @@
       <c r="B180" s="6">
         <v>2</v>
       </c>
-      <c r="C180" s="6"/>
+      <c r="C180" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D180" s="6"/>
       <c r="F180">
         <v>507</v>
@@ -4971,7 +5041,9 @@
       <c r="B181" s="6">
         <v>2</v>
       </c>
-      <c r="C181" s="6"/>
+      <c r="C181" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D181" s="6"/>
       <c r="F181">
         <v>508</v>
@@ -4991,17 +5063,19 @@
       <c r="B182" s="6">
         <v>9</v>
       </c>
-      <c r="C182" s="6"/>
+      <c r="C182" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D182" s="6"/>
       <c r="F182">
         <v>509</v>
       </c>
       <c r="G182">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I182" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.3">
@@ -5011,7 +5085,9 @@
       <c r="B183" s="6">
         <v>3</v>
       </c>
-      <c r="C183" s="6"/>
+      <c r="C183" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D183" s="6"/>
       <c r="F183">
         <v>511</v>
@@ -5031,7 +5107,9 @@
       <c r="B184" s="6">
         <v>2</v>
       </c>
-      <c r="C184" s="6"/>
+      <c r="C184" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D184" s="6"/>
       <c r="F184">
         <v>518</v>
@@ -5051,7 +5129,9 @@
       <c r="B185" s="6">
         <v>1</v>
       </c>
-      <c r="C185" s="6"/>
+      <c r="C185" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D185" s="6"/>
       <c r="F185">
         <v>521</v>
@@ -5071,7 +5151,9 @@
       <c r="B186" s="6">
         <v>2</v>
       </c>
-      <c r="C186" s="6"/>
+      <c r="C186" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D186" s="6"/>
       <c r="F186">
         <v>527</v>
@@ -5091,7 +5173,9 @@
       <c r="B187" s="6">
         <v>2</v>
       </c>
-      <c r="C187" s="6"/>
+      <c r="C187" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D187" s="6"/>
       <c r="F187">
         <v>528</v>
@@ -5111,7 +5195,9 @@
       <c r="B188" s="6">
         <v>7</v>
       </c>
-      <c r="C188" s="6"/>
+      <c r="C188" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D188" s="6"/>
       <c r="F188">
         <v>532</v>
@@ -5131,7 +5217,9 @@
       <c r="B189" s="6">
         <v>1</v>
       </c>
-      <c r="C189" s="6"/>
+      <c r="C189" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D189" s="6"/>
       <c r="F189">
         <v>533</v>
@@ -5151,7 +5239,9 @@
       <c r="B190" s="6">
         <v>2</v>
       </c>
-      <c r="C190" s="6"/>
+      <c r="C190" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D190" s="6"/>
       <c r="F190">
         <v>535</v>
@@ -5171,7 +5261,9 @@
       <c r="B191" s="6">
         <v>0</v>
       </c>
-      <c r="C191" s="6"/>
+      <c r="C191" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D191" s="6"/>
       <c r="F191">
         <v>538</v>
@@ -5191,7 +5283,9 @@
       <c r="B192" s="6">
         <v>2</v>
       </c>
-      <c r="C192" s="6"/>
+      <c r="C192" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D192" s="6"/>
       <c r="F192">
         <v>542</v>
@@ -5211,7 +5305,9 @@
       <c r="B193" s="6">
         <v>3</v>
       </c>
-      <c r="C193" s="6"/>
+      <c r="C193" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D193" s="6"/>
       <c r="F193">
         <v>543</v>
@@ -5231,17 +5327,19 @@
       <c r="B194" s="6">
         <v>1</v>
       </c>
-      <c r="C194" s="6"/>
+      <c r="C194" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D194" s="6"/>
       <c r="F194">
         <v>544</v>
       </c>
       <c r="G194">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I194" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.3">
@@ -5251,7 +5349,9 @@
       <c r="B195" s="6">
         <v>0</v>
       </c>
-      <c r="C195" s="6"/>
+      <c r="C195" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D195" s="6"/>
       <c r="F195">
         <v>547</v>
@@ -5271,7 +5371,9 @@
       <c r="B196" s="6">
         <v>0</v>
       </c>
-      <c r="C196" s="6"/>
+      <c r="C196" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D196" s="6"/>
       <c r="F196">
         <v>549</v>
@@ -5291,7 +5393,9 @@
       <c r="B197" s="6">
         <v>1</v>
       </c>
-      <c r="C197" s="6"/>
+      <c r="C197" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D197" s="6"/>
       <c r="F197">
         <v>553</v>
@@ -5311,7 +5415,9 @@
       <c r="B198" s="6">
         <v>3</v>
       </c>
-      <c r="C198" s="6"/>
+      <c r="C198" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D198" s="6"/>
       <c r="F198">
         <v>554</v>
@@ -5331,17 +5437,19 @@
       <c r="B199" s="6">
         <v>6</v>
       </c>
-      <c r="C199" s="6"/>
+      <c r="C199" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D199" s="6"/>
       <c r="F199">
         <v>555</v>
       </c>
       <c r="G199">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I199" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.3">
@@ -5351,7 +5459,9 @@
       <c r="B200" s="6">
         <v>6</v>
       </c>
-      <c r="C200" s="6"/>
+      <c r="C200" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D200" s="6"/>
       <c r="F200">
         <v>557</v>
@@ -5371,7 +5481,9 @@
       <c r="B201" s="6">
         <v>3</v>
       </c>
-      <c r="C201" s="6"/>
+      <c r="C201" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D201" s="6"/>
       <c r="F201">
         <v>561</v>
@@ -5391,7 +5503,9 @@
       <c r="B202" s="6">
         <v>6</v>
       </c>
-      <c r="C202" s="6"/>
+      <c r="C202" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D202" s="6"/>
       <c r="F202">
         <v>564</v>
@@ -5411,7 +5525,9 @@
       <c r="B203" s="6">
         <v>2</v>
       </c>
-      <c r="C203" s="6"/>
+      <c r="C203" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D203" s="6"/>
       <c r="F203">
         <v>565</v>
@@ -5431,7 +5547,9 @@
       <c r="B204" s="6">
         <v>1</v>
       </c>
-      <c r="C204" s="6"/>
+      <c r="C204" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D204" s="6"/>
       <c r="F204">
         <v>567</v>
@@ -5451,7 +5569,9 @@
       <c r="B205" s="6">
         <v>1</v>
       </c>
-      <c r="C205" s="6"/>
+      <c r="C205" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D205" s="6"/>
       <c r="F205">
         <v>568</v>
@@ -5471,7 +5591,9 @@
       <c r="B206" s="6">
         <v>1</v>
       </c>
-      <c r="C206" s="6"/>
+      <c r="C206" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D206" s="6"/>
       <c r="F206">
         <v>572</v>
@@ -5491,7 +5613,9 @@
       <c r="B207" s="6">
         <v>2</v>
       </c>
-      <c r="C207" s="6"/>
+      <c r="C207" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D207" s="6"/>
       <c r="F207">
         <v>573</v>
@@ -5511,7 +5635,9 @@
       <c r="B208" s="6">
         <v>2</v>
       </c>
-      <c r="C208" s="6"/>
+      <c r="C208" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D208" s="6"/>
       <c r="F208">
         <v>581</v>
@@ -5531,7 +5657,9 @@
       <c r="B209" s="6">
         <v>7</v>
       </c>
-      <c r="C209" s="6"/>
+      <c r="C209" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D209" s="6"/>
       <c r="F209">
         <v>582</v>
@@ -5551,7 +5679,9 @@
       <c r="B210" s="6">
         <v>4</v>
       </c>
-      <c r="C210" s="6"/>
+      <c r="C210" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D210" s="6"/>
       <c r="F210">
         <v>594</v>
@@ -5571,7 +5701,9 @@
       <c r="B211" s="6">
         <v>2</v>
       </c>
-      <c r="C211" s="6"/>
+      <c r="C211" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D211" s="6"/>
       <c r="F211">
         <v>596</v>
@@ -5591,7 +5723,9 @@
       <c r="B212" s="6">
         <v>4</v>
       </c>
-      <c r="C212" s="6"/>
+      <c r="C212" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D212" s="6"/>
       <c r="F212">
         <v>597</v>
@@ -5611,7 +5745,9 @@
       <c r="B213" s="6">
         <v>1</v>
       </c>
-      <c r="C213" s="6"/>
+      <c r="C213" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D213" s="6"/>
       <c r="F213">
         <v>598</v>
@@ -5631,7 +5767,9 @@
       <c r="B214" s="6">
         <v>0</v>
       </c>
-      <c r="C214" s="6"/>
+      <c r="C214" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D214" s="6"/>
       <c r="F214">
         <v>599</v>
@@ -5651,7 +5789,9 @@
       <c r="B215" s="6">
         <v>1</v>
       </c>
-      <c r="C215" s="6"/>
+      <c r="C215" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D215" s="6"/>
       <c r="F215">
         <v>601</v>
@@ -5671,7 +5811,9 @@
       <c r="B216" s="6">
         <v>5</v>
       </c>
-      <c r="C216" s="6"/>
+      <c r="C216" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D216" s="6"/>
       <c r="F216">
         <v>602</v>
@@ -5691,7 +5833,9 @@
       <c r="B217" s="6">
         <v>1</v>
       </c>
-      <c r="C217" s="6"/>
+      <c r="C217" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D217" s="6"/>
       <c r="F217">
         <v>605</v>
@@ -5711,7 +5855,9 @@
       <c r="B218" s="6">
         <v>2</v>
       </c>
-      <c r="C218" s="6"/>
+      <c r="C218" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D218" s="6"/>
       <c r="F218">
         <v>610</v>
@@ -5731,7 +5877,9 @@
       <c r="B219" s="6">
         <v>3</v>
       </c>
-      <c r="C219" s="6"/>
+      <c r="C219" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D219" s="6"/>
       <c r="F219">
         <v>611</v>
@@ -5751,7 +5899,9 @@
       <c r="B220" s="6">
         <v>0</v>
       </c>
-      <c r="C220" s="6"/>
+      <c r="C220" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D220" s="6"/>
       <c r="F220">
         <v>612</v>
@@ -5771,7 +5921,9 @@
       <c r="B221" s="6">
         <v>0</v>
       </c>
-      <c r="C221" s="6"/>
+      <c r="C221" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D221" s="6"/>
       <c r="F221">
         <v>613</v>
@@ -5791,7 +5943,9 @@
       <c r="B222" s="6">
         <v>2</v>
       </c>
-      <c r="C222" s="6"/>
+      <c r="C222" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D222" s="6"/>
       <c r="F222">
         <v>617</v>
@@ -5811,7 +5965,9 @@
       <c r="B223" s="6">
         <v>1</v>
       </c>
-      <c r="C223" s="6"/>
+      <c r="C223" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D223" s="6"/>
       <c r="F223">
         <v>620</v>
@@ -5831,17 +5987,19 @@
       <c r="B224" s="6">
         <v>1</v>
       </c>
-      <c r="C224" s="6"/>
+      <c r="C224" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D224" s="6"/>
       <c r="F224">
         <v>621</v>
       </c>
       <c r="G224">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I224" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.3">
@@ -5851,7 +6009,9 @@
       <c r="B225" s="6">
         <v>2</v>
       </c>
-      <c r="C225" s="6"/>
+      <c r="C225" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D225" s="6"/>
       <c r="F225">
         <v>626</v>
@@ -5871,7 +6031,9 @@
       <c r="B226" s="6">
         <v>0</v>
       </c>
-      <c r="C226" s="6"/>
+      <c r="C226" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D226" s="6"/>
       <c r="F226">
         <v>632</v>
@@ -5891,7 +6053,9 @@
       <c r="B227" s="6">
         <v>1</v>
       </c>
-      <c r="C227" s="6"/>
+      <c r="C227" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D227" s="6"/>
       <c r="F227">
         <v>637</v>
@@ -5911,7 +6075,9 @@
       <c r="B228" s="6">
         <v>3</v>
       </c>
-      <c r="C228" s="6"/>
+      <c r="C228" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D228" s="6"/>
       <c r="F228">
         <v>642</v>
@@ -5931,7 +6097,9 @@
       <c r="B229" s="6">
         <v>3</v>
       </c>
-      <c r="C229" s="6"/>
+      <c r="C229" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D229" s="6"/>
       <c r="F229">
         <v>644</v>
@@ -5951,7 +6119,9 @@
       <c r="B230" s="6">
         <v>1</v>
       </c>
-      <c r="C230" s="6"/>
+      <c r="C230" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D230" s="6"/>
       <c r="F230">
         <v>647</v>
@@ -5971,13 +6141,17 @@
       <c r="B231" s="6">
         <v>2</v>
       </c>
-      <c r="C231" s="6"/>
-      <c r="D231" s="6"/>
+      <c r="C231" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D231" s="6">
+        <v>6</v>
+      </c>
       <c r="F231">
         <v>650</v>
       </c>
       <c r="G231">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I231" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5991,7 +6165,9 @@
       <c r="B232" s="6">
         <v>4</v>
       </c>
-      <c r="C232" s="6"/>
+      <c r="C232" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D232" s="6"/>
       <c r="F232">
         <v>651</v>
@@ -6011,7 +6187,9 @@
       <c r="B233" s="6">
         <v>5</v>
       </c>
-      <c r="C233" s="6"/>
+      <c r="C233" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D233" s="6"/>
       <c r="F233">
         <v>655</v>
@@ -6031,7 +6209,9 @@
       <c r="B234" s="6">
         <v>2</v>
       </c>
-      <c r="C234" s="6"/>
+      <c r="C234" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D234" s="6"/>
       <c r="F234">
         <v>657</v>
@@ -6051,7 +6231,9 @@
       <c r="B235" s="6">
         <v>2</v>
       </c>
-      <c r="C235" s="6"/>
+      <c r="C235" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D235" s="6"/>
       <c r="F235">
         <v>662</v>
@@ -6071,7 +6253,9 @@
       <c r="B236" s="6">
         <v>2</v>
       </c>
-      <c r="C236" s="6"/>
+      <c r="C236" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D236" s="6"/>
       <c r="F236">
         <v>670</v>
@@ -6091,7 +6275,9 @@
       <c r="B237" s="6">
         <v>2</v>
       </c>
-      <c r="C237" s="6"/>
+      <c r="C237" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D237" s="6"/>
       <c r="F237">
         <v>676</v>
@@ -6111,7 +6297,9 @@
       <c r="B238" s="6">
         <v>4</v>
       </c>
-      <c r="C238" s="6"/>
+      <c r="C238" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D238" s="6"/>
       <c r="F238">
         <v>677</v>
@@ -6131,7 +6319,9 @@
       <c r="B239" s="6">
         <v>6</v>
       </c>
-      <c r="C239" s="6"/>
+      <c r="C239" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D239" s="6"/>
       <c r="F239">
         <v>678</v>
@@ -6151,7 +6341,9 @@
       <c r="B240" s="6">
         <v>2</v>
       </c>
-      <c r="C240" s="6"/>
+      <c r="C240" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D240" s="6"/>
       <c r="F240">
         <v>679</v>
@@ -6171,7 +6363,9 @@
       <c r="B241" s="6">
         <v>0</v>
       </c>
-      <c r="C241" s="6"/>
+      <c r="C241" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D241" s="6"/>
       <c r="F241">
         <v>680</v>
@@ -6191,7 +6385,9 @@
       <c r="B242" s="6">
         <v>8</v>
       </c>
-      <c r="C242" s="6"/>
+      <c r="C242" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D242" s="6"/>
       <c r="F242">
         <v>682</v>
@@ -6211,17 +6407,21 @@
       <c r="B243" s="6">
         <v>2</v>
       </c>
-      <c r="C243" s="6"/>
-      <c r="D243" s="6"/>
+      <c r="C243" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D243" s="6">
+        <v>6</v>
+      </c>
       <c r="F243">
         <v>685</v>
       </c>
       <c r="G243">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I243" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.3">
@@ -6231,17 +6431,19 @@
       <c r="B244" s="6">
         <v>7</v>
       </c>
-      <c r="C244" s="6"/>
+      <c r="C244" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D244" s="6"/>
       <c r="F244">
         <v>691</v>
       </c>
       <c r="G244">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I244" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.3">
@@ -6251,7 +6453,9 @@
       <c r="B245" s="6">
         <v>3</v>
       </c>
-      <c r="C245" s="6"/>
+      <c r="C245" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D245" s="6"/>
       <c r="F245">
         <v>693</v>
@@ -6271,7 +6475,9 @@
       <c r="B246" s="6">
         <v>2</v>
       </c>
-      <c r="C246" s="6"/>
+      <c r="C246" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D246" s="6"/>
       <c r="F246">
         <v>695</v>
@@ -6291,13 +6497,15 @@
       <c r="B247" s="6">
         <v>6</v>
       </c>
-      <c r="C247" s="6"/>
+      <c r="C247" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D247" s="6"/>
       <c r="F247">
         <v>700</v>
       </c>
       <c r="G247">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I247" s="6" t="str">
         <f t="shared" si="3"/>
@@ -6311,17 +6519,19 @@
       <c r="B248" s="6">
         <v>6</v>
       </c>
-      <c r="C248" s="6"/>
+      <c r="C248" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D248" s="6"/>
       <c r="F248">
         <v>705</v>
       </c>
       <c r="G248">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I248" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.3">
@@ -6331,7 +6541,9 @@
       <c r="B249" s="6">
         <v>1</v>
       </c>
-      <c r="C249" s="6"/>
+      <c r="C249" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D249" s="6"/>
       <c r="F249">
         <v>707</v>
@@ -6351,7 +6563,9 @@
       <c r="B250" s="6">
         <v>1</v>
       </c>
-      <c r="C250" s="6"/>
+      <c r="C250" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D250" s="6"/>
       <c r="F250">
         <v>718</v>
@@ -6371,7 +6585,9 @@
       <c r="B251" s="6">
         <v>2</v>
       </c>
-      <c r="C251" s="6"/>
+      <c r="C251" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D251" s="6"/>
       <c r="F251">
         <v>727</v>
@@ -6391,7 +6607,9 @@
       <c r="B252" s="6">
         <v>2</v>
       </c>
-      <c r="C252" s="6"/>
+      <c r="C252" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D252" s="6"/>
       <c r="F252">
         <v>729</v>
@@ -6411,7 +6629,9 @@
       <c r="B253" s="6">
         <v>9</v>
       </c>
-      <c r="C253" s="6"/>
+      <c r="C253" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D253" s="6"/>
       <c r="F253">
         <v>736</v>
@@ -6431,7 +6651,9 @@
       <c r="B254" s="6">
         <v>0</v>
       </c>
-      <c r="C254" s="6"/>
+      <c r="C254" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D254" s="6"/>
       <c r="F254">
         <v>741</v>
@@ -6451,7 +6673,9 @@
       <c r="B255" s="6">
         <v>7</v>
       </c>
-      <c r="C255" s="6"/>
+      <c r="C255" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D255" s="6"/>
       <c r="F255">
         <v>742</v>
@@ -6471,7 +6695,9 @@
       <c r="B256" s="6">
         <v>1</v>
       </c>
-      <c r="C256" s="6"/>
+      <c r="C256" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D256" s="6"/>
       <c r="F256">
         <v>744</v>
@@ -6491,7 +6717,9 @@
       <c r="B257" s="6">
         <v>4</v>
       </c>
-      <c r="C257" s="6"/>
+      <c r="C257" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D257" s="6"/>
       <c r="F257">
         <v>746</v>
@@ -6511,7 +6739,9 @@
       <c r="B258" s="6">
         <v>6</v>
       </c>
-      <c r="C258" s="6"/>
+      <c r="C258" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D258" s="6"/>
       <c r="F258">
         <v>748</v>
@@ -6531,7 +6761,9 @@
       <c r="B259" s="6">
         <v>2</v>
       </c>
-      <c r="C259" s="6"/>
+      <c r="C259" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D259" s="6"/>
       <c r="F259">
         <v>755</v>
@@ -6551,7 +6783,9 @@
       <c r="B260" s="6">
         <v>1</v>
       </c>
-      <c r="C260" s="6"/>
+      <c r="C260" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D260" s="6"/>
       <c r="F260">
         <v>756</v>
@@ -6571,7 +6805,9 @@
       <c r="B261" s="6">
         <v>2</v>
       </c>
-      <c r="C261" s="6"/>
+      <c r="C261" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D261" s="6"/>
       <c r="F261">
         <v>759</v>
@@ -6591,7 +6827,9 @@
       <c r="B262" s="6">
         <v>2</v>
       </c>
-      <c r="C262" s="6"/>
+      <c r="C262" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D262" s="6"/>
       <c r="F262">
         <v>761</v>
@@ -6611,7 +6849,9 @@
       <c r="B263" s="6">
         <v>5</v>
       </c>
-      <c r="C263" s="6"/>
+      <c r="C263" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D263" s="6"/>
       <c r="F263">
         <v>764</v>
@@ -6631,7 +6871,9 @@
       <c r="B264" s="6">
         <v>2</v>
       </c>
-      <c r="C264" s="6"/>
+      <c r="C264" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D264" s="6"/>
       <c r="F264">
         <v>765</v>
@@ -6651,7 +6893,9 @@
       <c r="B265" s="6">
         <v>3</v>
       </c>
-      <c r="C265" s="6"/>
+      <c r="C265" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D265" s="6"/>
       <c r="F265">
         <v>767</v>
@@ -6671,7 +6915,9 @@
       <c r="B266" s="6">
         <v>2</v>
       </c>
-      <c r="C266" s="6"/>
+      <c r="C266" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D266" s="6"/>
       <c r="F266">
         <v>772</v>
@@ -6691,7 +6937,9 @@
       <c r="B267" s="6">
         <v>3</v>
       </c>
-      <c r="C267" s="6"/>
+      <c r="C267" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D267" s="6"/>
       <c r="F267">
         <v>776</v>
@@ -6711,7 +6959,9 @@
       <c r="B268" s="6">
         <v>3</v>
       </c>
-      <c r="C268" s="6"/>
+      <c r="C268" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D268" s="6"/>
       <c r="F268">
         <v>781</v>
@@ -6731,7 +6981,9 @@
       <c r="B269" s="6">
         <v>4</v>
       </c>
-      <c r="C269" s="6"/>
+      <c r="C269" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D269" s="6"/>
       <c r="F269">
         <v>783</v>
@@ -6751,7 +7003,9 @@
       <c r="B270" s="6">
         <v>1</v>
       </c>
-      <c r="C270" s="6"/>
+      <c r="C270" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D270" s="6"/>
       <c r="F270">
         <v>785</v>
@@ -6771,7 +7025,9 @@
       <c r="B271" s="6">
         <v>5</v>
       </c>
-      <c r="C271" s="6"/>
+      <c r="C271" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D271" s="6"/>
       <c r="F271">
         <v>787</v>
@@ -6791,7 +7047,9 @@
       <c r="B272" s="6">
         <v>2</v>
       </c>
-      <c r="C272" s="6"/>
+      <c r="C272" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D272" s="6"/>
       <c r="F272">
         <v>789</v>
@@ -6811,7 +7069,9 @@
       <c r="B273" s="6">
         <v>7</v>
       </c>
-      <c r="C273" s="6"/>
+      <c r="C273" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D273" s="6"/>
       <c r="F273">
         <v>790</v>
@@ -6831,7 +7091,9 @@
       <c r="B274" s="6">
         <v>2</v>
       </c>
-      <c r="C274" s="6"/>
+      <c r="C274" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D274" s="6"/>
       <c r="F274">
         <v>794</v>
@@ -6851,7 +7113,9 @@
       <c r="B275" s="6">
         <v>0</v>
       </c>
-      <c r="C275" s="6"/>
+      <c r="C275" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D275" s="6"/>
       <c r="F275">
         <v>798</v>
@@ -6871,7 +7135,9 @@
       <c r="B276" s="6">
         <v>1</v>
       </c>
-      <c r="C276" s="6"/>
+      <c r="C276" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D276" s="6"/>
       <c r="F276">
         <v>801</v>
@@ -6891,7 +7157,9 @@
       <c r="B277" s="6">
         <v>0</v>
       </c>
-      <c r="C277" s="6"/>
+      <c r="C277" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D277" s="6"/>
       <c r="F277">
         <v>802</v>
@@ -6911,7 +7179,9 @@
       <c r="B278" s="6">
         <v>2</v>
       </c>
-      <c r="C278" s="6"/>
+      <c r="C278" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D278" s="6"/>
       <c r="F278">
         <v>803</v>
@@ -6931,7 +7201,9 @@
       <c r="B279" s="6">
         <v>6</v>
       </c>
-      <c r="C279" s="6"/>
+      <c r="C279" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D279" s="6"/>
       <c r="F279">
         <v>805</v>
@@ -6951,7 +7223,9 @@
       <c r="B280" s="6">
         <v>7</v>
       </c>
-      <c r="C280" s="6"/>
+      <c r="C280" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D280" s="6"/>
       <c r="F280">
         <v>807</v>
@@ -6971,7 +7245,9 @@
       <c r="B281" s="6">
         <v>5</v>
       </c>
-      <c r="C281" s="6"/>
+      <c r="C281" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D281" s="6"/>
       <c r="F281">
         <v>809</v>
@@ -6991,7 +7267,9 @@
       <c r="B282" s="6">
         <v>1</v>
       </c>
-      <c r="C282" s="6"/>
+      <c r="C282" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D282" s="6"/>
       <c r="F282">
         <v>810</v>
@@ -7011,7 +7289,9 @@
       <c r="B283" s="6">
         <v>0</v>
       </c>
-      <c r="C283" s="6"/>
+      <c r="C283" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D283" s="6"/>
       <c r="F283">
         <v>811</v>
@@ -7031,7 +7311,9 @@
       <c r="B284" s="6">
         <v>0</v>
       </c>
-      <c r="C284" s="6"/>
+      <c r="C284" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D284" s="6"/>
       <c r="F284">
         <v>812</v>
@@ -7051,7 +7333,9 @@
       <c r="B285" s="6">
         <v>1</v>
       </c>
-      <c r="C285" s="6"/>
+      <c r="C285" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D285" s="6"/>
       <c r="F285">
         <v>817</v>
@@ -7071,7 +7355,9 @@
       <c r="B286" s="6">
         <v>3</v>
       </c>
-      <c r="C286" s="6"/>
+      <c r="C286" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D286" s="6"/>
       <c r="F286">
         <v>819</v>
@@ -7091,7 +7377,9 @@
       <c r="B287" s="6">
         <v>2</v>
       </c>
-      <c r="C287" s="6"/>
+      <c r="C287" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D287" s="6"/>
       <c r="F287">
         <v>829</v>
@@ -7111,7 +7399,9 @@
       <c r="B288" s="6">
         <v>6</v>
       </c>
-      <c r="C288" s="6"/>
+      <c r="C288" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D288" s="6"/>
       <c r="F288">
         <v>831</v>
@@ -7131,7 +7421,9 @@
       <c r="B289" s="6">
         <v>1</v>
       </c>
-      <c r="C289" s="6"/>
+      <c r="C289" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D289" s="6"/>
       <c r="F289">
         <v>834</v>
@@ -7151,7 +7443,9 @@
       <c r="B290" s="6">
         <v>2</v>
       </c>
-      <c r="C290" s="6"/>
+      <c r="C290" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D290" s="6"/>
       <c r="F290">
         <v>838</v>
@@ -7171,7 +7465,9 @@
       <c r="B291" s="6">
         <v>1</v>
       </c>
-      <c r="C291" s="6"/>
+      <c r="C291" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D291" s="6"/>
       <c r="F291">
         <v>839</v>
@@ -7191,7 +7487,9 @@
       <c r="B292" s="6">
         <v>9</v>
       </c>
-      <c r="C292" s="6"/>
+      <c r="C292" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D292" s="6"/>
       <c r="F292">
         <v>840</v>
@@ -7211,7 +7509,9 @@
       <c r="B293" s="6">
         <v>7</v>
       </c>
-      <c r="C293" s="6"/>
+      <c r="C293" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D293" s="6"/>
       <c r="F293">
         <v>842</v>
@@ -7231,7 +7531,9 @@
       <c r="B294" s="6">
         <v>2</v>
       </c>
-      <c r="C294" s="6"/>
+      <c r="C294" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D294" s="6"/>
       <c r="F294">
         <v>844</v>
@@ -7251,7 +7553,9 @@
       <c r="B295" s="6">
         <v>3</v>
       </c>
-      <c r="C295" s="6"/>
+      <c r="C295" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D295" s="6"/>
       <c r="F295">
         <v>845</v>
@@ -7271,7 +7575,9 @@
       <c r="B296" s="6">
         <v>3</v>
       </c>
-      <c r="C296" s="6"/>
+      <c r="C296" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D296" s="6"/>
       <c r="F296">
         <v>847</v>
@@ -7291,7 +7597,9 @@
       <c r="B297" s="6">
         <v>3</v>
       </c>
-      <c r="C297" s="6"/>
+      <c r="C297" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D297" s="6"/>
       <c r="F297">
         <v>857</v>
@@ -7311,7 +7619,9 @@
       <c r="B298" s="6">
         <v>6</v>
       </c>
-      <c r="C298" s="6"/>
+      <c r="C298" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D298" s="6"/>
       <c r="F298">
         <v>859</v>
@@ -7331,7 +7641,9 @@
       <c r="B299" s="6">
         <v>6</v>
       </c>
-      <c r="C299" s="6"/>
+      <c r="C299" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D299" s="6"/>
       <c r="F299">
         <v>862</v>
@@ -7351,7 +7663,9 @@
       <c r="B300" s="6">
         <v>0</v>
       </c>
-      <c r="C300" s="6"/>
+      <c r="C300" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D300" s="6"/>
       <c r="F300">
         <v>864</v>
@@ -7371,7 +7685,9 @@
       <c r="B301" s="6">
         <v>1</v>
       </c>
-      <c r="C301" s="6"/>
+      <c r="C301" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D301" s="6"/>
       <c r="F301">
         <v>867</v>
@@ -7391,7 +7707,9 @@
       <c r="B302" s="6">
         <v>6</v>
       </c>
-      <c r="C302" s="6"/>
+      <c r="C302" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D302" s="6"/>
       <c r="F302">
         <v>869</v>
@@ -7411,7 +7729,9 @@
       <c r="B303" s="6">
         <v>0</v>
       </c>
-      <c r="C303" s="6"/>
+      <c r="C303" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D303" s="6"/>
       <c r="F303">
         <v>871</v>
@@ -7431,17 +7751,19 @@
       <c r="B304" s="6">
         <v>1</v>
       </c>
-      <c r="C304" s="6"/>
+      <c r="C304" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D304" s="6"/>
       <c r="F304">
         <v>874</v>
       </c>
       <c r="G304">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I304" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.3">
@@ -7451,7 +7773,9 @@
       <c r="B305" s="6">
         <v>2</v>
       </c>
-      <c r="C305" s="6"/>
+      <c r="C305" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D305" s="6"/>
       <c r="F305">
         <v>879</v>
@@ -7471,7 +7795,9 @@
       <c r="B306" s="6">
         <v>2</v>
       </c>
-      <c r="C306" s="6"/>
+      <c r="C306" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D306" s="6"/>
       <c r="F306">
         <v>881</v>
@@ -7491,7 +7817,9 @@
       <c r="B307" s="6">
         <v>2</v>
       </c>
-      <c r="C307" s="6"/>
+      <c r="C307" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D307" s="6"/>
       <c r="F307">
         <v>887</v>
@@ -7511,7 +7839,9 @@
       <c r="B308" s="6">
         <v>2</v>
       </c>
-      <c r="C308" s="6"/>
+      <c r="C308" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D308" s="6"/>
       <c r="F308">
         <v>889</v>
@@ -7531,7 +7861,9 @@
       <c r="B309" s="6">
         <v>3</v>
       </c>
-      <c r="C309" s="6"/>
+      <c r="C309" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D309" s="6"/>
       <c r="F309">
         <v>897</v>
@@ -7551,7 +7883,9 @@
       <c r="B310" s="6">
         <v>1</v>
       </c>
-      <c r="C310" s="6"/>
+      <c r="C310" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D310" s="6"/>
       <c r="F310">
         <v>900</v>
@@ -7571,7 +7905,9 @@
       <c r="B311" s="6">
         <v>0</v>
       </c>
-      <c r="C311" s="6"/>
+      <c r="C311" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D311" s="6"/>
       <c r="F311">
         <v>903</v>
@@ -7591,7 +7927,9 @@
       <c r="B312" s="6">
         <v>3</v>
       </c>
-      <c r="C312" s="6"/>
+      <c r="C312" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D312" s="6"/>
       <c r="F312">
         <v>907</v>
@@ -7611,7 +7949,9 @@
       <c r="B313" s="6">
         <v>3</v>
       </c>
-      <c r="C313" s="6"/>
+      <c r="C313" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D313" s="6"/>
       <c r="F313">
         <v>911</v>
@@ -7631,7 +7971,9 @@
       <c r="B314" s="6">
         <v>3</v>
       </c>
-      <c r="C314" s="6"/>
+      <c r="C314" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D314" s="6"/>
       <c r="F314">
         <v>912</v>
@@ -7651,7 +7993,9 @@
       <c r="B315" s="6">
         <v>4</v>
       </c>
-      <c r="C315" s="6"/>
+      <c r="C315" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D315" s="6"/>
       <c r="F315">
         <v>926</v>
@@ -7671,7 +8015,9 @@
       <c r="B316" s="6">
         <v>4</v>
       </c>
-      <c r="C316" s="6"/>
+      <c r="C316" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D316" s="6"/>
       <c r="F316">
         <v>927</v>
@@ -7691,7 +8037,9 @@
       <c r="B317" s="6">
         <v>2</v>
       </c>
-      <c r="C317" s="6"/>
+      <c r="C317" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D317" s="6"/>
       <c r="F317">
         <v>929</v>
@@ -7711,7 +8059,9 @@
       <c r="B318" s="6">
         <v>0</v>
       </c>
-      <c r="C318" s="6"/>
+      <c r="C318" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D318" s="6"/>
       <c r="F318">
         <v>930</v>
@@ -7731,7 +8081,9 @@
       <c r="B319" s="6">
         <v>0</v>
       </c>
-      <c r="C319" s="6"/>
+      <c r="C319" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D319" s="6"/>
       <c r="F319">
         <v>932</v>
@@ -7751,7 +8103,9 @@
       <c r="B320" s="6">
         <v>5</v>
       </c>
-      <c r="C320" s="6"/>
+      <c r="C320" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D320" s="6"/>
       <c r="F320">
         <v>937</v>
@@ -7771,7 +8125,9 @@
       <c r="B321" s="6">
         <v>2</v>
       </c>
-      <c r="C321" s="6"/>
+      <c r="C321" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D321" s="6"/>
       <c r="F321">
         <v>940</v>
@@ -7791,7 +8147,9 @@
       <c r="B322" s="6">
         <v>2</v>
       </c>
-      <c r="C322" s="6"/>
+      <c r="C322" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D322" s="6"/>
       <c r="F322">
         <v>942</v>
@@ -7811,7 +8169,9 @@
       <c r="B323" s="6">
         <v>0</v>
       </c>
-      <c r="C323" s="6"/>
+      <c r="C323" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D323" s="6"/>
       <c r="F323">
         <v>944</v>
@@ -7831,7 +8191,9 @@
       <c r="B324" s="6">
         <v>2</v>
       </c>
-      <c r="C324" s="6"/>
+      <c r="C324" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D324" s="6"/>
       <c r="F324">
         <v>945</v>
@@ -7851,7 +8213,9 @@
       <c r="B325" s="6">
         <v>0</v>
       </c>
-      <c r="C325" s="6"/>
+      <c r="C325" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D325" s="6"/>
       <c r="F325">
         <v>949</v>
@@ -7871,7 +8235,9 @@
       <c r="B326" s="6">
         <v>0</v>
       </c>
-      <c r="C326" s="6"/>
+      <c r="C326" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D326" s="6"/>
       <c r="F326">
         <v>952</v>
@@ -7891,7 +8257,9 @@
       <c r="B327" s="6">
         <v>6</v>
       </c>
-      <c r="C327" s="6"/>
+      <c r="C327" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D327" s="6"/>
       <c r="F327">
         <v>962</v>
@@ -7911,7 +8279,9 @@
       <c r="B328" s="6">
         <v>1</v>
       </c>
-      <c r="C328" s="6"/>
+      <c r="C328" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D328" s="6"/>
       <c r="F328">
         <v>964</v>
@@ -7931,7 +8301,9 @@
       <c r="B329" s="6">
         <v>4</v>
       </c>
-      <c r="C329" s="6"/>
+      <c r="C329" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D329" s="6"/>
       <c r="F329">
         <v>965</v>
@@ -7951,7 +8323,9 @@
       <c r="B330" s="6">
         <v>1</v>
       </c>
-      <c r="C330" s="6"/>
+      <c r="C330" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D330" s="6"/>
       <c r="F330">
         <v>969</v>
@@ -7971,17 +8345,19 @@
       <c r="B331" s="6">
         <v>1</v>
       </c>
-      <c r="C331" s="6"/>
+      <c r="C331" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D331" s="6"/>
       <c r="F331">
         <v>978</v>
       </c>
       <c r="G331">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I331" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.3">
@@ -7991,7 +8367,9 @@
       <c r="B332" s="6">
         <v>1</v>
       </c>
-      <c r="C332" s="6"/>
+      <c r="C332" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D332" s="6"/>
       <c r="F332">
         <v>979</v>
@@ -8011,7 +8389,9 @@
       <c r="B333" s="6">
         <v>9</v>
       </c>
-      <c r="C333" s="6"/>
+      <c r="C333" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D333" s="6"/>
       <c r="F333">
         <v>990</v>
@@ -8031,7 +8411,9 @@
       <c r="B334" s="6">
         <v>2</v>
       </c>
-      <c r="C334" s="6"/>
+      <c r="C334" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D334" s="6"/>
       <c r="F334">
         <v>998</v>
@@ -8051,7 +8433,9 @@
       <c r="B335" s="6">
         <v>1</v>
       </c>
-      <c r="C335" s="6"/>
+      <c r="C335" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D335" s="6"/>
       <c r="F335">
         <v>999</v>
@@ -8071,7 +8455,9 @@
       <c r="B336" s="6">
         <v>2</v>
       </c>
-      <c r="C336" s="6"/>
+      <c r="C336" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D336" s="6"/>
       <c r="F336">
         <v>1001</v>
@@ -8091,7 +8477,9 @@
       <c r="B337" s="6">
         <v>5</v>
       </c>
-      <c r="C337" s="6"/>
+      <c r="C337" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D337" s="6"/>
       <c r="F337">
         <v>1003</v>
@@ -8111,7 +8499,9 @@
       <c r="B338" s="6">
         <v>2</v>
       </c>
-      <c r="C338" s="6"/>
+      <c r="C338" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D338" s="6"/>
       <c r="F338">
         <v>1005</v>
@@ -8131,7 +8521,9 @@
       <c r="B339" s="6">
         <v>2</v>
       </c>
-      <c r="C339" s="6"/>
+      <c r="C339" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D339" s="6"/>
       <c r="F339">
         <v>1010</v>
@@ -8151,7 +8543,9 @@
       <c r="B340" s="6">
         <v>5</v>
       </c>
-      <c r="C340" s="6"/>
+      <c r="C340" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D340" s="6"/>
       <c r="F340">
         <v>1011</v>
@@ -8171,7 +8565,9 @@
       <c r="B341" s="6">
         <v>2</v>
       </c>
-      <c r="C341" s="6"/>
+      <c r="C341" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D341" s="6"/>
       <c r="F341">
         <v>1017</v>
@@ -8191,7 +8587,9 @@
       <c r="B342" s="6">
         <v>0</v>
       </c>
-      <c r="C342" s="6"/>
+      <c r="C342" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D342" s="6"/>
       <c r="F342">
         <v>1018</v>
@@ -8211,7 +8609,9 @@
       <c r="B343" s="6">
         <v>6</v>
       </c>
-      <c r="C343" s="6"/>
+      <c r="C343" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D343" s="6"/>
       <c r="F343">
         <v>1023</v>
@@ -8231,7 +8631,9 @@
       <c r="B344" s="6">
         <v>1</v>
       </c>
-      <c r="C344" s="6"/>
+      <c r="C344" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D344" s="6"/>
       <c r="F344">
         <v>1025</v>
@@ -8251,17 +8653,19 @@
       <c r="B345" s="6">
         <v>9</v>
       </c>
-      <c r="C345" s="6"/>
+      <c r="C345" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D345" s="6"/>
       <c r="F345">
         <v>1027</v>
       </c>
       <c r="G345">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I345" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.3">
@@ -8271,7 +8675,9 @@
       <c r="B346" s="6">
         <v>5</v>
       </c>
-      <c r="C346" s="6"/>
+      <c r="C346" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D346" s="6"/>
       <c r="F346">
         <v>1029</v>
@@ -8291,7 +8697,9 @@
       <c r="B347" s="6">
         <v>0</v>
       </c>
-      <c r="C347" s="6"/>
+      <c r="C347" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D347" s="6"/>
       <c r="F347">
         <v>1032</v>
@@ -8311,7 +8719,9 @@
       <c r="B348" s="6">
         <v>4</v>
       </c>
-      <c r="C348" s="6"/>
+      <c r="C348" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D348" s="6"/>
       <c r="F348">
         <v>1034</v>
@@ -8331,7 +8741,9 @@
       <c r="B349" s="6">
         <v>2</v>
       </c>
-      <c r="C349" s="6"/>
+      <c r="C349" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D349" s="6"/>
       <c r="F349">
         <v>1036</v>
@@ -8351,17 +8763,19 @@
       <c r="B350" s="6">
         <v>6</v>
       </c>
-      <c r="C350" s="6"/>
+      <c r="C350" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D350" s="6"/>
       <c r="F350">
         <v>1037</v>
       </c>
       <c r="G350">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I350" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.3">
@@ -8371,7 +8785,9 @@
       <c r="B351" s="6">
         <v>4</v>
       </c>
-      <c r="C351" s="6"/>
+      <c r="C351" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D351" s="6"/>
       <c r="F351">
         <v>1041</v>
@@ -8391,7 +8807,9 @@
       <c r="B352" s="6">
         <v>0</v>
       </c>
-      <c r="C352" s="6"/>
+      <c r="C352" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D352" s="6"/>
       <c r="F352">
         <v>1044</v>
@@ -8411,7 +8829,9 @@
       <c r="B353" s="6">
         <v>1</v>
       </c>
-      <c r="C353" s="6"/>
+      <c r="C353" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D353" s="6"/>
       <c r="F353">
         <v>1047</v>
@@ -8431,7 +8851,9 @@
       <c r="B354" s="6">
         <v>2</v>
       </c>
-      <c r="C354" s="6"/>
+      <c r="C354" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D354" s="6"/>
       <c r="F354">
         <v>1048</v>
@@ -8451,7 +8873,9 @@
       <c r="B355" s="6">
         <v>1</v>
       </c>
-      <c r="C355" s="6"/>
+      <c r="C355" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D355" s="6"/>
       <c r="F355">
         <v>1052</v>
@@ -8471,7 +8895,9 @@
       <c r="B356" s="6">
         <v>2</v>
       </c>
-      <c r="C356" s="6"/>
+      <c r="C356" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D356" s="6"/>
       <c r="F356">
         <v>1053</v>
@@ -8491,7 +8917,9 @@
       <c r="B357" s="6">
         <v>1</v>
       </c>
-      <c r="C357" s="6"/>
+      <c r="C357" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D357" s="6"/>
       <c r="F357">
         <v>1055</v>
@@ -8511,7 +8939,9 @@
       <c r="B358" s="6">
         <v>1</v>
       </c>
-      <c r="C358" s="6"/>
+      <c r="C358" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D358" s="6"/>
       <c r="F358">
         <v>1057</v>
@@ -8531,17 +8961,19 @@
       <c r="B359" s="6">
         <v>1</v>
       </c>
-      <c r="C359" s="6"/>
+      <c r="C359" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D359" s="6"/>
       <c r="F359">
         <v>1061</v>
       </c>
       <c r="G359">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I359" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.3">
@@ -8551,7 +8983,9 @@
       <c r="B360" s="6">
         <v>2</v>
       </c>
-      <c r="C360" s="6"/>
+      <c r="C360" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D360" s="6"/>
       <c r="F360">
         <v>1064</v>
@@ -8571,7 +9005,9 @@
       <c r="B361" s="6">
         <v>1</v>
       </c>
-      <c r="C361" s="6"/>
+      <c r="C361" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D361" s="6"/>
       <c r="F361">
         <v>1071</v>
@@ -8591,7 +9027,9 @@
       <c r="B362" s="6">
         <v>2</v>
       </c>
-      <c r="C362" s="6"/>
+      <c r="C362" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D362" s="6"/>
       <c r="F362">
         <v>1072</v>
@@ -8611,7 +9049,9 @@
       <c r="B363" s="6">
         <v>2</v>
       </c>
-      <c r="C363" s="6"/>
+      <c r="C363" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D363" s="6"/>
       <c r="F363">
         <v>1073</v>
@@ -8631,7 +9071,9 @@
       <c r="B364" s="6">
         <v>1</v>
       </c>
-      <c r="C364" s="6"/>
+      <c r="C364" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D364" s="6"/>
       <c r="F364">
         <v>1075</v>
@@ -8651,7 +9093,9 @@
       <c r="B365" s="6">
         <v>7</v>
       </c>
-      <c r="C365" s="6"/>
+      <c r="C365" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D365" s="6"/>
       <c r="F365">
         <v>1078</v>
@@ -8671,7 +9115,9 @@
       <c r="B366" s="6">
         <v>1</v>
       </c>
-      <c r="C366" s="6"/>
+      <c r="C366" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D366" s="6"/>
       <c r="F366">
         <v>1080</v>
@@ -8691,7 +9137,9 @@
       <c r="B367" s="6">
         <v>0</v>
       </c>
-      <c r="C367" s="6"/>
+      <c r="C367" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D367" s="6"/>
       <c r="F367">
         <v>1084</v>
@@ -8711,7 +9159,9 @@
       <c r="B368" s="6">
         <v>1</v>
       </c>
-      <c r="C368" s="6"/>
+      <c r="C368" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D368" s="6"/>
       <c r="F368">
         <v>1089</v>
@@ -8731,7 +9181,9 @@
       <c r="B369" s="6">
         <v>6</v>
       </c>
-      <c r="C369" s="6"/>
+      <c r="C369" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D369" s="6"/>
       <c r="F369">
         <v>1090</v>
@@ -8751,7 +9203,9 @@
       <c r="B370" s="6">
         <v>6</v>
       </c>
-      <c r="C370" s="6"/>
+      <c r="C370" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D370" s="6"/>
       <c r="F370">
         <v>1091</v>
@@ -8771,7 +9225,9 @@
       <c r="B371" s="6">
         <v>4</v>
       </c>
-      <c r="C371" s="6"/>
+      <c r="C371" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D371" s="6"/>
       <c r="F371">
         <v>1093</v>
@@ -8791,7 +9247,9 @@
       <c r="B372" s="6">
         <v>3</v>
       </c>
-      <c r="C372" s="6"/>
+      <c r="C372" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D372" s="6"/>
       <c r="F372">
         <v>1094</v>
@@ -8811,7 +9269,9 @@
       <c r="B373" s="6">
         <v>4</v>
       </c>
-      <c r="C373" s="6"/>
+      <c r="C373" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D373" s="6"/>
       <c r="F373">
         <v>1097</v>
@@ -8831,7 +9291,9 @@
       <c r="B374" s="6">
         <v>2</v>
       </c>
-      <c r="C374" s="6"/>
+      <c r="C374" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D374" s="6"/>
       <c r="F374">
         <v>1100</v>
@@ -8851,7 +9313,9 @@
       <c r="B375" s="6">
         <v>7</v>
       </c>
-      <c r="C375" s="6"/>
+      <c r="C375" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D375" s="6"/>
       <c r="F375">
         <v>1102</v>
@@ -8871,7 +9335,9 @@
       <c r="B376" s="6">
         <v>0</v>
       </c>
-      <c r="C376" s="6"/>
+      <c r="C376" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D376" s="6"/>
       <c r="F376">
         <v>1103</v>
@@ -8891,7 +9357,9 @@
       <c r="B377" s="6">
         <v>1</v>
       </c>
-      <c r="C377" s="6"/>
+      <c r="C377" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D377" s="6"/>
       <c r="F377">
         <v>1105</v>
@@ -8911,7 +9379,9 @@
       <c r="B378" s="6">
         <v>0</v>
       </c>
-      <c r="C378" s="6"/>
+      <c r="C378" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D378" s="6"/>
       <c r="F378">
         <v>1110</v>
@@ -8931,7 +9401,9 @@
       <c r="B379" s="6">
         <v>1</v>
       </c>
-      <c r="C379" s="6"/>
+      <c r="C379" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D379" s="6"/>
       <c r="F379">
         <v>1113</v>
@@ -8951,7 +9423,9 @@
       <c r="B380" s="6">
         <v>4</v>
       </c>
-      <c r="C380" s="6"/>
+      <c r="C380" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D380" s="6"/>
       <c r="F380">
         <v>1114</v>
@@ -8971,7 +9445,9 @@
       <c r="B381" s="6">
         <v>1</v>
       </c>
-      <c r="C381" s="6"/>
+      <c r="C381" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D381" s="6"/>
       <c r="F381">
         <v>1116</v>
@@ -8991,7 +9467,9 @@
       <c r="B382" s="6">
         <v>4</v>
       </c>
-      <c r="C382" s="6"/>
+      <c r="C382" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D382" s="6"/>
       <c r="F382">
         <v>1124</v>
@@ -9011,7 +9489,9 @@
       <c r="B383" s="6">
         <v>2</v>
       </c>
-      <c r="C383" s="6"/>
+      <c r="C383" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D383" s="6"/>
       <c r="F383">
         <v>1125</v>
@@ -9031,7 +9511,9 @@
       <c r="B384" s="6">
         <v>1</v>
       </c>
-      <c r="C384" s="6"/>
+      <c r="C384" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D384" s="6"/>
       <c r="F384">
         <v>1127</v>
@@ -9051,7 +9533,9 @@
       <c r="B385" s="6">
         <v>5</v>
       </c>
-      <c r="C385" s="6"/>
+      <c r="C385" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D385" s="6"/>
       <c r="F385">
         <v>1128</v>
@@ -9071,7 +9555,9 @@
       <c r="B386" s="6">
         <v>5</v>
       </c>
-      <c r="C386" s="6"/>
+      <c r="C386" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D386" s="6"/>
       <c r="F386">
         <v>1133</v>
@@ -9091,7 +9577,9 @@
       <c r="B387" s="6">
         <v>1</v>
       </c>
-      <c r="C387" s="6"/>
+      <c r="C387" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D387" s="6"/>
       <c r="F387">
         <v>1134</v>
@@ -9111,7 +9599,9 @@
       <c r="B388" s="6">
         <v>2</v>
       </c>
-      <c r="C388" s="6"/>
+      <c r="C388" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D388" s="6"/>
       <c r="F388">
         <v>1135</v>
@@ -9131,7 +9621,9 @@
       <c r="B389" s="6">
         <v>6</v>
       </c>
-      <c r="C389" s="6"/>
+      <c r="C389" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D389" s="6"/>
       <c r="F389">
         <v>1149</v>
@@ -9151,7 +9643,9 @@
       <c r="B390" s="6">
         <v>4</v>
       </c>
-      <c r="C390" s="6"/>
+      <c r="C390" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D390" s="6"/>
       <c r="F390">
         <v>1151</v>
@@ -9171,7 +9665,9 @@
       <c r="B391" s="6">
         <v>1</v>
       </c>
-      <c r="C391" s="6"/>
+      <c r="C391" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D391" s="6"/>
       <c r="F391">
         <v>1157</v>
@@ -9191,7 +9687,9 @@
       <c r="B392" s="6">
         <v>4</v>
       </c>
-      <c r="C392" s="6"/>
+      <c r="C392" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D392" s="6"/>
       <c r="F392">
         <v>1159</v>
@@ -9211,7 +9709,9 @@
       <c r="B393" s="6">
         <v>6</v>
       </c>
-      <c r="C393" s="6"/>
+      <c r="C393" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D393" s="6"/>
       <c r="F393">
         <v>1161</v>
@@ -9231,7 +9731,9 @@
       <c r="B394" s="6">
         <v>9</v>
       </c>
-      <c r="C394" s="6"/>
+      <c r="C394" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D394" s="6"/>
       <c r="F394">
         <v>1173</v>
@@ -9251,7 +9753,9 @@
       <c r="B395" s="6">
         <v>2</v>
       </c>
-      <c r="C395" s="6"/>
+      <c r="C395" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D395" s="6"/>
       <c r="F395">
         <v>1174</v>
@@ -9271,7 +9775,9 @@
       <c r="B396" s="6">
         <v>3</v>
       </c>
-      <c r="C396" s="6"/>
+      <c r="C396" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D396" s="6"/>
       <c r="F396">
         <v>1177</v>
@@ -9291,7 +9797,9 @@
       <c r="B397" s="6">
         <v>1</v>
       </c>
-      <c r="C397" s="6"/>
+      <c r="C397" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D397" s="6"/>
       <c r="F397">
         <v>1178</v>
@@ -9311,7 +9819,9 @@
       <c r="B398" s="6">
         <v>3</v>
       </c>
-      <c r="C398" s="6"/>
+      <c r="C398" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D398" s="6"/>
       <c r="F398">
         <v>1179</v>
@@ -9331,7 +9841,9 @@
       <c r="B399" s="6">
         <v>2</v>
       </c>
-      <c r="C399" s="6"/>
+      <c r="C399" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D399" s="6"/>
       <c r="F399">
         <v>1187</v>
@@ -9351,7 +9863,9 @@
       <c r="B400" s="6">
         <v>7</v>
       </c>
-      <c r="C400" s="6"/>
+      <c r="C400" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D400" s="6"/>
       <c r="F400">
         <v>1188</v>
@@ -9371,7 +9885,9 @@
       <c r="B401" s="6">
         <v>6</v>
       </c>
-      <c r="C401" s="6"/>
+      <c r="C401" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D401" s="6"/>
       <c r="F401">
         <v>1195</v>
@@ -9391,8 +9907,12 @@
       <c r="B402" s="6">
         <v>1</v>
       </c>
-      <c r="C402" s="6"/>
-      <c r="D402" s="6"/>
+      <c r="C402" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D402" s="6">
+        <v>0</v>
+      </c>
       <c r="F402">
         <v>1196</v>
       </c>
@@ -9411,17 +9931,19 @@
       <c r="B403" s="6">
         <v>0</v>
       </c>
-      <c r="C403" s="6"/>
+      <c r="C403" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D403" s="6"/>
       <c r="F403">
         <v>1200</v>
       </c>
       <c r="G403">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I403" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.3">
@@ -9431,7 +9953,9 @@
       <c r="B404" s="6">
         <v>0</v>
       </c>
-      <c r="C404" s="6"/>
+      <c r="C404" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D404" s="6"/>
       <c r="F404">
         <v>1204</v>
@@ -9451,7 +9975,9 @@
       <c r="B405" s="6">
         <v>3</v>
       </c>
-      <c r="C405" s="6"/>
+      <c r="C405" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D405" s="6"/>
       <c r="F405">
         <v>1206</v>
@@ -9471,7 +9997,9 @@
       <c r="B406" s="6">
         <v>4</v>
       </c>
-      <c r="C406" s="6"/>
+      <c r="C406" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D406" s="6"/>
       <c r="F406">
         <v>1207</v>
@@ -9491,7 +10019,9 @@
       <c r="B407" s="6">
         <v>0</v>
       </c>
-      <c r="C407" s="6"/>
+      <c r="C407" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D407" s="6"/>
       <c r="F407">
         <v>1210</v>
@@ -9511,7 +10041,9 @@
       <c r="B408" s="6">
         <v>9</v>
       </c>
-      <c r="C408" s="6"/>
+      <c r="C408" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D408" s="6"/>
       <c r="F408">
         <v>1211</v>
@@ -9531,7 +10063,9 @@
       <c r="B409" s="6">
         <v>1</v>
       </c>
-      <c r="C409" s="6"/>
+      <c r="C409" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D409" s="6"/>
       <c r="F409">
         <v>1213</v>
@@ -9551,7 +10085,9 @@
       <c r="B410" s="6">
         <v>1</v>
       </c>
-      <c r="C410" s="6"/>
+      <c r="C410" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D410" s="6"/>
       <c r="F410">
         <v>1216</v>
@@ -9571,7 +10107,9 @@
       <c r="B411" s="6">
         <v>2</v>
       </c>
-      <c r="C411" s="6"/>
+      <c r="C411" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D411" s="6"/>
       <c r="F411">
         <v>1220</v>
@@ -9591,7 +10129,9 @@
       <c r="B412" s="6">
         <v>3</v>
       </c>
-      <c r="C412" s="6"/>
+      <c r="C412" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D412" s="6"/>
       <c r="F412">
         <v>1221</v>
@@ -9611,7 +10151,9 @@
       <c r="B413" s="6">
         <v>2</v>
       </c>
-      <c r="C413" s="6"/>
+      <c r="C413" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D413" s="6"/>
       <c r="F413">
         <v>1222</v>
@@ -9631,7 +10173,9 @@
       <c r="B414" s="6">
         <v>3</v>
       </c>
-      <c r="C414" s="6"/>
+      <c r="C414" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D414" s="6"/>
       <c r="F414">
         <v>1225</v>
@@ -9651,7 +10195,9 @@
       <c r="B415" s="6">
         <v>2</v>
       </c>
-      <c r="C415" s="6"/>
+      <c r="C415" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D415" s="6"/>
       <c r="F415">
         <v>1228</v>
@@ -9671,7 +10217,9 @@
       <c r="B416" s="6">
         <v>6</v>
       </c>
-      <c r="C416" s="6"/>
+      <c r="C416" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D416" s="6"/>
       <c r="F416">
         <v>1233</v>
@@ -9691,7 +10239,9 @@
       <c r="B417" s="6">
         <v>1</v>
       </c>
-      <c r="C417" s="6"/>
+      <c r="C417" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D417" s="6"/>
       <c r="F417">
         <v>1234</v>
@@ -9711,7 +10261,9 @@
       <c r="B418" s="6">
         <v>6</v>
       </c>
-      <c r="C418" s="6"/>
+      <c r="C418" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D418" s="6"/>
       <c r="F418">
         <v>1235</v>
@@ -9731,7 +10283,9 @@
       <c r="B419" s="6">
         <v>3</v>
       </c>
-      <c r="C419" s="6"/>
+      <c r="C419" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D419" s="6"/>
       <c r="F419">
         <v>1236</v>
@@ -9751,7 +10305,9 @@
       <c r="B420" s="6">
         <v>2</v>
       </c>
-      <c r="C420" s="6"/>
+      <c r="C420" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D420" s="6"/>
       <c r="F420">
         <v>1237</v>
@@ -9771,7 +10327,9 @@
       <c r="B421" s="6">
         <v>1</v>
       </c>
-      <c r="C421" s="6"/>
+      <c r="C421" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D421" s="6"/>
       <c r="F421">
         <v>1239</v>
@@ -9791,7 +10349,9 @@
       <c r="B422" s="6">
         <v>2</v>
       </c>
-      <c r="C422" s="6"/>
+      <c r="C422" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D422" s="6"/>
       <c r="F422">
         <v>1241</v>
@@ -9811,7 +10371,9 @@
       <c r="B423" s="6">
         <v>2</v>
       </c>
-      <c r="C423" s="6"/>
+      <c r="C423" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D423" s="6"/>
       <c r="F423">
         <v>1242</v>
@@ -9831,7 +10393,9 @@
       <c r="B424" s="6">
         <v>1</v>
       </c>
-      <c r="C424" s="6"/>
+      <c r="C424" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D424" s="6"/>
       <c r="F424">
         <v>1244</v>
@@ -9851,7 +10415,9 @@
       <c r="B425" s="6">
         <v>3</v>
       </c>
-      <c r="C425" s="6"/>
+      <c r="C425" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D425" s="6"/>
       <c r="F425">
         <v>1251</v>
@@ -9871,7 +10437,9 @@
       <c r="B426" s="6">
         <v>7</v>
       </c>
-      <c r="C426" s="6"/>
+      <c r="C426" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D426" s="6"/>
       <c r="F426">
         <v>1253</v>
@@ -9891,7 +10459,9 @@
       <c r="B427" s="6">
         <v>2</v>
       </c>
-      <c r="C427" s="6"/>
+      <c r="C427" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D427" s="6"/>
       <c r="F427">
         <v>1255</v>
@@ -9911,7 +10481,9 @@
       <c r="B428" s="6">
         <v>1</v>
       </c>
-      <c r="C428" s="6"/>
+      <c r="C428" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D428" s="6"/>
       <c r="F428">
         <v>1260</v>
@@ -9931,7 +10503,9 @@
       <c r="B429" s="6">
         <v>2</v>
       </c>
-      <c r="C429" s="6"/>
+      <c r="C429" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D429" s="6"/>
       <c r="F429">
         <v>1261</v>
@@ -9951,7 +10525,9 @@
       <c r="B430" s="6">
         <v>3</v>
       </c>
-      <c r="C430" s="6"/>
+      <c r="C430" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D430" s="6"/>
       <c r="F430">
         <v>1268</v>
@@ -9971,7 +10547,9 @@
       <c r="B431" s="6">
         <v>1</v>
       </c>
-      <c r="C431" s="6"/>
+      <c r="C431" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D431" s="6"/>
       <c r="F431">
         <v>1270</v>
@@ -9991,7 +10569,9 @@
       <c r="B432" s="6">
         <v>2</v>
       </c>
-      <c r="C432" s="6"/>
+      <c r="C432" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D432" s="6"/>
       <c r="F432">
         <v>1272</v>
@@ -10011,7 +10591,9 @@
       <c r="B433" s="6">
         <v>0</v>
       </c>
-      <c r="C433" s="6"/>
+      <c r="C433" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D433" s="6"/>
       <c r="F433">
         <v>1278</v>
@@ -10031,17 +10613,19 @@
       <c r="B434" s="6">
         <v>2</v>
       </c>
-      <c r="C434" s="6"/>
+      <c r="C434" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D434" s="6"/>
       <c r="F434">
         <v>1283</v>
       </c>
       <c r="G434">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I434" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="435" spans="1:9" x14ac:dyDescent="0.3">
@@ -10051,7 +10635,9 @@
       <c r="B435" s="6">
         <v>2</v>
       </c>
-      <c r="C435" s="6"/>
+      <c r="C435" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D435" s="6"/>
       <c r="F435">
         <v>1286</v>
@@ -10071,7 +10657,9 @@
       <c r="B436" s="6">
         <v>2</v>
       </c>
-      <c r="C436" s="6"/>
+      <c r="C436" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D436" s="6"/>
       <c r="F436">
         <v>1289</v>
@@ -10091,7 +10679,9 @@
       <c r="B437" s="6">
         <v>1</v>
       </c>
-      <c r="C437" s="6"/>
+      <c r="C437" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D437" s="6"/>
       <c r="F437">
         <v>1292</v>
@@ -10111,7 +10701,9 @@
       <c r="B438" s="6">
         <v>3</v>
       </c>
-      <c r="C438" s="6"/>
+      <c r="C438" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D438" s="6"/>
       <c r="F438">
         <v>1295</v>
@@ -10131,7 +10723,9 @@
       <c r="B439" s="6">
         <v>9</v>
       </c>
-      <c r="C439" s="6"/>
+      <c r="C439" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D439" s="6"/>
       <c r="F439">
         <v>1298</v>
@@ -10151,7 +10745,9 @@
       <c r="B440" s="6">
         <v>0</v>
       </c>
-      <c r="C440" s="6"/>
+      <c r="C440" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D440" s="6"/>
       <c r="F440">
         <v>1299</v>
@@ -10171,7 +10767,9 @@
       <c r="B441" s="6">
         <v>1</v>
       </c>
-      <c r="C441" s="6"/>
+      <c r="C441" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D441" s="6"/>
       <c r="F441">
         <v>1302</v>
@@ -10191,7 +10789,9 @@
       <c r="B442" s="6">
         <v>1</v>
       </c>
-      <c r="C442" s="6"/>
+      <c r="C442" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D442" s="6"/>
       <c r="F442">
         <v>1307</v>
@@ -10211,7 +10811,9 @@
       <c r="B443" s="6">
         <v>1</v>
       </c>
-      <c r="C443" s="6"/>
+      <c r="C443" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D443" s="6"/>
       <c r="F443">
         <v>1309</v>
@@ -10231,7 +10833,9 @@
       <c r="B444" s="6">
         <v>0</v>
       </c>
-      <c r="C444" s="6"/>
+      <c r="C444" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D444" s="6"/>
       <c r="F444">
         <v>1316</v>
@@ -10251,7 +10855,9 @@
       <c r="B445" s="6">
         <v>4</v>
       </c>
-      <c r="C445" s="6"/>
+      <c r="C445" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D445" s="6"/>
       <c r="F445">
         <v>1317</v>
@@ -10271,7 +10877,9 @@
       <c r="B446" s="6">
         <v>6</v>
       </c>
-      <c r="C446" s="6"/>
+      <c r="C446" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D446" s="6"/>
       <c r="F446">
         <v>1320</v>
@@ -10291,7 +10899,9 @@
       <c r="B447" s="6">
         <v>2</v>
       </c>
-      <c r="C447" s="6"/>
+      <c r="C447" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D447" s="6"/>
       <c r="F447">
         <v>1323</v>
@@ -10311,7 +10921,9 @@
       <c r="B448" s="6">
         <v>3</v>
       </c>
-      <c r="C448" s="6"/>
+      <c r="C448" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D448" s="6"/>
       <c r="F448">
         <v>1338</v>
@@ -10331,7 +10943,9 @@
       <c r="B449" s="6">
         <v>1</v>
       </c>
-      <c r="C449" s="6"/>
+      <c r="C449" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D449" s="6"/>
       <c r="F449">
         <v>1345</v>
@@ -10351,7 +10965,9 @@
       <c r="B450" s="6">
         <v>1</v>
       </c>
-      <c r="C450" s="6"/>
+      <c r="C450" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D450" s="6"/>
       <c r="F450">
         <v>1350</v>
@@ -10371,7 +10987,9 @@
       <c r="B451" s="6">
         <v>8</v>
       </c>
-      <c r="C451" s="6"/>
+      <c r="C451" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D451" s="6"/>
       <c r="F451">
         <v>1351</v>
@@ -10391,7 +11009,9 @@
       <c r="B452" s="6">
         <v>0</v>
       </c>
-      <c r="C452" s="6"/>
+      <c r="C452" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D452" s="6"/>
       <c r="F452">
         <v>1356</v>
@@ -10411,7 +11031,9 @@
       <c r="B453" s="6">
         <v>0</v>
       </c>
-      <c r="C453" s="6"/>
+      <c r="C453" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D453" s="6"/>
       <c r="F453">
         <v>1357</v>
@@ -10431,7 +11053,9 @@
       <c r="B454" s="6">
         <v>0</v>
       </c>
-      <c r="C454" s="6"/>
+      <c r="C454" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D454" s="6"/>
       <c r="F454">
         <v>1359</v>
@@ -10451,7 +11075,9 @@
       <c r="B455" s="6">
         <v>0</v>
       </c>
-      <c r="C455" s="6"/>
+      <c r="C455" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D455" s="6"/>
       <c r="F455">
         <v>1361</v>
@@ -10471,7 +11097,9 @@
       <c r="B456" s="6">
         <v>2</v>
       </c>
-      <c r="C456" s="6"/>
+      <c r="C456" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D456" s="6"/>
       <c r="F456">
         <v>1362</v>
@@ -10491,7 +11119,9 @@
       <c r="B457" s="6">
         <v>2</v>
       </c>
-      <c r="C457" s="6"/>
+      <c r="C457" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D457" s="6"/>
       <c r="F457">
         <v>1364</v>
@@ -10511,7 +11141,9 @@
       <c r="B458" s="6">
         <v>4</v>
       </c>
-      <c r="C458" s="6"/>
+      <c r="C458" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D458" s="6"/>
       <c r="F458">
         <v>1373</v>
@@ -10531,7 +11163,9 @@
       <c r="B459" s="6">
         <v>2</v>
       </c>
-      <c r="C459" s="6"/>
+      <c r="C459" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D459" s="6"/>
       <c r="F459">
         <v>1376</v>
@@ -10551,7 +11185,9 @@
       <c r="B460" s="6">
         <v>5</v>
       </c>
-      <c r="C460" s="6"/>
+      <c r="C460" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D460" s="6"/>
       <c r="F460">
         <v>1378</v>
@@ -10571,7 +11207,9 @@
       <c r="B461" s="6">
         <v>1</v>
       </c>
-      <c r="C461" s="6"/>
+      <c r="C461" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D461" s="6"/>
       <c r="F461">
         <v>1381</v>
@@ -10591,8 +11229,12 @@
       <c r="B462" s="6">
         <v>2</v>
       </c>
-      <c r="C462" s="6"/>
-      <c r="D462" s="6"/>
+      <c r="C462" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D462" s="6">
+        <v>1</v>
+      </c>
       <c r="F462">
         <v>1391</v>
       </c>
@@ -10611,7 +11253,9 @@
       <c r="B463" s="6">
         <v>1</v>
       </c>
-      <c r="C463" s="6"/>
+      <c r="C463" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D463" s="6"/>
       <c r="F463">
         <v>1392</v>
@@ -10631,7 +11275,9 @@
       <c r="B464" s="6">
         <v>2</v>
       </c>
-      <c r="C464" s="6"/>
+      <c r="C464" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D464" s="6"/>
       <c r="F464">
         <v>1393</v>
@@ -10651,7 +11297,9 @@
       <c r="B465" s="6">
         <v>0</v>
       </c>
-      <c r="C465" s="6"/>
+      <c r="C465" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D465" s="6"/>
       <c r="F465">
         <v>1395</v>
@@ -10671,7 +11319,9 @@
       <c r="B466" s="6">
         <v>7</v>
       </c>
-      <c r="C466" s="6"/>
+      <c r="C466" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D466" s="6"/>
       <c r="F466">
         <v>1398</v>
@@ -10691,7 +11341,9 @@
       <c r="B467" s="6">
         <v>3</v>
       </c>
-      <c r="C467" s="6"/>
+      <c r="C467" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D467" s="6"/>
       <c r="F467">
         <v>1406</v>
@@ -10711,7 +11363,9 @@
       <c r="B468" s="6">
         <v>6</v>
       </c>
-      <c r="C468" s="6"/>
+      <c r="C468" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D468" s="6"/>
       <c r="F468">
         <v>1407</v>
@@ -10731,7 +11385,9 @@
       <c r="B469" s="6">
         <v>3</v>
       </c>
-      <c r="C469" s="6"/>
+      <c r="C469" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D469" s="6"/>
       <c r="F469">
         <v>1412</v>
@@ -10751,7 +11407,9 @@
       <c r="B470" s="6">
         <v>8</v>
       </c>
-      <c r="C470" s="6"/>
+      <c r="C470" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D470" s="6"/>
       <c r="F470">
         <v>1413</v>
@@ -10771,7 +11429,9 @@
       <c r="B471" s="6">
         <v>1</v>
       </c>
-      <c r="C471" s="6"/>
+      <c r="C471" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D471" s="6"/>
       <c r="F471">
         <v>1419</v>
@@ -10791,7 +11451,9 @@
       <c r="B472" s="6">
         <v>0</v>
       </c>
-      <c r="C472" s="6"/>
+      <c r="C472" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D472" s="6"/>
       <c r="F472">
         <v>1421</v>
@@ -10811,7 +11473,9 @@
       <c r="B473" s="6">
         <v>1</v>
       </c>
-      <c r="C473" s="6"/>
+      <c r="C473" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D473" s="6"/>
       <c r="F473">
         <v>1422</v>
@@ -10831,17 +11495,19 @@
       <c r="B474" s="6">
         <v>6</v>
       </c>
-      <c r="C474" s="6"/>
+      <c r="C474" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D474" s="6"/>
       <c r="F474">
         <v>1426</v>
       </c>
       <c r="G474">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I474" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="475" spans="1:9" x14ac:dyDescent="0.3">
@@ -10851,7 +11517,9 @@
       <c r="B475" s="6">
         <v>1</v>
       </c>
-      <c r="C475" s="6"/>
+      <c r="C475" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D475" s="6"/>
       <c r="F475">
         <v>1431</v>
@@ -10871,7 +11539,9 @@
       <c r="B476" s="6">
         <v>4</v>
       </c>
-      <c r="C476" s="6"/>
+      <c r="C476" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D476" s="6"/>
       <c r="F476">
         <v>1436</v>
@@ -10891,7 +11561,9 @@
       <c r="B477" s="6">
         <v>4</v>
       </c>
-      <c r="C477" s="6"/>
+      <c r="C477" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D477" s="6"/>
       <c r="F477">
         <v>1437</v>
@@ -10911,7 +11583,9 @@
       <c r="B478" s="6">
         <v>2</v>
       </c>
-      <c r="C478" s="6"/>
+      <c r="C478" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D478" s="6"/>
       <c r="F478">
         <v>1444</v>
@@ -10931,7 +11605,9 @@
       <c r="B479" s="6">
         <v>0</v>
       </c>
-      <c r="C479" s="6"/>
+      <c r="C479" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D479" s="6"/>
       <c r="F479">
         <v>1451</v>
@@ -10951,7 +11627,9 @@
       <c r="B480" s="6">
         <v>8</v>
       </c>
-      <c r="C480" s="6"/>
+      <c r="C480" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D480" s="6"/>
       <c r="F480">
         <v>1453</v>
@@ -10971,7 +11649,9 @@
       <c r="B481" s="6">
         <v>1</v>
       </c>
-      <c r="C481" s="6"/>
+      <c r="C481" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D481" s="6"/>
       <c r="F481">
         <v>1454</v>
@@ -10991,7 +11671,9 @@
       <c r="B482" s="6">
         <v>3</v>
       </c>
-      <c r="C482" s="6"/>
+      <c r="C482" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D482" s="6"/>
       <c r="F482">
         <v>1456</v>
@@ -11011,7 +11693,9 @@
       <c r="B483" s="6">
         <v>0</v>
       </c>
-      <c r="C483" s="6"/>
+      <c r="C483" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D483" s="6"/>
       <c r="F483">
         <v>1461</v>
@@ -11031,7 +11715,9 @@
       <c r="B484" s="6">
         <v>0</v>
       </c>
-      <c r="C484" s="6"/>
+      <c r="C484" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D484" s="6"/>
       <c r="F484">
         <v>1462</v>
@@ -11051,7 +11737,9 @@
       <c r="B485" s="6">
         <v>2</v>
       </c>
-      <c r="C485" s="6"/>
+      <c r="C485" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D485" s="6"/>
       <c r="F485">
         <v>1465</v>
@@ -11071,7 +11759,9 @@
       <c r="B486" s="6">
         <v>6</v>
       </c>
-      <c r="C486" s="6"/>
+      <c r="C486" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D486" s="6"/>
       <c r="F486">
         <v>1468</v>
@@ -11091,17 +11781,19 @@
       <c r="B487" s="6">
         <v>6</v>
       </c>
-      <c r="C487" s="6"/>
+      <c r="C487" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D487" s="6"/>
       <c r="F487">
         <v>1472</v>
       </c>
       <c r="G487">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I487" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="488" spans="1:9" x14ac:dyDescent="0.3">
@@ -11111,17 +11803,19 @@
       <c r="B488" s="6">
         <v>1</v>
       </c>
-      <c r="C488" s="6"/>
+      <c r="C488" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D488" s="6"/>
       <c r="F488">
         <v>1474</v>
       </c>
       <c r="G488">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I488" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="489" spans="1:9" x14ac:dyDescent="0.3">
@@ -11131,7 +11825,9 @@
       <c r="B489" s="6">
         <v>0</v>
       </c>
-      <c r="C489" s="6"/>
+      <c r="C489" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D489" s="6"/>
       <c r="F489">
         <v>1475</v>
@@ -11151,7 +11847,9 @@
       <c r="B490" s="6">
         <v>3</v>
       </c>
-      <c r="C490" s="6"/>
+      <c r="C490" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D490" s="6"/>
       <c r="F490">
         <v>1477</v>
@@ -11171,7 +11869,9 @@
       <c r="B491" s="6">
         <v>6</v>
       </c>
-      <c r="C491" s="6"/>
+      <c r="C491" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D491" s="6"/>
       <c r="F491">
         <v>1480</v>
@@ -11191,7 +11891,9 @@
       <c r="B492" s="6">
         <v>6</v>
       </c>
-      <c r="C492" s="6"/>
+      <c r="C492" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D492" s="6"/>
       <c r="F492">
         <v>1483</v>
@@ -11211,7 +11913,9 @@
       <c r="B493" s="6">
         <v>6</v>
       </c>
-      <c r="C493" s="6"/>
+      <c r="C493" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D493" s="6"/>
       <c r="F493">
         <v>1487</v>
@@ -11231,7 +11935,9 @@
       <c r="B494" s="6">
         <v>7</v>
       </c>
-      <c r="C494" s="6"/>
+      <c r="C494" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D494" s="6"/>
       <c r="F494">
         <v>1488</v>
@@ -11251,7 +11957,9 @@
       <c r="B495" s="6">
         <v>1</v>
       </c>
-      <c r="C495" s="6"/>
+      <c r="C495" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D495" s="6"/>
       <c r="F495">
         <v>1491</v>
@@ -11271,7 +11979,9 @@
       <c r="B496" s="6">
         <v>2</v>
       </c>
-      <c r="C496" s="6"/>
+      <c r="C496" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D496" s="6"/>
       <c r="F496">
         <v>1502</v>
@@ -11291,7 +12001,9 @@
       <c r="B497" s="6">
         <v>5</v>
       </c>
-      <c r="C497" s="6"/>
+      <c r="C497" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D497" s="6"/>
       <c r="F497">
         <v>1503</v>
@@ -11311,7 +12023,9 @@
       <c r="B498" s="6">
         <v>6</v>
       </c>
-      <c r="C498" s="6"/>
+      <c r="C498" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D498" s="6"/>
       <c r="F498">
         <v>1505</v>
@@ -11331,17 +12045,19 @@
       <c r="B499" s="6">
         <v>1</v>
       </c>
-      <c r="C499" s="6"/>
+      <c r="C499" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D499" s="6"/>
       <c r="F499">
         <v>1507</v>
       </c>
       <c r="G499">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I499" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="500" spans="1:9" x14ac:dyDescent="0.3">
@@ -11351,7 +12067,9 @@
       <c r="B500" s="6">
         <v>0</v>
       </c>
-      <c r="C500" s="6"/>
+      <c r="C500" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D500" s="6"/>
       <c r="F500">
         <v>1509</v>
@@ -11371,7 +12089,9 @@
       <c r="B501" s="6">
         <v>6</v>
       </c>
-      <c r="C501" s="6"/>
+      <c r="C501" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D501" s="6"/>
       <c r="F501">
         <v>1510</v>
@@ -11391,7 +12111,9 @@
       <c r="B502" s="6">
         <v>1</v>
       </c>
-      <c r="C502" s="6"/>
+      <c r="C502" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D502" s="6"/>
       <c r="F502">
         <v>1511</v>
@@ -11411,17 +12133,19 @@
       <c r="B503" s="6">
         <v>6</v>
       </c>
-      <c r="C503" s="6"/>
+      <c r="C503" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D503" s="6"/>
       <c r="F503">
         <v>1512</v>
       </c>
       <c r="G503">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I503" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="504" spans="1:9" x14ac:dyDescent="0.3">
@@ -11431,7 +12155,9 @@
       <c r="B504" s="6">
         <v>2</v>
       </c>
-      <c r="C504" s="6"/>
+      <c r="C504" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D504" s="6"/>
       <c r="F504">
         <v>1517</v>
@@ -11451,7 +12177,9 @@
       <c r="B505" s="6">
         <v>5</v>
       </c>
-      <c r="C505" s="6"/>
+      <c r="C505" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D505" s="6"/>
       <c r="F505">
         <v>1525</v>
@@ -11471,7 +12199,9 @@
       <c r="B506" s="6">
         <v>2</v>
       </c>
-      <c r="C506" s="6"/>
+      <c r="C506" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D506" s="6"/>
       <c r="F506">
         <v>1532</v>
@@ -11491,7 +12221,9 @@
       <c r="B507" s="6">
         <v>0</v>
       </c>
-      <c r="C507" s="6"/>
+      <c r="C507" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D507" s="6"/>
       <c r="F507">
         <v>1533</v>
@@ -11511,7 +12243,9 @@
       <c r="B508" s="6">
         <v>2</v>
       </c>
-      <c r="C508" s="6"/>
+      <c r="C508" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D508" s="6"/>
       <c r="F508">
         <v>1536</v>
@@ -11531,7 +12265,9 @@
       <c r="B509" s="6">
         <v>2</v>
       </c>
-      <c r="C509" s="6"/>
+      <c r="C509" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D509" s="6"/>
       <c r="F509">
         <v>1537</v>
@@ -11551,17 +12287,19 @@
       <c r="B510" s="6">
         <v>2</v>
       </c>
-      <c r="C510" s="6"/>
+      <c r="C510" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D510" s="6"/>
       <c r="F510">
         <v>1538</v>
       </c>
       <c r="G510">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I510" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="511" spans="1:9" x14ac:dyDescent="0.3">
@@ -11571,7 +12309,9 @@
       <c r="B511" s="6">
         <v>1</v>
       </c>
-      <c r="C511" s="6"/>
+      <c r="C511" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D511" s="6"/>
       <c r="F511">
         <v>1545</v>
@@ -11591,7 +12331,9 @@
       <c r="B512" s="6">
         <v>1</v>
       </c>
-      <c r="C512" s="6"/>
+      <c r="C512" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D512" s="6"/>
       <c r="F512">
         <v>1547</v>
@@ -11611,7 +12353,9 @@
       <c r="B513" s="6">
         <v>2</v>
       </c>
-      <c r="C513" s="6"/>
+      <c r="C513" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D513" s="6"/>
       <c r="F513">
         <v>1553</v>
@@ -11631,7 +12375,9 @@
       <c r="B514" s="6">
         <v>1</v>
       </c>
-      <c r="C514" s="6"/>
+      <c r="C514" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D514" s="6"/>
       <c r="F514">
         <v>1554</v>
@@ -11651,7 +12397,9 @@
       <c r="B515" s="6">
         <v>1</v>
       </c>
-      <c r="C515" s="6"/>
+      <c r="C515" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D515" s="6"/>
       <c r="F515">
         <v>1556</v>
@@ -11671,7 +12419,9 @@
       <c r="B516" s="6">
         <v>3</v>
       </c>
-      <c r="C516" s="6"/>
+      <c r="C516" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D516" s="6"/>
       <c r="F516">
         <v>1558</v>
@@ -11691,7 +12441,9 @@
       <c r="B517" s="6">
         <v>6</v>
       </c>
-      <c r="C517" s="6"/>
+      <c r="C517" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D517" s="6"/>
       <c r="F517">
         <v>1563</v>
@@ -11711,17 +12463,19 @@
       <c r="B518" s="6">
         <v>9</v>
       </c>
-      <c r="C518" s="6"/>
+      <c r="C518" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D518" s="6"/>
       <c r="F518">
         <v>1566</v>
       </c>
       <c r="G518">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I518" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="519" spans="1:9" x14ac:dyDescent="0.3">
@@ -11731,7 +12485,9 @@
       <c r="B519" s="6">
         <v>4</v>
       </c>
-      <c r="C519" s="6"/>
+      <c r="C519" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D519" s="6"/>
       <c r="F519">
         <v>1572</v>
@@ -11751,7 +12507,9 @@
       <c r="B520" s="6">
         <v>2</v>
       </c>
-      <c r="C520" s="6"/>
+      <c r="C520" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D520" s="6"/>
       <c r="F520">
         <v>1580</v>
@@ -11771,7 +12529,9 @@
       <c r="B521" s="6">
         <v>9</v>
       </c>
-      <c r="C521" s="6"/>
+      <c r="C521" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D521" s="6"/>
       <c r="F521">
         <v>1583</v>
@@ -11791,7 +12551,9 @@
       <c r="B522" s="6">
         <v>2</v>
       </c>
-      <c r="C522" s="6"/>
+      <c r="C522" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D522" s="6"/>
       <c r="F522">
         <v>1587</v>
@@ -11811,7 +12573,9 @@
       <c r="B523" s="6">
         <v>5</v>
       </c>
-      <c r="C523" s="6"/>
+      <c r="C523" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D523" s="6"/>
       <c r="F523">
         <v>1590</v>
@@ -11831,7 +12595,9 @@
       <c r="B524" s="6">
         <v>1</v>
       </c>
-      <c r="C524" s="6"/>
+      <c r="C524" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D524" s="6"/>
       <c r="F524">
         <v>1591</v>
@@ -11851,7 +12617,9 @@
       <c r="B525" s="6">
         <v>8</v>
       </c>
-      <c r="C525" s="6"/>
+      <c r="C525" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D525" s="6"/>
       <c r="F525">
         <v>1600</v>
@@ -11871,7 +12639,9 @@
       <c r="B526" s="6">
         <v>0</v>
       </c>
-      <c r="C526" s="6"/>
+      <c r="C526" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D526" s="6"/>
       <c r="F526">
         <v>1601</v>
@@ -11891,7 +12661,9 @@
       <c r="B527" s="6">
         <v>6</v>
       </c>
-      <c r="C527" s="6"/>
+      <c r="C527" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D527" s="6"/>
       <c r="F527">
         <v>1606</v>
@@ -11911,7 +12683,9 @@
       <c r="B528" s="6">
         <v>6</v>
       </c>
-      <c r="C528" s="6"/>
+      <c r="C528" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D528" s="6"/>
       <c r="F528">
         <v>1608</v>
@@ -11931,7 +12705,9 @@
       <c r="B529" s="6">
         <v>5</v>
       </c>
-      <c r="C529" s="6"/>
+      <c r="C529" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D529" s="6"/>
       <c r="F529">
         <v>1612</v>
@@ -11951,7 +12727,9 @@
       <c r="B530" s="6">
         <v>4</v>
       </c>
-      <c r="C530" s="6"/>
+      <c r="C530" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D530" s="6"/>
       <c r="F530">
         <v>1613</v>
@@ -11971,7 +12749,9 @@
       <c r="B531" s="6">
         <v>0</v>
       </c>
-      <c r="C531" s="6"/>
+      <c r="C531" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D531" s="6"/>
       <c r="F531">
         <v>1618</v>
@@ -11991,7 +12771,9 @@
       <c r="B532" s="6">
         <v>0</v>
       </c>
-      <c r="C532" s="6"/>
+      <c r="C532" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D532" s="6"/>
       <c r="F532">
         <v>1620</v>
@@ -12011,7 +12793,9 @@
       <c r="B533" s="6">
         <v>1</v>
       </c>
-      <c r="C533" s="6"/>
+      <c r="C533" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D533" s="6"/>
       <c r="F533">
         <v>1621</v>
@@ -12031,7 +12815,9 @@
       <c r="B534" s="6">
         <v>7</v>
       </c>
-      <c r="C534" s="6"/>
+      <c r="C534" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D534" s="6"/>
       <c r="F534">
         <v>1624</v>
@@ -12051,7 +12837,9 @@
       <c r="B535" s="6">
         <v>1</v>
       </c>
-      <c r="C535" s="6"/>
+      <c r="C535" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D535" s="6"/>
       <c r="F535">
         <v>1626</v>
@@ -12071,7 +12859,9 @@
       <c r="B536" s="6">
         <v>0</v>
       </c>
-      <c r="C536" s="6"/>
+      <c r="C536" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D536" s="6"/>
       <c r="F536">
         <v>1628</v>
@@ -12091,7 +12881,9 @@
       <c r="B537" s="6">
         <v>0</v>
       </c>
-      <c r="C537" s="6"/>
+      <c r="C537" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D537" s="6"/>
       <c r="F537">
         <v>1642</v>
@@ -12111,7 +12903,9 @@
       <c r="B538" s="6">
         <v>2</v>
       </c>
-      <c r="C538" s="6"/>
+      <c r="C538" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D538" s="6"/>
       <c r="F538">
         <v>1650</v>
@@ -12131,17 +12925,19 @@
       <c r="B539" s="6">
         <v>0</v>
       </c>
-      <c r="C539" s="6"/>
+      <c r="C539" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D539" s="6"/>
       <c r="F539">
         <v>1653</v>
       </c>
       <c r="G539">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I539" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="540" spans="1:9" x14ac:dyDescent="0.3">
@@ -12151,7 +12947,9 @@
       <c r="B540" s="6">
         <v>4</v>
       </c>
-      <c r="C540" s="6"/>
+      <c r="C540" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D540" s="6"/>
       <c r="F540">
         <v>1655</v>
@@ -12171,7 +12969,9 @@
       <c r="B541" s="6">
         <v>1</v>
       </c>
-      <c r="C541" s="6"/>
+      <c r="C541" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D541" s="6"/>
       <c r="F541">
         <v>1657</v>
@@ -12191,7 +12991,9 @@
       <c r="B542" s="6">
         <v>0</v>
       </c>
-      <c r="C542" s="6"/>
+      <c r="C542" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D542" s="6"/>
       <c r="F542">
         <v>1659</v>
@@ -12211,7 +13013,9 @@
       <c r="B543" s="6">
         <v>8</v>
       </c>
-      <c r="C543" s="6"/>
+      <c r="C543" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D543" s="6"/>
       <c r="F543">
         <v>1662</v>
@@ -12231,7 +13035,9 @@
       <c r="B544" s="6">
         <v>2</v>
       </c>
-      <c r="C544" s="6"/>
+      <c r="C544" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D544" s="6"/>
       <c r="F544">
         <v>1665</v>
@@ -12251,8 +13057,12 @@
       <c r="B545" s="6">
         <v>2</v>
       </c>
-      <c r="C545" s="6"/>
-      <c r="D545" s="6"/>
+      <c r="C545" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D545" s="6">
+        <v>1</v>
+      </c>
       <c r="F545">
         <v>1672</v>
       </c>
@@ -12271,7 +13081,9 @@
       <c r="B546" s="6">
         <v>2</v>
       </c>
-      <c r="C546" s="6"/>
+      <c r="C546" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D546" s="6"/>
       <c r="F546">
         <v>1674</v>
@@ -12291,7 +13103,9 @@
       <c r="B547" s="6">
         <v>3</v>
       </c>
-      <c r="C547" s="6"/>
+      <c r="C547" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D547" s="6"/>
       <c r="F547">
         <v>1675</v>
@@ -12311,7 +13125,9 @@
       <c r="B548" s="6">
         <v>1</v>
       </c>
-      <c r="C548" s="6"/>
+      <c r="C548" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D548" s="6"/>
       <c r="F548">
         <v>1681</v>
@@ -12331,7 +13147,9 @@
       <c r="B549" s="6">
         <v>6</v>
       </c>
-      <c r="C549" s="6"/>
+      <c r="C549" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D549" s="6"/>
       <c r="F549">
         <v>1684</v>
@@ -12351,7 +13169,9 @@
       <c r="B550" s="6">
         <v>6</v>
       </c>
-      <c r="C550" s="6"/>
+      <c r="C550" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D550" s="6"/>
       <c r="F550">
         <v>1688</v>
@@ -12371,7 +13191,9 @@
       <c r="B551" s="6">
         <v>2</v>
       </c>
-      <c r="C551" s="6"/>
+      <c r="C551" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D551" s="6"/>
       <c r="F551">
         <v>1689</v>
@@ -12391,7 +13213,9 @@
       <c r="B552" s="6">
         <v>2</v>
       </c>
-      <c r="C552" s="6"/>
+      <c r="C552" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D552" s="6"/>
       <c r="F552">
         <v>1690</v>
@@ -12411,7 +13235,9 @@
       <c r="B553" s="6">
         <v>1</v>
       </c>
-      <c r="C553" s="6"/>
+      <c r="C553" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D553" s="6"/>
       <c r="F553">
         <v>1691</v>
@@ -12431,7 +13257,9 @@
       <c r="B554" s="6">
         <v>1</v>
       </c>
-      <c r="C554" s="6"/>
+      <c r="C554" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D554" s="6"/>
       <c r="F554">
         <v>1702</v>
@@ -12451,7 +13279,9 @@
       <c r="B555" s="6">
         <v>1</v>
       </c>
-      <c r="C555" s="6"/>
+      <c r="C555" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D555" s="6"/>
       <c r="F555">
         <v>1706</v>
@@ -12471,17 +13301,19 @@
       <c r="B556" s="6">
         <v>7</v>
       </c>
-      <c r="C556" s="6"/>
+      <c r="C556" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D556" s="6"/>
       <c r="F556">
         <v>1710</v>
       </c>
       <c r="G556">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I556" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="557" spans="1:9" x14ac:dyDescent="0.3">
@@ -12491,7 +13323,9 @@
       <c r="B557" s="6">
         <v>3</v>
       </c>
-      <c r="C557" s="6"/>
+      <c r="C557" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D557" s="6"/>
       <c r="F557">
         <v>1712</v>
@@ -12511,7 +13345,9 @@
       <c r="B558" s="6">
         <v>6</v>
       </c>
-      <c r="C558" s="6"/>
+      <c r="C558" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D558" s="6"/>
       <c r="F558">
         <v>1713</v>
@@ -12531,7 +13367,9 @@
       <c r="B559" s="6">
         <v>9</v>
       </c>
-      <c r="C559" s="6"/>
+      <c r="C559" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D559" s="6"/>
       <c r="F559">
         <v>1717</v>
@@ -12551,7 +13389,9 @@
       <c r="B560" s="6">
         <v>6</v>
       </c>
-      <c r="C560" s="6"/>
+      <c r="C560" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D560" s="6"/>
       <c r="F560">
         <v>1718</v>
@@ -12571,7 +13411,9 @@
       <c r="B561" s="6">
         <v>1</v>
       </c>
-      <c r="C561" s="6"/>
+      <c r="C561" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D561" s="6"/>
       <c r="F561">
         <v>1720</v>
@@ -12591,7 +13433,9 @@
       <c r="B562" s="6">
         <v>0</v>
       </c>
-      <c r="C562" s="6"/>
+      <c r="C562" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D562" s="6"/>
       <c r="F562">
         <v>1721</v>
@@ -12611,7 +13455,9 @@
       <c r="B563" s="6">
         <v>7</v>
       </c>
-      <c r="C563" s="6"/>
+      <c r="C563" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D563" s="6"/>
       <c r="F563">
         <v>1725</v>
@@ -12631,7 +13477,9 @@
       <c r="B564" s="6">
         <v>4</v>
       </c>
-      <c r="C564" s="6"/>
+      <c r="C564" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D564" s="6"/>
       <c r="F564">
         <v>1727</v>
@@ -12651,7 +13499,9 @@
       <c r="B565" s="6">
         <v>1</v>
       </c>
-      <c r="C565" s="6"/>
+      <c r="C565" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D565" s="6"/>
       <c r="F565">
         <v>1730</v>
@@ -12671,7 +13521,9 @@
       <c r="B566" s="6">
         <v>6</v>
       </c>
-      <c r="C566" s="6"/>
+      <c r="C566" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D566" s="6"/>
       <c r="F566">
         <v>1731</v>
@@ -12691,7 +13543,9 @@
       <c r="B567" s="6">
         <v>1</v>
       </c>
-      <c r="C567" s="6"/>
+      <c r="C567" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D567" s="6"/>
       <c r="F567">
         <v>1735</v>
@@ -12711,7 +13565,9 @@
       <c r="B568" s="6">
         <v>6</v>
       </c>
-      <c r="C568" s="6"/>
+      <c r="C568" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D568" s="6"/>
       <c r="F568">
         <v>1736</v>
@@ -12731,7 +13587,9 @@
       <c r="B569" s="6">
         <v>3</v>
       </c>
-      <c r="C569" s="6"/>
+      <c r="C569" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D569" s="6"/>
       <c r="F569">
         <v>1738</v>
@@ -12751,7 +13609,9 @@
       <c r="B570" s="6">
         <v>6</v>
       </c>
-      <c r="C570" s="6"/>
+      <c r="C570" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D570" s="6"/>
       <c r="F570">
         <v>1741</v>
@@ -12771,7 +13631,9 @@
       <c r="B571" s="6">
         <v>0</v>
       </c>
-      <c r="C571" s="6"/>
+      <c r="C571" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D571" s="6"/>
       <c r="F571">
         <v>1742</v>
@@ -12791,7 +13653,9 @@
       <c r="B572" s="6">
         <v>1</v>
       </c>
-      <c r="C572" s="6"/>
+      <c r="C572" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D572" s="6"/>
       <c r="F572">
         <v>1743</v>
@@ -12811,7 +13675,9 @@
       <c r="B573" s="6">
         <v>6</v>
       </c>
-      <c r="C573" s="6"/>
+      <c r="C573" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D573" s="6"/>
       <c r="F573">
         <v>1744</v>
@@ -12831,7 +13697,9 @@
       <c r="B574" s="6">
         <v>1</v>
       </c>
-      <c r="C574" s="6"/>
+      <c r="C574" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D574" s="6"/>
       <c r="F574">
         <v>1745</v>
@@ -12851,7 +13719,9 @@
       <c r="B575" s="6">
         <v>2</v>
       </c>
-      <c r="C575" s="6"/>
+      <c r="C575" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D575" s="6"/>
       <c r="F575">
         <v>1749</v>
@@ -12871,7 +13741,9 @@
       <c r="B576" s="6">
         <v>3</v>
       </c>
-      <c r="C576" s="6"/>
+      <c r="C576" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D576" s="6"/>
       <c r="F576">
         <v>1756</v>
@@ -12891,7 +13763,9 @@
       <c r="B577" s="6">
         <v>0</v>
       </c>
-      <c r="C577" s="6"/>
+      <c r="C577" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D577" s="6"/>
       <c r="F577">
         <v>1763</v>
@@ -12911,7 +13785,9 @@
       <c r="B578" s="6">
         <v>0</v>
       </c>
-      <c r="C578" s="6"/>
+      <c r="C578" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D578" s="6"/>
       <c r="F578">
         <v>1764</v>
@@ -12931,7 +13807,9 @@
       <c r="B579" s="6">
         <v>1</v>
       </c>
-      <c r="C579" s="6"/>
+      <c r="C579" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D579" s="6"/>
       <c r="F579">
         <v>1766</v>
@@ -12951,7 +13829,9 @@
       <c r="B580" s="6">
         <v>0</v>
       </c>
-      <c r="C580" s="6"/>
+      <c r="C580" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D580" s="6"/>
       <c r="F580">
         <v>1767</v>
@@ -12971,7 +13851,9 @@
       <c r="B581" s="6">
         <v>1</v>
       </c>
-      <c r="C581" s="6"/>
+      <c r="C581" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D581" s="6"/>
       <c r="F581">
         <v>1778</v>
@@ -12991,7 +13873,9 @@
       <c r="B582" s="6">
         <v>0</v>
       </c>
-      <c r="C582" s="6"/>
+      <c r="C582" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D582" s="6"/>
       <c r="F582">
         <v>1780</v>
@@ -13011,7 +13895,9 @@
       <c r="B583" s="6">
         <v>1</v>
       </c>
-      <c r="C583" s="6"/>
+      <c r="C583" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D583" s="6"/>
       <c r="F583">
         <v>1786</v>
@@ -13031,7 +13917,9 @@
       <c r="B584" s="6">
         <v>4</v>
       </c>
-      <c r="C584" s="6"/>
+      <c r="C584" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D584" s="6"/>
       <c r="F584">
         <v>1788</v>
@@ -13051,7 +13939,9 @@
       <c r="B585" s="6">
         <v>2</v>
       </c>
-      <c r="C585" s="6"/>
+      <c r="C585" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D585" s="6"/>
       <c r="F585">
         <v>1795</v>
@@ -13071,7 +13961,9 @@
       <c r="B586" s="6">
         <v>7</v>
       </c>
-      <c r="C586" s="6"/>
+      <c r="C586" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D586" s="6"/>
       <c r="F586">
         <v>1800</v>
@@ -13091,7 +13983,9 @@
       <c r="B587" s="6">
         <v>1</v>
       </c>
-      <c r="C587" s="6"/>
+      <c r="C587" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D587" s="6"/>
       <c r="F587">
         <v>1801</v>
@@ -13111,17 +14005,19 @@
       <c r="B588" s="6">
         <v>1</v>
       </c>
-      <c r="C588" s="6"/>
+      <c r="C588" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D588" s="6"/>
       <c r="F588">
         <v>1809</v>
       </c>
       <c r="G588">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I588" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="589" spans="1:9" x14ac:dyDescent="0.3">
@@ -13131,7 +14027,9 @@
       <c r="B589" s="6">
         <v>3</v>
       </c>
-      <c r="C589" s="6"/>
+      <c r="C589" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D589" s="6"/>
       <c r="F589">
         <v>1811</v>
@@ -13151,7 +14049,9 @@
       <c r="B590" s="6">
         <v>0</v>
       </c>
-      <c r="C590" s="6"/>
+      <c r="C590" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D590" s="6"/>
       <c r="F590">
         <v>1814</v>
@@ -13171,7 +14071,9 @@
       <c r="B591" s="6">
         <v>6</v>
       </c>
-      <c r="C591" s="6"/>
+      <c r="C591" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D591" s="6"/>
       <c r="F591">
         <v>1815</v>
@@ -13191,7 +14093,9 @@
       <c r="B592" s="6">
         <v>3</v>
       </c>
-      <c r="C592" s="6"/>
+      <c r="C592" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D592" s="6"/>
       <c r="F592">
         <v>1817</v>
@@ -13211,7 +14115,9 @@
       <c r="B593" s="6">
         <v>2</v>
       </c>
-      <c r="C593" s="6"/>
+      <c r="C593" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D593" s="6"/>
       <c r="F593">
         <v>1820</v>
@@ -13231,8 +14137,12 @@
       <c r="B594" s="6">
         <v>6</v>
       </c>
-      <c r="C594" s="6"/>
-      <c r="D594" s="6"/>
+      <c r="C594" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D594" s="6">
+        <v>4</v>
+      </c>
       <c r="F594">
         <v>1829</v>
       </c>
@@ -13251,7 +14161,9 @@
       <c r="B595" s="6">
         <v>2</v>
       </c>
-      <c r="C595" s="6"/>
+      <c r="C595" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D595" s="6"/>
       <c r="F595">
         <v>1831</v>
@@ -13271,7 +14183,9 @@
       <c r="B596" s="6">
         <v>2</v>
       </c>
-      <c r="C596" s="6"/>
+      <c r="C596" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D596" s="6"/>
       <c r="F596">
         <v>1833</v>
@@ -13291,7 +14205,9 @@
       <c r="B597" s="6">
         <v>7</v>
       </c>
-      <c r="C597" s="6"/>
+      <c r="C597" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D597" s="6"/>
       <c r="F597">
         <v>1837</v>
@@ -13311,7 +14227,9 @@
       <c r="B598" s="6">
         <v>8</v>
       </c>
-      <c r="C598" s="6"/>
+      <c r="C598" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D598" s="6"/>
       <c r="F598">
         <v>1839</v>
@@ -13331,7 +14249,9 @@
       <c r="B599" s="6">
         <v>1</v>
       </c>
-      <c r="C599" s="6"/>
+      <c r="C599" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D599" s="6"/>
       <c r="F599">
         <v>1842</v>
@@ -13351,7 +14271,9 @@
       <c r="B600" s="6">
         <v>9</v>
       </c>
-      <c r="C600" s="6"/>
+      <c r="C600" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D600" s="6"/>
       <c r="F600">
         <v>1844</v>
@@ -13371,7 +14293,9 @@
       <c r="B601" s="6">
         <v>0</v>
       </c>
-      <c r="C601" s="6"/>
+      <c r="C601" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D601" s="6"/>
       <c r="F601">
         <v>1845</v>
@@ -13391,7 +14315,9 @@
       <c r="B602" s="6">
         <v>1</v>
       </c>
-      <c r="C602" s="6"/>
+      <c r="C602" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D602" s="6"/>
       <c r="F602">
         <v>1846</v>
@@ -13411,7 +14337,9 @@
       <c r="B603" s="6">
         <v>3</v>
       </c>
-      <c r="C603" s="6"/>
+      <c r="C603" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D603" s="6"/>
       <c r="F603">
         <v>1847</v>
@@ -13431,7 +14359,9 @@
       <c r="B604" s="6">
         <v>1</v>
       </c>
-      <c r="C604" s="6"/>
+      <c r="C604" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D604" s="6"/>
       <c r="F604">
         <v>1850</v>
@@ -13451,7 +14381,9 @@
       <c r="B605" s="6">
         <v>2</v>
       </c>
-      <c r="C605" s="6"/>
+      <c r="C605" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D605" s="6"/>
       <c r="F605">
         <v>1859</v>
@@ -13471,7 +14403,9 @@
       <c r="B606" s="6">
         <v>6</v>
       </c>
-      <c r="C606" s="6"/>
+      <c r="C606" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D606" s="6"/>
       <c r="F606">
         <v>1861</v>
@@ -13491,7 +14425,9 @@
       <c r="B607" s="6">
         <v>7</v>
       </c>
-      <c r="C607" s="6"/>
+      <c r="C607" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D607" s="6"/>
       <c r="F607">
         <v>1864</v>
@@ -13511,7 +14447,9 @@
       <c r="B608" s="6">
         <v>0</v>
       </c>
-      <c r="C608" s="6"/>
+      <c r="C608" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D608" s="6"/>
       <c r="F608">
         <v>1866</v>
@@ -13531,7 +14469,9 @@
       <c r="B609" s="6">
         <v>1</v>
       </c>
-      <c r="C609" s="6"/>
+      <c r="C609" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D609" s="6"/>
       <c r="F609">
         <v>1872</v>
@@ -13551,7 +14491,9 @@
       <c r="B610" s="6">
         <v>1</v>
       </c>
-      <c r="C610" s="6"/>
+      <c r="C610" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D610" s="6"/>
       <c r="F610">
         <v>1874</v>
@@ -13571,7 +14513,9 @@
       <c r="B611" s="6">
         <v>2</v>
       </c>
-      <c r="C611" s="6"/>
+      <c r="C611" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D611" s="6"/>
       <c r="F611">
         <v>1877</v>
@@ -13591,7 +14535,9 @@
       <c r="B612" s="6">
         <v>2</v>
       </c>
-      <c r="C612" s="6"/>
+      <c r="C612" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D612" s="6"/>
       <c r="F612">
         <v>1880</v>
@@ -13611,17 +14557,19 @@
       <c r="B613" s="6">
         <v>9</v>
       </c>
-      <c r="C613" s="6"/>
+      <c r="C613" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D613" s="6"/>
       <c r="F613">
         <v>1883</v>
       </c>
       <c r="G613">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I613" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="614" spans="1:9" x14ac:dyDescent="0.3">
@@ -13631,7 +14579,9 @@
       <c r="B614" s="6">
         <v>5</v>
       </c>
-      <c r="C614" s="6"/>
+      <c r="C614" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D614" s="6"/>
       <c r="F614">
         <v>1889</v>
@@ -13651,7 +14601,9 @@
       <c r="B615" s="6">
         <v>1</v>
       </c>
-      <c r="C615" s="6"/>
+      <c r="C615" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D615" s="6"/>
       <c r="F615">
         <v>1891</v>
@@ -13671,7 +14623,9 @@
       <c r="B616" s="6">
         <v>1</v>
       </c>
-      <c r="C616" s="6"/>
+      <c r="C616" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D616" s="6"/>
       <c r="F616">
         <v>1896</v>
@@ -13691,7 +14645,9 @@
       <c r="B617" s="6">
         <v>2</v>
       </c>
-      <c r="C617" s="6"/>
+      <c r="C617" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D617" s="6"/>
       <c r="F617">
         <v>1904</v>
@@ -13711,7 +14667,9 @@
       <c r="B618" s="6">
         <v>1</v>
       </c>
-      <c r="C618" s="6"/>
+      <c r="C618" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D618" s="6"/>
       <c r="F618">
         <v>1910</v>
@@ -13731,17 +14689,19 @@
       <c r="B619" s="6">
         <v>1</v>
       </c>
-      <c r="C619" s="6"/>
+      <c r="C619" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D619" s="6"/>
       <c r="F619">
         <v>1911</v>
       </c>
       <c r="G619">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I619" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="620" spans="1:9" x14ac:dyDescent="0.3">
@@ -13751,13 +14711,15 @@
       <c r="B620" s="6">
         <v>6</v>
       </c>
-      <c r="C620" s="6"/>
+      <c r="C620" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D620" s="6"/>
       <c r="F620">
         <v>1912</v>
       </c>
       <c r="G620">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I620" s="6" t="str">
         <f t="shared" si="9"/>
@@ -13771,7 +14733,9 @@
       <c r="B621" s="6">
         <v>1</v>
       </c>
-      <c r="C621" s="6"/>
+      <c r="C621" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D621" s="6"/>
       <c r="F621">
         <v>1915</v>
@@ -13791,7 +14755,9 @@
       <c r="B622" s="6">
         <v>0</v>
       </c>
-      <c r="C622" s="6"/>
+      <c r="C622" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D622" s="6"/>
       <c r="F622">
         <v>1916</v>
@@ -13811,7 +14777,9 @@
       <c r="B623" s="6">
         <v>1</v>
       </c>
-      <c r="C623" s="6"/>
+      <c r="C623" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D623" s="6"/>
       <c r="F623">
         <v>1924</v>
@@ -13831,7 +14799,9 @@
       <c r="B624" s="6">
         <v>2</v>
       </c>
-      <c r="C624" s="6"/>
+      <c r="C624" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D624" s="6"/>
       <c r="F624">
         <v>1925</v>
@@ -13851,7 +14821,9 @@
       <c r="B625" s="6">
         <v>0</v>
       </c>
-      <c r="C625" s="6"/>
+      <c r="C625" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D625" s="6"/>
       <c r="F625">
         <v>1926</v>
@@ -13871,7 +14843,9 @@
       <c r="B626" s="6">
         <v>2</v>
       </c>
-      <c r="C626" s="6"/>
+      <c r="C626" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D626" s="6"/>
       <c r="F626">
         <v>1933</v>
@@ -13891,7 +14865,9 @@
       <c r="B627" s="6">
         <v>0</v>
       </c>
-      <c r="C627" s="6"/>
+      <c r="C627" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D627" s="6"/>
       <c r="F627">
         <v>1936</v>
@@ -13911,7 +14887,9 @@
       <c r="B628" s="6">
         <v>1</v>
       </c>
-      <c r="C628" s="6"/>
+      <c r="C628" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D628" s="6"/>
       <c r="F628">
         <v>1938</v>
@@ -13931,7 +14909,9 @@
       <c r="B629" s="6">
         <v>1</v>
       </c>
-      <c r="C629" s="6"/>
+      <c r="C629" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D629" s="6"/>
       <c r="F629">
         <v>1939</v>
@@ -13951,7 +14931,9 @@
       <c r="B630" s="6">
         <v>3</v>
       </c>
-      <c r="C630" s="6"/>
+      <c r="C630" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D630" s="6"/>
       <c r="F630">
         <v>1940</v>
@@ -13971,7 +14953,9 @@
       <c r="B631" s="6">
         <v>6</v>
       </c>
-      <c r="C631" s="6"/>
+      <c r="C631" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D631" s="6"/>
       <c r="F631">
         <v>1941</v>
@@ -13991,7 +14975,9 @@
       <c r="B632" s="6">
         <v>0</v>
       </c>
-      <c r="C632" s="6"/>
+      <c r="C632" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D632" s="6"/>
       <c r="F632">
         <v>1950</v>
@@ -14011,7 +14997,9 @@
       <c r="B633" s="6">
         <v>6</v>
       </c>
-      <c r="C633" s="6"/>
+      <c r="C633" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D633" s="6"/>
       <c r="F633">
         <v>1951</v>
@@ -14031,7 +15019,9 @@
       <c r="B634" s="6">
         <v>3</v>
       </c>
-      <c r="C634" s="6"/>
+      <c r="C634" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D634" s="6"/>
       <c r="F634">
         <v>1953</v>
@@ -14051,7 +15041,9 @@
       <c r="B635" s="6">
         <v>2</v>
       </c>
-      <c r="C635" s="6"/>
+      <c r="C635" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D635" s="6"/>
       <c r="F635">
         <v>1954</v>
@@ -14071,7 +15063,9 @@
       <c r="B636" s="6">
         <v>1</v>
       </c>
-      <c r="C636" s="6"/>
+      <c r="C636" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D636" s="6"/>
       <c r="F636">
         <v>1960</v>
@@ -14091,7 +15085,9 @@
       <c r="B637" s="6">
         <v>1</v>
       </c>
-      <c r="C637" s="6"/>
+      <c r="C637" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D637" s="6"/>
       <c r="F637">
         <v>1961</v>
@@ -14111,7 +15107,9 @@
       <c r="B638" s="6">
         <v>2</v>
       </c>
-      <c r="C638" s="6"/>
+      <c r="C638" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D638" s="6"/>
       <c r="F638">
         <v>1962</v>
@@ -14131,7 +15129,9 @@
       <c r="B639" s="6">
         <v>5</v>
       </c>
-      <c r="C639" s="6"/>
+      <c r="C639" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D639" s="6"/>
       <c r="F639">
         <v>1965</v>
@@ -14151,7 +15151,9 @@
       <c r="B640" s="6">
         <v>1</v>
       </c>
-      <c r="C640" s="6"/>
+      <c r="C640" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D640" s="6"/>
       <c r="F640">
         <v>1966</v>
@@ -14171,7 +15173,9 @@
       <c r="B641" s="6">
         <v>1</v>
       </c>
-      <c r="C641" s="6"/>
+      <c r="C641" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D641" s="6"/>
       <c r="F641">
         <v>1967</v>
@@ -14191,7 +15195,9 @@
       <c r="B642" s="6">
         <v>8</v>
       </c>
-      <c r="C642" s="6"/>
+      <c r="C642" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D642" s="6"/>
       <c r="F642">
         <v>1971</v>
@@ -14211,7 +15217,9 @@
       <c r="B643" s="6">
         <v>9</v>
       </c>
-      <c r="C643" s="6"/>
+      <c r="C643" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D643" s="6"/>
       <c r="F643">
         <v>1973</v>
@@ -14231,7 +15239,9 @@
       <c r="B644" s="6">
         <v>6</v>
       </c>
-      <c r="C644" s="6"/>
+      <c r="C644" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D644" s="6"/>
       <c r="F644">
         <v>1977</v>
@@ -14251,7 +15261,9 @@
       <c r="B645" s="6">
         <v>6</v>
       </c>
-      <c r="C645" s="6"/>
+      <c r="C645" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D645" s="6"/>
       <c r="F645">
         <v>1980</v>
@@ -14271,7 +15283,9 @@
       <c r="B646" s="6">
         <v>2</v>
       </c>
-      <c r="C646" s="6"/>
+      <c r="C646" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D646" s="6"/>
       <c r="F646">
         <v>1985</v>
@@ -14291,7 +15305,9 @@
       <c r="B647" s="6">
         <v>0</v>
       </c>
-      <c r="C647" s="6"/>
+      <c r="C647" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D647" s="6"/>
       <c r="F647">
         <v>1988</v>
@@ -14311,7 +15327,9 @@
       <c r="B648" s="6">
         <v>1</v>
       </c>
-      <c r="C648" s="6"/>
+      <c r="C648" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D648" s="6"/>
       <c r="F648">
         <v>1992</v>
@@ -14331,7 +15349,9 @@
       <c r="B649" s="6">
         <v>5</v>
       </c>
-      <c r="C649" s="6"/>
+      <c r="C649" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D649" s="6"/>
       <c r="F649">
         <v>1995</v>
@@ -14351,7 +15371,9 @@
       <c r="B650" s="6">
         <v>2</v>
       </c>
-      <c r="C650" s="6"/>
+      <c r="C650" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D650" s="6"/>
       <c r="F650">
         <v>2004</v>
@@ -14371,7 +15393,9 @@
       <c r="B651" s="6">
         <v>6</v>
       </c>
-      <c r="C651" s="6"/>
+      <c r="C651" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D651" s="6"/>
       <c r="F651">
         <v>2005</v>
@@ -14391,7 +15415,9 @@
       <c r="B652" s="6">
         <v>2</v>
       </c>
-      <c r="C652" s="6"/>
+      <c r="C652" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D652" s="6"/>
       <c r="F652">
         <v>2007</v>
@@ -14411,7 +15437,9 @@
       <c r="B653" s="6">
         <v>2</v>
       </c>
-      <c r="C653" s="6"/>
+      <c r="C653" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D653" s="6"/>
       <c r="F653">
         <v>2009</v>
@@ -14431,7 +15459,9 @@
       <c r="B654" s="6">
         <v>2</v>
       </c>
-      <c r="C654" s="6"/>
+      <c r="C654" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D654" s="6"/>
       <c r="F654">
         <v>2011</v>
@@ -14451,7 +15481,9 @@
       <c r="B655" s="6">
         <v>4</v>
       </c>
-      <c r="C655" s="6"/>
+      <c r="C655" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D655" s="6"/>
       <c r="F655">
         <v>2014</v>
@@ -14471,7 +15503,9 @@
       <c r="B656" s="6">
         <v>2</v>
       </c>
-      <c r="C656" s="6"/>
+      <c r="C656" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D656" s="6"/>
       <c r="F656">
         <v>2015</v>
@@ -14491,7 +15525,9 @@
       <c r="B657" s="6">
         <v>0</v>
       </c>
-      <c r="C657" s="6"/>
+      <c r="C657" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D657" s="6"/>
       <c r="F657">
         <v>2022</v>
@@ -14511,17 +15547,19 @@
       <c r="B658" s="6">
         <v>1</v>
       </c>
-      <c r="C658" s="6"/>
+      <c r="C658" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D658" s="6"/>
       <c r="F658">
         <v>2025</v>
       </c>
       <c r="G658">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I658" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="659" spans="1:9" x14ac:dyDescent="0.3">
@@ -14531,17 +15569,19 @@
       <c r="B659" s="6">
         <v>1</v>
       </c>
-      <c r="C659" s="6"/>
+      <c r="C659" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D659" s="6"/>
       <c r="F659">
         <v>2028</v>
       </c>
       <c r="G659">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I659" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="660" spans="1:9" x14ac:dyDescent="0.3">
@@ -14551,7 +15591,9 @@
       <c r="B660" s="6">
         <v>1</v>
       </c>
-      <c r="C660" s="6"/>
+      <c r="C660" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D660" s="6"/>
       <c r="F660">
         <v>2029</v>
@@ -14571,7 +15613,9 @@
       <c r="B661" s="6">
         <v>5</v>
       </c>
-      <c r="C661" s="6"/>
+      <c r="C661" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D661" s="6"/>
       <c r="F661">
         <v>2030</v>
@@ -14591,7 +15635,9 @@
       <c r="B662" s="6">
         <v>1</v>
       </c>
-      <c r="C662" s="6"/>
+      <c r="C662" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D662" s="6"/>
       <c r="F662">
         <v>2031</v>
@@ -14611,7 +15657,9 @@
       <c r="B663" s="6">
         <v>1</v>
       </c>
-      <c r="C663" s="6"/>
+      <c r="C663" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D663" s="6"/>
       <c r="F663">
         <v>2033</v>
@@ -14631,7 +15679,9 @@
       <c r="B664" s="6">
         <v>5</v>
       </c>
-      <c r="C664" s="6"/>
+      <c r="C664" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D664" s="6"/>
       <c r="F664">
         <v>2044</v>
@@ -14651,7 +15701,9 @@
       <c r="B665" s="6">
         <v>2</v>
       </c>
-      <c r="C665" s="6"/>
+      <c r="C665" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D665" s="6"/>
       <c r="F665">
         <v>2045</v>
@@ -14671,7 +15723,9 @@
       <c r="B666" s="6">
         <v>4</v>
       </c>
-      <c r="C666" s="6"/>
+      <c r="C666" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D666" s="6"/>
       <c r="F666">
         <v>2050</v>
@@ -14691,7 +15745,9 @@
       <c r="B667" s="6">
         <v>6</v>
       </c>
-      <c r="C667" s="6"/>
+      <c r="C667" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D667" s="6"/>
       <c r="F667">
         <v>2051</v>
@@ -14711,7 +15767,9 @@
       <c r="B668" s="6">
         <v>2</v>
       </c>
-      <c r="C668" s="6"/>
+      <c r="C668" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D668" s="6"/>
       <c r="F668">
         <v>2053</v>
@@ -14731,7 +15789,9 @@
       <c r="B669" s="6">
         <v>1</v>
       </c>
-      <c r="C669" s="6"/>
+      <c r="C669" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D669" s="6"/>
       <c r="F669">
         <v>2059</v>
@@ -14751,7 +15811,9 @@
       <c r="B670" s="6">
         <v>3</v>
       </c>
-      <c r="C670" s="6"/>
+      <c r="C670" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D670" s="6"/>
       <c r="F670">
         <v>2063</v>
@@ -14771,7 +15833,9 @@
       <c r="B671" s="6">
         <v>1</v>
       </c>
-      <c r="C671" s="6"/>
+      <c r="C671" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D671" s="6"/>
       <c r="F671">
         <v>2066</v>
@@ -14791,7 +15855,9 @@
       <c r="B672" s="6">
         <v>0</v>
       </c>
-      <c r="C672" s="6"/>
+      <c r="C672" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D672" s="6"/>
       <c r="F672">
         <v>2073</v>
@@ -14811,7 +15877,9 @@
       <c r="B673" s="6">
         <v>1</v>
       </c>
-      <c r="C673" s="6"/>
+      <c r="C673" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D673" s="6"/>
       <c r="F673">
         <v>2078</v>
@@ -14831,7 +15899,9 @@
       <c r="B674" s="6">
         <v>0</v>
       </c>
-      <c r="C674" s="6"/>
+      <c r="C674" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D674" s="6"/>
       <c r="F674">
         <v>2079</v>
@@ -14851,7 +15921,9 @@
       <c r="B675" s="6">
         <v>0</v>
       </c>
-      <c r="C675" s="6"/>
+      <c r="C675" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D675" s="6"/>
       <c r="F675">
         <v>2086</v>
@@ -14871,7 +15943,9 @@
       <c r="B676" s="6">
         <v>2</v>
       </c>
-      <c r="C676" s="6"/>
+      <c r="C676" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D676" s="6"/>
       <c r="F676">
         <v>2090</v>
@@ -14891,7 +15965,9 @@
       <c r="B677" s="6">
         <v>2</v>
       </c>
-      <c r="C677" s="6"/>
+      <c r="C677" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D677" s="6"/>
       <c r="F677">
         <v>2096</v>
@@ -14911,7 +15987,9 @@
       <c r="B678" s="6">
         <v>5</v>
       </c>
-      <c r="C678" s="6"/>
+      <c r="C678" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D678" s="6"/>
       <c r="F678">
         <v>2112</v>
@@ -14931,7 +16009,9 @@
       <c r="B679" s="6">
         <v>3</v>
       </c>
-      <c r="C679" s="6"/>
+      <c r="C679" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D679" s="6"/>
       <c r="F679">
         <v>2113</v>
@@ -14951,7 +16031,9 @@
       <c r="B680" s="6">
         <v>0</v>
       </c>
-      <c r="C680" s="6"/>
+      <c r="C680" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D680" s="6"/>
       <c r="F680">
         <v>2119</v>
@@ -14971,7 +16053,9 @@
       <c r="B681" s="6">
         <v>8</v>
       </c>
-      <c r="C681" s="6"/>
+      <c r="C681" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D681" s="6"/>
       <c r="F681">
         <v>2123</v>
@@ -14991,7 +16075,9 @@
       <c r="B682" s="6">
         <v>0</v>
       </c>
-      <c r="C682" s="6"/>
+      <c r="C682" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D682" s="6"/>
       <c r="F682">
         <v>2126</v>
@@ -15011,7 +16097,9 @@
       <c r="B683" s="6">
         <v>1</v>
       </c>
-      <c r="C683" s="6"/>
+      <c r="C683" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D683" s="6"/>
       <c r="F683">
         <v>2130</v>
@@ -15031,7 +16119,9 @@
       <c r="B684" s="6">
         <v>6</v>
       </c>
-      <c r="C684" s="6"/>
+      <c r="C684" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D684" s="6"/>
       <c r="F684">
         <v>2132</v>
@@ -15051,7 +16141,9 @@
       <c r="B685" s="6">
         <v>6</v>
       </c>
-      <c r="C685" s="6"/>
+      <c r="C685" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D685" s="6"/>
       <c r="F685">
         <v>2138</v>
@@ -15071,7 +16163,9 @@
       <c r="B686" s="6">
         <v>2</v>
       </c>
-      <c r="C686" s="6"/>
+      <c r="C686" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D686" s="6"/>
       <c r="F686">
         <v>2149</v>
@@ -15091,8 +16185,12 @@
       <c r="B687" s="6">
         <v>2</v>
       </c>
-      <c r="C687" s="6"/>
-      <c r="D687" s="6"/>
+      <c r="C687" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D687" s="6">
+        <v>1</v>
+      </c>
       <c r="F687">
         <v>2153</v>
       </c>
@@ -15217,11 +16315,11 @@
         <v>2164</v>
       </c>
       <c r="G693">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I693" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="694" spans="1:9" x14ac:dyDescent="0.3">
@@ -15517,11 +16615,11 @@
         <v>2216</v>
       </c>
       <c r="G708">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I708" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="709" spans="1:9" x14ac:dyDescent="0.3">
@@ -16057,11 +17155,11 @@
         <v>2298</v>
       </c>
       <c r="G735">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I735" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="736" spans="1:9" x14ac:dyDescent="0.3">
@@ -16417,11 +17515,11 @@
         <v>2354</v>
       </c>
       <c r="G753">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I753" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="754" spans="1:9" x14ac:dyDescent="0.3">
@@ -17057,7 +18155,7 @@
         <v>2448</v>
       </c>
       <c r="G785">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I785" s="6" t="str">
         <f t="shared" si="12"/>
@@ -18837,11 +19935,11 @@
         <v>2714</v>
       </c>
       <c r="G874">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I874" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="875" spans="1:9" x14ac:dyDescent="0.3">
@@ -19257,11 +20355,11 @@
         <v>2783</v>
       </c>
       <c r="G895">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I895" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="896" spans="1:9" x14ac:dyDescent="0.3">
@@ -19417,11 +20515,11 @@
         <v>2802</v>
       </c>
       <c r="G903">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I903" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="904" spans="1:9" x14ac:dyDescent="0.3">
@@ -19877,11 +20975,11 @@
         <v>2852</v>
       </c>
       <c r="G926">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I926" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="927" spans="1:9" x14ac:dyDescent="0.3">
@@ -20177,11 +21275,11 @@
         <v>2901</v>
       </c>
       <c r="G941">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I941" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="942" spans="1:9" x14ac:dyDescent="0.3">
@@ -20237,11 +21335,11 @@
         <v>2907</v>
       </c>
       <c r="G944">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I944" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="945" spans="1:9" x14ac:dyDescent="0.3">
@@ -20897,11 +21995,11 @@
         <v>2994</v>
       </c>
       <c r="G977">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I977" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="978" spans="1:9" x14ac:dyDescent="0.3">
@@ -20937,11 +22035,11 @@
         <v>3008</v>
       </c>
       <c r="G979">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I979" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="980" spans="1:9" x14ac:dyDescent="0.3">
@@ -21117,11 +22215,11 @@
         <v>3044</v>
       </c>
       <c r="G988">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I988" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="989" spans="1:9" x14ac:dyDescent="0.3">
@@ -21257,11 +22355,11 @@
         <v>3075</v>
       </c>
       <c r="G995">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I995" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="996" spans="1:9" x14ac:dyDescent="0.3">
@@ -21297,11 +22395,11 @@
         <v>3079</v>
       </c>
       <c r="G997">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I997" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="998" spans="1:9" x14ac:dyDescent="0.3">

--- a/compareOP.xlsx
+++ b/compareOP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DUT\Ki 2\Edge AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D52865-C367-4247-99B8-A454AE73D3BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5ED780C-6664-4FE0-B750-6E6F6C6DBB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{56603411-7B59-498E-88B9-7E9448248F05}"/>
   </bookViews>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="L2" s="4">
         <f>COUNTIF(I2:I1001, "T")</f>
-        <v>966</v>
+        <v>950</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="L3" s="4">
         <f>L2/1000*100</f>
-        <v>96.6</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -3223,11 +3223,11 @@
         <v>270</v>
       </c>
       <c r="G98">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I98" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
@@ -3399,11 +3399,11 @@
         <v>289</v>
       </c>
       <c r="G106">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I106" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
@@ -3663,11 +3663,11 @@
         <v>324</v>
       </c>
       <c r="G118">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I118" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
@@ -4279,11 +4279,11 @@
         <v>415</v>
       </c>
       <c r="G146">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I146" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.3">
@@ -4477,11 +4477,11 @@
         <v>435</v>
       </c>
       <c r="G155">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I155" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
@@ -5005,11 +5005,11 @@
         <v>506</v>
       </c>
       <c r="G179">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I179" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
@@ -5071,11 +5071,11 @@
         <v>509</v>
       </c>
       <c r="G182">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I182" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.3">
@@ -5445,11 +5445,11 @@
         <v>555</v>
       </c>
       <c r="G199">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I199" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.3">
@@ -6151,7 +6151,7 @@
         <v>650</v>
       </c>
       <c r="G231">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I231" s="6" t="str">
         <f t="shared" si="3"/>
@@ -6417,7 +6417,7 @@
         <v>685</v>
       </c>
       <c r="G243">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I243" s="6" t="str">
         <f t="shared" si="3"/>
@@ -6439,11 +6439,11 @@
         <v>691</v>
       </c>
       <c r="G244">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I244" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.3">
@@ -6505,11 +6505,11 @@
         <v>700</v>
       </c>
       <c r="G247">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I247" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.3">
@@ -6637,11 +6637,11 @@
         <v>736</v>
       </c>
       <c r="G253">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I253" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.3">
@@ -6769,11 +6769,11 @@
         <v>755</v>
       </c>
       <c r="G259">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I259" s="6" t="str">
         <f t="shared" ref="I259:I322" si="4">IF(B259=G259, "T", "F")</f>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.3">
@@ -6923,11 +6923,11 @@
         <v>772</v>
       </c>
       <c r="G266">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I266" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.3">
@@ -7891,11 +7891,11 @@
         <v>900</v>
       </c>
       <c r="G310">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I310" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.3">
@@ -8353,11 +8353,11 @@
         <v>978</v>
       </c>
       <c r="G331">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I331" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.3">
@@ -8661,11 +8661,11 @@
         <v>1027</v>
       </c>
       <c r="G345">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I345" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.3">
@@ -8969,7 +8969,7 @@
         <v>1061</v>
       </c>
       <c r="G359">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I359" s="6" t="str">
         <f t="shared" si="5"/>
@@ -9123,11 +9123,11 @@
         <v>1080</v>
       </c>
       <c r="G366">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I366" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.3">
@@ -9629,11 +9629,11 @@
         <v>1149</v>
       </c>
       <c r="G389">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I389" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="390" spans="1:9" x14ac:dyDescent="0.3">
@@ -10621,7 +10621,7 @@
         <v>1283</v>
       </c>
       <c r="G434">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I434" s="6" t="str">
         <f t="shared" si="6"/>
@@ -10819,11 +10819,11 @@
         <v>1309</v>
       </c>
       <c r="G443">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I443" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="444" spans="1:9" x14ac:dyDescent="0.3">
@@ -12295,11 +12295,11 @@
         <v>1538</v>
       </c>
       <c r="G510">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I510" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="511" spans="1:9" x14ac:dyDescent="0.3">
@@ -12471,11 +12471,11 @@
         <v>1566</v>
       </c>
       <c r="G518">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I518" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="519" spans="1:9" x14ac:dyDescent="0.3">
@@ -12955,11 +12955,11 @@
         <v>1655</v>
       </c>
       <c r="G540">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I540" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="541" spans="1:9" x14ac:dyDescent="0.3">
@@ -13067,7 +13067,7 @@
         <v>1672</v>
       </c>
       <c r="G545">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I545" s="6" t="str">
         <f t="shared" si="8"/>
@@ -14147,11 +14147,11 @@
         <v>1829</v>
       </c>
       <c r="G594">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I594" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="595" spans="1:9" x14ac:dyDescent="0.3">
@@ -14565,11 +14565,11 @@
         <v>1883</v>
       </c>
       <c r="G613">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I613" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="614" spans="1:9" x14ac:dyDescent="0.3">
@@ -14719,11 +14719,11 @@
         <v>1912</v>
       </c>
       <c r="G620">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I620" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="621" spans="1:9" x14ac:dyDescent="0.3">
@@ -16195,7 +16195,7 @@
         <v>2153</v>
       </c>
       <c r="G687">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I687" s="6" t="str">
         <f t="shared" si="10"/>
@@ -17155,11 +17155,11 @@
         <v>2298</v>
       </c>
       <c r="G735">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I735" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="736" spans="1:9" x14ac:dyDescent="0.3">
@@ -17595,11 +17595,11 @@
         <v>2359</v>
       </c>
       <c r="G757">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I757" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="758" spans="1:9" x14ac:dyDescent="0.3">
@@ -18155,11 +18155,11 @@
         <v>2448</v>
       </c>
       <c r="G785">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I785" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="786" spans="1:9" x14ac:dyDescent="0.3">
@@ -18495,11 +18495,11 @@
         <v>2498</v>
       </c>
       <c r="G802">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I802" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="803" spans="1:9" x14ac:dyDescent="0.3">
@@ -19935,11 +19935,11 @@
         <v>2714</v>
       </c>
       <c r="G874">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I874" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="875" spans="1:9" x14ac:dyDescent="0.3">
@@ -20795,11 +20795,11 @@
         <v>2829</v>
       </c>
       <c r="G917">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I917" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="918" spans="1:9" x14ac:dyDescent="0.3">
@@ -20815,7 +20815,7 @@
         <v>2830</v>
       </c>
       <c r="G918">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I918" s="6" t="str">
         <f t="shared" si="14"/>
@@ -20975,11 +20975,11 @@
         <v>2852</v>
       </c>
       <c r="G926">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I926" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="927" spans="1:9" x14ac:dyDescent="0.3">
@@ -21275,11 +21275,11 @@
         <v>2901</v>
       </c>
       <c r="G941">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I941" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="942" spans="1:9" x14ac:dyDescent="0.3">
@@ -21335,11 +21335,11 @@
         <v>2907</v>
       </c>
       <c r="G944">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I944" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="945" spans="1:9" x14ac:dyDescent="0.3">
@@ -22215,11 +22215,11 @@
         <v>3044</v>
       </c>
       <c r="G988">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I988" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="989" spans="1:9" x14ac:dyDescent="0.3">
@@ -22295,11 +22295,11 @@
         <v>3057</v>
       </c>
       <c r="G992">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I992" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="993" spans="1:9" x14ac:dyDescent="0.3">

--- a/compareOP.xlsx
+++ b/compareOP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DUT\Ki 2\Edge AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76480449-2449-4498-BFFB-0BB30C4F3353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DCE91DF-654B-4BB1-B5C7-3264F3E053B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{56603411-7B59-498E-88B9-7E9448248F05}"/>
   </bookViews>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="L2" s="4">
         <f>COUNTIF(I2:I1001, "T")</f>
-        <v>962</v>
+        <v>967</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="L3" s="4">
         <f>L2/1000*100</f>
-        <v>96.2</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -1615,11 +1615,11 @@
         <v>80</v>
       </c>
       <c r="G26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I26" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
@@ -2056,7 +2056,7 @@
         <v>157</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I47" s="6" t="str">
         <f t="shared" si="0"/>
@@ -2728,7 +2728,7 @@
         <v>229</v>
       </c>
       <c r="G79">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I79" s="6" t="str">
         <f t="shared" si="1"/>
@@ -3001,11 +3001,11 @@
         <v>256</v>
       </c>
       <c r="G92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I92" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
@@ -3232,11 +3232,11 @@
         <v>282</v>
       </c>
       <c r="G103">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I103" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
@@ -3547,11 +3547,11 @@
         <v>324</v>
       </c>
       <c r="G118">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I118" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
@@ -3631,11 +3631,11 @@
         <v>340</v>
       </c>
       <c r="G122">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I122" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
@@ -4240,11 +4240,11 @@
         <v>424</v>
       </c>
       <c r="G151">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I151" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.3">
@@ -4324,7 +4324,7 @@
         <v>435</v>
       </c>
       <c r="G155">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I155" s="6" t="str">
         <f t="shared" si="2"/>
@@ -4408,11 +4408,11 @@
         <v>443</v>
       </c>
       <c r="G159">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I159" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
@@ -4555,11 +4555,11 @@
         <v>461</v>
       </c>
       <c r="G166">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I166" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
@@ -4786,11 +4786,11 @@
         <v>495</v>
       </c>
       <c r="G177">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I177" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.3">
@@ -5143,11 +5143,11 @@
         <v>544</v>
       </c>
       <c r="G194">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I194" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.3">
@@ -5542,11 +5542,11 @@
         <v>598</v>
       </c>
       <c r="G213">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I213" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.3">
@@ -5773,11 +5773,11 @@
         <v>621</v>
       </c>
       <c r="G224">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I224" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.3">
@@ -6172,7 +6172,7 @@
         <v>685</v>
       </c>
       <c r="G243">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I243" s="6" t="str">
         <f t="shared" si="3"/>
@@ -6256,7 +6256,7 @@
         <v>700</v>
       </c>
       <c r="G247">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I247" s="6" t="str">
         <f t="shared" si="3"/>
@@ -6277,7 +6277,7 @@
         <v>705</v>
       </c>
       <c r="G248">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I248" s="6" t="str">
         <f t="shared" si="3"/>
@@ -6382,7 +6382,7 @@
         <v>736</v>
       </c>
       <c r="G253">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I253" s="6" t="str">
         <f t="shared" si="3"/>
@@ -6508,11 +6508,11 @@
         <v>755</v>
       </c>
       <c r="G259">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I259" s="6" t="str">
         <f t="shared" ref="I259:I322" si="4">IF(B259=G259, "T", "F")</f>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.3">
@@ -6655,11 +6655,11 @@
         <v>772</v>
       </c>
       <c r="G266">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I266" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.3">
@@ -8020,11 +8020,11 @@
         <v>978</v>
       </c>
       <c r="G331">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I331" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.3">
@@ -8314,11 +8314,11 @@
         <v>1027</v>
       </c>
       <c r="G345">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I345" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.3">
@@ -8608,11 +8608,11 @@
         <v>1061</v>
       </c>
       <c r="G359">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I359" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.3">
@@ -8755,11 +8755,11 @@
         <v>1080</v>
       </c>
       <c r="G366">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I366" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.3">
@@ -9490,11 +9490,11 @@
         <v>1195</v>
       </c>
       <c r="G401">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I401" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="402" spans="1:9" x14ac:dyDescent="0.3">
@@ -9532,7 +9532,7 @@
         <v>1200</v>
       </c>
       <c r="G403">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I403" s="6" t="str">
         <f t="shared" si="6"/>
@@ -10183,11 +10183,11 @@
         <v>1283</v>
       </c>
       <c r="G434">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I434" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="435" spans="1:9" x14ac:dyDescent="0.3">
@@ -10750,7 +10750,7 @@
         <v>1381</v>
       </c>
       <c r="G461">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I461" s="6" t="str">
         <f t="shared" si="7"/>
@@ -10897,11 +10897,11 @@
         <v>1407</v>
       </c>
       <c r="G468">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I468" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="469" spans="1:9" x14ac:dyDescent="0.3">
@@ -11317,11 +11317,11 @@
         <v>1474</v>
       </c>
       <c r="G488">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I488" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="489" spans="1:9" x14ac:dyDescent="0.3">
@@ -11401,11 +11401,11 @@
         <v>1483</v>
       </c>
       <c r="G492">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I492" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="493" spans="1:9" x14ac:dyDescent="0.3">
@@ -11779,11 +11779,11 @@
         <v>1538</v>
       </c>
       <c r="G510">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I510" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="511" spans="1:9" x14ac:dyDescent="0.3">
@@ -11947,11 +11947,11 @@
         <v>1566</v>
       </c>
       <c r="G518">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I518" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="519" spans="1:9" x14ac:dyDescent="0.3">
@@ -13417,11 +13417,11 @@
         <v>1809</v>
       </c>
       <c r="G588">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I588" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="589" spans="1:9" x14ac:dyDescent="0.3">
@@ -13942,11 +13942,11 @@
         <v>1883</v>
       </c>
       <c r="G613">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I613" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="614" spans="1:9" x14ac:dyDescent="0.3">
@@ -14089,11 +14089,11 @@
         <v>1912</v>
       </c>
       <c r="G620">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I620" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="621" spans="1:9" x14ac:dyDescent="0.3">
@@ -14341,11 +14341,11 @@
         <v>1950</v>
       </c>
       <c r="G632">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I632" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="633" spans="1:9" x14ac:dyDescent="0.3">
@@ -14887,11 +14887,11 @@
         <v>2025</v>
       </c>
       <c r="G658">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I658" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="659" spans="1:9" x14ac:dyDescent="0.3">
@@ -14908,11 +14908,11 @@
         <v>2028</v>
       </c>
       <c r="G659">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I659" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="660" spans="1:9" x14ac:dyDescent="0.3">
@@ -15076,11 +15076,11 @@
         <v>2051</v>
       </c>
       <c r="G667">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I667" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="668" spans="1:9" x14ac:dyDescent="0.3">
@@ -15622,11 +15622,11 @@
         <v>2164</v>
       </c>
       <c r="G693">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I693" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="694" spans="1:9" x14ac:dyDescent="0.3">
@@ -15916,11 +15916,11 @@
         <v>2212</v>
       </c>
       <c r="G707">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I707" s="6" t="str">
         <f t="shared" ref="I707:I770" si="11">IF(B707=G707, "T", "F")</f>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="708" spans="1:9" x14ac:dyDescent="0.3">
@@ -16882,11 +16882,11 @@
         <v>2354</v>
       </c>
       <c r="G753">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I753" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="754" spans="1:9" x14ac:dyDescent="0.3">
@@ -17050,11 +17050,11 @@
         <v>2369</v>
       </c>
       <c r="G761">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I761" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="762" spans="1:9" x14ac:dyDescent="0.3">
@@ -17743,11 +17743,11 @@
         <v>2482</v>
       </c>
       <c r="G794">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I794" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="795" spans="1:9" x14ac:dyDescent="0.3">
@@ -17911,11 +17911,11 @@
         <v>2498</v>
       </c>
       <c r="G802">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I802" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="803" spans="1:9" x14ac:dyDescent="0.3">
@@ -18940,11 +18940,11 @@
         <v>2650</v>
       </c>
       <c r="G851">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I851" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="852" spans="1:9" x14ac:dyDescent="0.3">
@@ -20473,11 +20473,11 @@
         <v>2850</v>
       </c>
       <c r="G924">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I924" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="925" spans="1:9" x14ac:dyDescent="0.3">
@@ -20515,7 +20515,7 @@
         <v>2852</v>
       </c>
       <c r="G926">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I926" s="6" t="str">
         <f t="shared" si="14"/>
@@ -20830,11 +20830,11 @@
         <v>2901</v>
       </c>
       <c r="G941">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I941" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="942" spans="1:9" x14ac:dyDescent="0.3">
@@ -21586,11 +21586,11 @@
         <v>2994</v>
       </c>
       <c r="G977">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I977" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="978" spans="1:9" x14ac:dyDescent="0.3">
@@ -21817,11 +21817,11 @@
         <v>3044</v>
       </c>
       <c r="G988">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I988" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="989" spans="1:9" x14ac:dyDescent="0.3">
@@ -21901,11 +21901,11 @@
         <v>3057</v>
       </c>
       <c r="G992">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I992" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="993" spans="1:9" x14ac:dyDescent="0.3">
@@ -22006,11 +22006,11 @@
         <v>3079</v>
       </c>
       <c r="G997">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I997" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="998" spans="1:9" x14ac:dyDescent="0.3">

--- a/compareOP.xlsx
+++ b/compareOP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DUT\Ki 2\Edge AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DCE91DF-654B-4BB1-B5C7-3264F3E053B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73F165F-37D7-4AEF-A862-19873D3D0400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{56603411-7B59-498E-88B9-7E9448248F05}"/>
   </bookViews>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="L2" s="4">
         <f>COUNTIF(I2:I1001, "T")</f>
-        <v>967</v>
+        <v>960</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="L3" s="4">
         <f>L2/1000*100</f>
-        <v>96.7</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -1552,11 +1552,11 @@
         <v>70</v>
       </c>
       <c r="G23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I23" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
@@ -1615,11 +1615,11 @@
         <v>80</v>
       </c>
       <c r="G26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I26" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
@@ -1951,11 +1951,11 @@
         <v>139</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I42" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
@@ -2056,11 +2056,11 @@
         <v>157</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
@@ -2266,11 +2266,11 @@
         <v>177</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
@@ -2539,11 +2539,11 @@
         <v>210</v>
       </c>
       <c r="G70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I70" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
@@ -3001,11 +3001,11 @@
         <v>256</v>
       </c>
       <c r="G92">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I92" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
@@ -3547,11 +3547,11 @@
         <v>324</v>
       </c>
       <c r="G118">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I118" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
@@ -4030,11 +4030,11 @@
         <v>407</v>
       </c>
       <c r="G141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I141" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
@@ -4240,11 +4240,11 @@
         <v>424</v>
       </c>
       <c r="G151">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I151" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.3">
@@ -4324,7 +4324,7 @@
         <v>435</v>
       </c>
       <c r="G155">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I155" s="6" t="str">
         <f t="shared" si="2"/>
@@ -4408,11 +4408,11 @@
         <v>443</v>
       </c>
       <c r="G159">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I159" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
@@ -4555,11 +4555,11 @@
         <v>461</v>
       </c>
       <c r="G166">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I166" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
@@ -4786,11 +4786,11 @@
         <v>495</v>
       </c>
       <c r="G177">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I177" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.3">
@@ -4828,11 +4828,11 @@
         <v>506</v>
       </c>
       <c r="G179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I179" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
@@ -4891,11 +4891,11 @@
         <v>509</v>
       </c>
       <c r="G182">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I182" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.3">
@@ -5920,11 +5920,11 @@
         <v>650</v>
       </c>
       <c r="G231">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I231" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.3">
@@ -6172,7 +6172,7 @@
         <v>685</v>
       </c>
       <c r="G243">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I243" s="6" t="str">
         <f t="shared" si="3"/>
@@ -6256,11 +6256,11 @@
         <v>700</v>
       </c>
       <c r="G247">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I247" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.3">
@@ -6277,11 +6277,11 @@
         <v>705</v>
       </c>
       <c r="G248">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I248" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.3">
@@ -6382,11 +6382,11 @@
         <v>736</v>
       </c>
       <c r="G253">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I253" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.3">
@@ -6739,11 +6739,11 @@
         <v>785</v>
       </c>
       <c r="G270">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I270" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.3">
@@ -8314,7 +8314,7 @@
         <v>1027</v>
       </c>
       <c r="G345">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I345" s="6" t="str">
         <f t="shared" si="5"/>
@@ -8608,11 +8608,11 @@
         <v>1061</v>
       </c>
       <c r="G359">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I359" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.3">
@@ -8755,11 +8755,11 @@
         <v>1080</v>
       </c>
       <c r="G366">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I366" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.3">
@@ -9490,11 +9490,11 @@
         <v>1195</v>
       </c>
       <c r="G401">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I401" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="402" spans="1:9" x14ac:dyDescent="0.3">
@@ -9532,11 +9532,11 @@
         <v>1200</v>
       </c>
       <c r="G403">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I403" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.3">
@@ -10183,11 +10183,11 @@
         <v>1283</v>
       </c>
       <c r="G434">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I434" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="435" spans="1:9" x14ac:dyDescent="0.3">
@@ -10750,7 +10750,7 @@
         <v>1381</v>
       </c>
       <c r="G461">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I461" s="6" t="str">
         <f t="shared" si="7"/>
@@ -10897,11 +10897,11 @@
         <v>1407</v>
       </c>
       <c r="G468">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I468" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="469" spans="1:9" x14ac:dyDescent="0.3">
@@ -11317,7 +11317,7 @@
         <v>1474</v>
       </c>
       <c r="G488">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I488" s="6" t="str">
         <f t="shared" si="7"/>
@@ -11779,11 +11779,11 @@
         <v>1538</v>
       </c>
       <c r="G510">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I510" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="511" spans="1:9" x14ac:dyDescent="0.3">
@@ -13543,11 +13543,11 @@
         <v>1829</v>
       </c>
       <c r="G594">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I594" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="595" spans="1:9" x14ac:dyDescent="0.3">
@@ -13711,11 +13711,11 @@
         <v>1846</v>
       </c>
       <c r="G602">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I602" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="603" spans="1:9" x14ac:dyDescent="0.3">
@@ -14341,11 +14341,11 @@
         <v>1950</v>
       </c>
       <c r="G632">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I632" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="633" spans="1:9" x14ac:dyDescent="0.3">
@@ -15076,11 +15076,11 @@
         <v>2051</v>
       </c>
       <c r="G667">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I667" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="668" spans="1:9" x14ac:dyDescent="0.3">
@@ -15622,11 +15622,11 @@
         <v>2164</v>
       </c>
       <c r="G693">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I693" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="694" spans="1:9" x14ac:dyDescent="0.3">
@@ -15916,7 +15916,7 @@
         <v>2212</v>
       </c>
       <c r="G707">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I707" s="6" t="str">
         <f t="shared" ref="I707:I770" si="11">IF(B707=G707, "T", "F")</f>
@@ -16252,11 +16252,11 @@
         <v>2254</v>
       </c>
       <c r="G723">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I723" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="724" spans="1:9" x14ac:dyDescent="0.3">
@@ -16462,11 +16462,11 @@
         <v>2293</v>
       </c>
       <c r="G733">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I733" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="734" spans="1:9" x14ac:dyDescent="0.3">
@@ -17050,11 +17050,11 @@
         <v>2369</v>
       </c>
       <c r="G761">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I761" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="762" spans="1:9" x14ac:dyDescent="0.3">
@@ -17197,11 +17197,11 @@
         <v>2390</v>
       </c>
       <c r="G768">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I768" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="769" spans="1:9" x14ac:dyDescent="0.3">
@@ -17743,11 +17743,11 @@
         <v>2482</v>
       </c>
       <c r="G794">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I794" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="795" spans="1:9" x14ac:dyDescent="0.3">
@@ -17911,11 +17911,11 @@
         <v>2498</v>
       </c>
       <c r="G802">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I802" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="803" spans="1:9" x14ac:dyDescent="0.3">
@@ -18184,11 +18184,11 @@
         <v>2530</v>
       </c>
       <c r="G815">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I815" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="816" spans="1:9" x14ac:dyDescent="0.3">
@@ -19423,11 +19423,11 @@
         <v>2714</v>
       </c>
       <c r="G874">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I874" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="875" spans="1:9" x14ac:dyDescent="0.3">
@@ -20347,11 +20347,11 @@
         <v>2830</v>
       </c>
       <c r="G918">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I918" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="919" spans="1:9" x14ac:dyDescent="0.3">
@@ -20515,7 +20515,7 @@
         <v>2852</v>
       </c>
       <c r="G926">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I926" s="6" t="str">
         <f t="shared" si="14"/>
@@ -20830,11 +20830,11 @@
         <v>2901</v>
       </c>
       <c r="G941">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I941" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="942" spans="1:9" x14ac:dyDescent="0.3">
@@ -20893,7 +20893,7 @@
         <v>2907</v>
       </c>
       <c r="G944">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I944" s="6" t="str">
         <f t="shared" si="14"/>
@@ -21901,7 +21901,7 @@
         <v>3057</v>
       </c>
       <c r="G992">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I992" s="6" t="str">
         <f t="shared" si="15"/>
@@ -22006,11 +22006,11 @@
         <v>3079</v>
       </c>
       <c r="G997">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I997" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="998" spans="1:9" x14ac:dyDescent="0.3">

--- a/compareOP.xlsx
+++ b/compareOP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DUT\Ki 2\Edge AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73F165F-37D7-4AEF-A862-19873D3D0400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{029F255C-2BC4-4443-9276-66A8FD30EB0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{56603411-7B59-498E-88B9-7E9448248F05}"/>
   </bookViews>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="L2" s="4">
         <f>COUNTIF(I2:I1001, "T")</f>
-        <v>960</v>
+        <v>957</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="L3" s="4">
         <f>L2/1000*100</f>
-        <v>96</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -1135,11 +1135,11 @@
         <v>14</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I5" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
@@ -1489,11 +1489,11 @@
         <v>63</v>
       </c>
       <c r="G20">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I20" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
@@ -1552,11 +1552,11 @@
         <v>70</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I23" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
@@ -1867,11 +1867,11 @@
         <v>123</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
@@ -1951,11 +1951,11 @@
         <v>139</v>
       </c>
       <c r="G42">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I42" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
@@ -2266,11 +2266,11 @@
         <v>177</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
@@ -3001,11 +3001,11 @@
         <v>256</v>
       </c>
       <c r="G92">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I92" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
@@ -3631,11 +3631,11 @@
         <v>340</v>
       </c>
       <c r="G122">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I122" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
@@ -4030,11 +4030,11 @@
         <v>407</v>
       </c>
       <c r="G141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I141" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
@@ -4324,7 +4324,7 @@
         <v>435</v>
       </c>
       <c r="G155">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I155" s="6" t="str">
         <f t="shared" si="2"/>
@@ -4408,11 +4408,11 @@
         <v>443</v>
       </c>
       <c r="G159">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I159" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
@@ -4828,11 +4828,11 @@
         <v>506</v>
       </c>
       <c r="G179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I179" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
@@ -4891,7 +4891,7 @@
         <v>509</v>
       </c>
       <c r="G182">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I182" s="6" t="str">
         <f t="shared" si="2"/>
@@ -5143,11 +5143,11 @@
         <v>544</v>
       </c>
       <c r="G194">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I194" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.3">
@@ -5773,11 +5773,11 @@
         <v>621</v>
       </c>
       <c r="G224">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I224" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.3">
@@ -5920,7 +5920,7 @@
         <v>650</v>
       </c>
       <c r="G231">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I231" s="6" t="str">
         <f t="shared" si="3"/>
@@ -6172,7 +6172,7 @@
         <v>685</v>
       </c>
       <c r="G243">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I243" s="6" t="str">
         <f t="shared" si="3"/>
@@ -6739,11 +6739,11 @@
         <v>785</v>
       </c>
       <c r="G270">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I270" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.3">
@@ -7327,11 +7327,11 @@
         <v>859</v>
       </c>
       <c r="G298">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I298" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.3">
@@ -8020,11 +8020,11 @@
         <v>978</v>
       </c>
       <c r="G331">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I331" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.3">
@@ -8419,11 +8419,11 @@
         <v>1037</v>
       </c>
       <c r="G350">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I350" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.3">
@@ -9532,11 +9532,11 @@
         <v>1200</v>
       </c>
       <c r="G403">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I403" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.3">
@@ -10897,7 +10897,7 @@
         <v>1407</v>
       </c>
       <c r="G468">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I468" s="6" t="str">
         <f t="shared" si="7"/>
@@ -11632,11 +11632,11 @@
         <v>1512</v>
       </c>
       <c r="G503">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I503" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="504" spans="1:9" x14ac:dyDescent="0.3">
@@ -11779,11 +11779,11 @@
         <v>1538</v>
       </c>
       <c r="G510">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I510" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="511" spans="1:9" x14ac:dyDescent="0.3">
@@ -13417,11 +13417,11 @@
         <v>1809</v>
       </c>
       <c r="G588">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I588" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="589" spans="1:9" x14ac:dyDescent="0.3">
@@ -13543,7 +13543,7 @@
         <v>1829</v>
       </c>
       <c r="G594">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I594" s="6" t="str">
         <f t="shared" si="9"/>
@@ -13711,11 +13711,11 @@
         <v>1846</v>
       </c>
       <c r="G602">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I602" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="603" spans="1:9" x14ac:dyDescent="0.3">
@@ -13942,7 +13942,7 @@
         <v>1883</v>
       </c>
       <c r="G613">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I613" s="6" t="str">
         <f t="shared" si="9"/>
@@ -14068,11 +14068,11 @@
         <v>1911</v>
       </c>
       <c r="G619">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I619" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="620" spans="1:9" x14ac:dyDescent="0.3">
@@ -14089,11 +14089,11 @@
         <v>1912</v>
       </c>
       <c r="G620">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I620" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="621" spans="1:9" x14ac:dyDescent="0.3">
@@ -14908,11 +14908,11 @@
         <v>2028</v>
       </c>
       <c r="G659">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I659" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="660" spans="1:9" x14ac:dyDescent="0.3">
@@ -15076,11 +15076,11 @@
         <v>2051</v>
       </c>
       <c r="G667">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I667" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="668" spans="1:9" x14ac:dyDescent="0.3">
@@ -15370,11 +15370,11 @@
         <v>2123</v>
       </c>
       <c r="G681">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I681" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="682" spans="1:9" x14ac:dyDescent="0.3">
@@ -15496,11 +15496,11 @@
         <v>2153</v>
       </c>
       <c r="G687">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I687" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="688" spans="1:9" x14ac:dyDescent="0.3">
@@ -15622,11 +15622,11 @@
         <v>2164</v>
       </c>
       <c r="G693">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I693" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="694" spans="1:9" x14ac:dyDescent="0.3">
@@ -16252,11 +16252,11 @@
         <v>2254</v>
       </c>
       <c r="G723">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I723" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="724" spans="1:9" x14ac:dyDescent="0.3">
@@ -16462,11 +16462,11 @@
         <v>2293</v>
       </c>
       <c r="G733">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I733" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="734" spans="1:9" x14ac:dyDescent="0.3">
@@ -16483,11 +16483,11 @@
         <v>2295</v>
       </c>
       <c r="G734">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I734" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="735" spans="1:9" x14ac:dyDescent="0.3">
@@ -17197,11 +17197,11 @@
         <v>2390</v>
       </c>
       <c r="G768">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I768" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="769" spans="1:9" x14ac:dyDescent="0.3">
@@ -17911,11 +17911,11 @@
         <v>2498</v>
       </c>
       <c r="G802">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I802" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="803" spans="1:9" x14ac:dyDescent="0.3">
@@ -18184,11 +18184,11 @@
         <v>2530</v>
       </c>
       <c r="G815">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I815" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="816" spans="1:9" x14ac:dyDescent="0.3">
@@ -18688,11 +18688,11 @@
         <v>2609</v>
       </c>
       <c r="G839">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I839" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="840" spans="1:9" x14ac:dyDescent="0.3">
@@ -18940,11 +18940,11 @@
         <v>2650</v>
       </c>
       <c r="G851">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I851" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="852" spans="1:9" x14ac:dyDescent="0.3">
@@ -20158,11 +20158,11 @@
         <v>2810</v>
       </c>
       <c r="G909">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I909" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="910" spans="1:9" x14ac:dyDescent="0.3">
@@ -20515,7 +20515,7 @@
         <v>2852</v>
       </c>
       <c r="G926">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I926" s="6" t="str">
         <f t="shared" si="14"/>
@@ -20830,11 +20830,11 @@
         <v>2901</v>
       </c>
       <c r="G941">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I941" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="942" spans="1:9" x14ac:dyDescent="0.3">
@@ -21817,11 +21817,11 @@
         <v>3044</v>
       </c>
       <c r="G988">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I988" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="989" spans="1:9" x14ac:dyDescent="0.3">
@@ -21901,11 +21901,11 @@
         <v>3057</v>
       </c>
       <c r="G992">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I992" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="993" spans="1:9" x14ac:dyDescent="0.3">
@@ -22006,7 +22006,7 @@
         <v>3079</v>
       </c>
       <c r="G997">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I997" s="6" t="str">
         <f t="shared" si="15"/>

--- a/compareOP.xlsx
+++ b/compareOP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DUT\Ki 2\Edge AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{029F255C-2BC4-4443-9276-66A8FD30EB0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8EDB4B5-321A-4460-8171-A431E2C19E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{56603411-7B59-498E-88B9-7E9448248F05}"/>
   </bookViews>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="L2" s="4">
         <f>COUNTIF(I2:I1001, "T")</f>
-        <v>957</v>
+        <v>836</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="L3" s="4">
         <f>L2/1000*100</f>
-        <v>95.7</v>
+        <v>83.6</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -1135,7 +1135,7 @@
         <v>14</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I5" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1363,11 +1363,11 @@
         <v>51</v>
       </c>
       <c r="G15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I15" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1463,11 +1463,11 @@
         <v>59</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I19" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="O19" s="10" t="s">
         <v>7</v>
@@ -1489,7 +1489,7 @@
         <v>63</v>
       </c>
       <c r="G20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I20" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1510,11 +1510,11 @@
         <v>67</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I21" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
@@ -1552,11 +1552,11 @@
         <v>70</v>
       </c>
       <c r="G23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I23" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
@@ -1636,11 +1636,11 @@
         <v>87</v>
       </c>
       <c r="G27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I27" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
@@ -1678,11 +1678,11 @@
         <v>93</v>
       </c>
       <c r="G29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I29" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
@@ -1867,7 +1867,7 @@
         <v>123</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I38" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1993,11 +1993,11 @@
         <v>144</v>
       </c>
       <c r="G44">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I44" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
@@ -2161,11 +2161,11 @@
         <v>170</v>
       </c>
       <c r="G52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I52" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
@@ -2224,11 +2224,11 @@
         <v>175</v>
       </c>
       <c r="G55">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I55" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
@@ -2329,11 +2329,11 @@
         <v>183</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I60" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
@@ -2476,11 +2476,11 @@
         <v>199</v>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I67" s="6" t="str">
         <f t="shared" ref="I67:I130" si="1">IF(B67=G67, "T", "F")</f>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
@@ -2539,7 +2539,7 @@
         <v>210</v>
       </c>
       <c r="G70">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I70" s="6" t="str">
         <f t="shared" si="1"/>
@@ -2938,11 +2938,11 @@
         <v>251</v>
       </c>
       <c r="G89">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I89" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.3">
@@ -3127,11 +3127,11 @@
         <v>270</v>
       </c>
       <c r="G98">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I98" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
@@ -3169,11 +3169,11 @@
         <v>276</v>
       </c>
       <c r="G100">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I100" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
@@ -3379,11 +3379,11 @@
         <v>299</v>
       </c>
       <c r="G110">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I110" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
@@ -3547,11 +3547,11 @@
         <v>324</v>
       </c>
       <c r="G118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I118" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
@@ -3631,7 +3631,7 @@
         <v>340</v>
       </c>
       <c r="G122">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I122" s="6" t="str">
         <f t="shared" si="1"/>
@@ -3967,11 +3967,11 @@
         <v>387</v>
       </c>
       <c r="G138">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I138" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
@@ -4135,11 +4135,11 @@
         <v>415</v>
       </c>
       <c r="G146">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I146" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.3">
@@ -4219,11 +4219,11 @@
         <v>423</v>
       </c>
       <c r="G150">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I150" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.3">
@@ -4240,11 +4240,11 @@
         <v>424</v>
       </c>
       <c r="G151">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I151" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.3">
@@ -4324,7 +4324,7 @@
         <v>435</v>
       </c>
       <c r="G155">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I155" s="6" t="str">
         <f t="shared" si="2"/>
@@ -4345,11 +4345,11 @@
         <v>436</v>
       </c>
       <c r="G156">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I156" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.3">
@@ -4408,11 +4408,11 @@
         <v>443</v>
       </c>
       <c r="G159">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I159" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
@@ -4429,11 +4429,11 @@
         <v>445</v>
       </c>
       <c r="G160">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I160" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.3">
@@ -4555,11 +4555,11 @@
         <v>461</v>
       </c>
       <c r="G166">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I166" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
@@ -4786,11 +4786,11 @@
         <v>495</v>
       </c>
       <c r="G177">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I177" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.3">
@@ -4828,11 +4828,11 @@
         <v>506</v>
       </c>
       <c r="G179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I179" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
@@ -4849,11 +4849,11 @@
         <v>507</v>
       </c>
       <c r="G180">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I180" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.3">
@@ -4891,11 +4891,11 @@
         <v>509</v>
       </c>
       <c r="G182">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I182" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.3">
@@ -5059,11 +5059,11 @@
         <v>535</v>
       </c>
       <c r="G190">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I190" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.3">
@@ -5227,11 +5227,11 @@
         <v>554</v>
       </c>
       <c r="G198">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I198" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.3">
@@ -5332,11 +5332,11 @@
         <v>565</v>
       </c>
       <c r="G203">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I203" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.3">
@@ -5353,11 +5353,11 @@
         <v>567</v>
       </c>
       <c r="G204">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I204" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.3">
@@ -5542,7 +5542,7 @@
         <v>598</v>
       </c>
       <c r="G213">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I213" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5752,11 +5752,11 @@
         <v>620</v>
       </c>
       <c r="G223">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I223" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.3">
@@ -5773,7 +5773,7 @@
         <v>621</v>
       </c>
       <c r="G224">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I224" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5794,11 +5794,11 @@
         <v>626</v>
       </c>
       <c r="G225">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I225" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.3">
@@ -5899,11 +5899,11 @@
         <v>647</v>
       </c>
       <c r="G230">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I230" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.3">
@@ -5920,7 +5920,7 @@
         <v>650</v>
       </c>
       <c r="G231">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I231" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5962,11 +5962,11 @@
         <v>655</v>
       </c>
       <c r="G233">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I233" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.3">
@@ -6025,11 +6025,11 @@
         <v>670</v>
       </c>
       <c r="G236">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I236" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.3">
@@ -6088,11 +6088,11 @@
         <v>678</v>
       </c>
       <c r="G239">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I239" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.3">
@@ -6193,11 +6193,11 @@
         <v>691</v>
       </c>
       <c r="G244">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I244" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.3">
@@ -6256,11 +6256,11 @@
         <v>700</v>
       </c>
       <c r="G247">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I247" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.3">
@@ -6277,11 +6277,11 @@
         <v>705</v>
       </c>
       <c r="G248">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I248" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.3">
@@ -6508,11 +6508,11 @@
         <v>755</v>
       </c>
       <c r="G259">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I259" s="6" t="str">
         <f t="shared" ref="I259:I322" si="4">IF(B259=G259, "T", "F")</f>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.3">
@@ -7327,7 +7327,7 @@
         <v>859</v>
       </c>
       <c r="G298">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I298" s="6" t="str">
         <f t="shared" si="4"/>
@@ -7915,11 +7915,11 @@
         <v>952</v>
       </c>
       <c r="G326">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I326" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.3">
@@ -7936,11 +7936,11 @@
         <v>962</v>
       </c>
       <c r="G327">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I327" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.3">
@@ -8020,7 +8020,7 @@
         <v>978</v>
       </c>
       <c r="G331">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I331" s="6" t="str">
         <f t="shared" si="5"/>
@@ -8314,11 +8314,11 @@
         <v>1027</v>
       </c>
       <c r="G345">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I345" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.3">
@@ -8419,11 +8419,11 @@
         <v>1037</v>
       </c>
       <c r="G350">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I350" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.3">
@@ -8608,11 +8608,11 @@
         <v>1061</v>
       </c>
       <c r="G359">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I359" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.3">
@@ -8734,11 +8734,11 @@
         <v>1078</v>
       </c>
       <c r="G365">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I365" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.3">
@@ -8839,11 +8839,11 @@
         <v>1091</v>
       </c>
       <c r="G370">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I370" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.3">
@@ -9028,11 +9028,11 @@
         <v>1113</v>
       </c>
       <c r="G379">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I379" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="380" spans="1:9" x14ac:dyDescent="0.3">
@@ -9154,11 +9154,11 @@
         <v>1128</v>
       </c>
       <c r="G385">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I385" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.3">
@@ -9217,11 +9217,11 @@
         <v>1135</v>
       </c>
       <c r="G388">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I388" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="389" spans="1:9" x14ac:dyDescent="0.3">
@@ -9238,11 +9238,11 @@
         <v>1149</v>
       </c>
       <c r="G389">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I389" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="390" spans="1:9" x14ac:dyDescent="0.3">
@@ -9469,11 +9469,11 @@
         <v>1188</v>
       </c>
       <c r="G400">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I400" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.3">
@@ -9490,11 +9490,11 @@
         <v>1195</v>
       </c>
       <c r="G401">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I401" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="402" spans="1:9" x14ac:dyDescent="0.3">
@@ -9511,11 +9511,11 @@
         <v>1196</v>
       </c>
       <c r="G402">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I402" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.3">
@@ -9532,7 +9532,7 @@
         <v>1200</v>
       </c>
       <c r="G403">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I403" s="6" t="str">
         <f t="shared" si="6"/>
@@ -9658,11 +9658,11 @@
         <v>1213</v>
       </c>
       <c r="G409">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I409" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.3">
@@ -9679,11 +9679,11 @@
         <v>1216</v>
       </c>
       <c r="G410">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I410" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.3">
@@ -10120,11 +10120,11 @@
         <v>1270</v>
       </c>
       <c r="G431">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I431" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="432" spans="1:9" x14ac:dyDescent="0.3">
@@ -10204,11 +10204,11 @@
         <v>1286</v>
       </c>
       <c r="G435">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I435" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="436" spans="1:9" x14ac:dyDescent="0.3">
@@ -10372,11 +10372,11 @@
         <v>1309</v>
       </c>
       <c r="G443">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I443" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="444" spans="1:9" x14ac:dyDescent="0.3">
@@ -10435,11 +10435,11 @@
         <v>1320</v>
       </c>
       <c r="G446">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I446" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="447" spans="1:9" x14ac:dyDescent="0.3">
@@ -10855,11 +10855,11 @@
         <v>1398</v>
       </c>
       <c r="G466">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I466" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="467" spans="1:9" x14ac:dyDescent="0.3">
@@ -10897,7 +10897,7 @@
         <v>1407</v>
       </c>
       <c r="G468">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I468" s="6" t="str">
         <f t="shared" si="7"/>
@@ -10939,11 +10939,11 @@
         <v>1413</v>
       </c>
       <c r="G470">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I470" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="471" spans="1:9" x14ac:dyDescent="0.3">
@@ -11002,11 +11002,11 @@
         <v>1422</v>
       </c>
       <c r="G473">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I473" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="474" spans="1:9" x14ac:dyDescent="0.3">
@@ -11023,11 +11023,11 @@
         <v>1426</v>
       </c>
       <c r="G474">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I474" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="475" spans="1:9" x14ac:dyDescent="0.3">
@@ -11296,11 +11296,11 @@
         <v>1472</v>
       </c>
       <c r="G487">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I487" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="488" spans="1:9" x14ac:dyDescent="0.3">
@@ -11317,11 +11317,11 @@
         <v>1474</v>
       </c>
       <c r="G488">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I488" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="489" spans="1:9" x14ac:dyDescent="0.3">
@@ -11401,11 +11401,11 @@
         <v>1483</v>
       </c>
       <c r="G492">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I492" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="493" spans="1:9" x14ac:dyDescent="0.3">
@@ -11590,11 +11590,11 @@
         <v>1510</v>
       </c>
       <c r="G501">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I501" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="502" spans="1:9" x14ac:dyDescent="0.3">
@@ -11632,11 +11632,11 @@
         <v>1512</v>
       </c>
       <c r="G503">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I503" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="504" spans="1:9" x14ac:dyDescent="0.3">
@@ -11779,11 +11779,11 @@
         <v>1538</v>
       </c>
       <c r="G510">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I510" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="511" spans="1:9" x14ac:dyDescent="0.3">
@@ -11863,11 +11863,11 @@
         <v>1554</v>
       </c>
       <c r="G514">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I514" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="515" spans="1:9" x14ac:dyDescent="0.3">
@@ -12409,11 +12409,11 @@
         <v>1655</v>
       </c>
       <c r="G540">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I540" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="541" spans="1:9" x14ac:dyDescent="0.3">
@@ -12451,11 +12451,11 @@
         <v>1659</v>
       </c>
       <c r="G542">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I542" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="543" spans="1:9" x14ac:dyDescent="0.3">
@@ -12745,11 +12745,11 @@
         <v>1710</v>
       </c>
       <c r="G556">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I556" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="557" spans="1:9" x14ac:dyDescent="0.3">
@@ -12829,11 +12829,11 @@
         <v>1718</v>
       </c>
       <c r="G560">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I560" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="561" spans="1:9" x14ac:dyDescent="0.3">
@@ -12892,11 +12892,11 @@
         <v>1725</v>
       </c>
       <c r="G563">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I563" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="564" spans="1:9" x14ac:dyDescent="0.3">
@@ -12934,11 +12934,11 @@
         <v>1730</v>
       </c>
       <c r="G565">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I565" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="566" spans="1:9" x14ac:dyDescent="0.3">
@@ -12955,11 +12955,11 @@
         <v>1731</v>
       </c>
       <c r="G566">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I566" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="567" spans="1:9" x14ac:dyDescent="0.3">
@@ -12976,11 +12976,11 @@
         <v>1735</v>
       </c>
       <c r="G567">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I567" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="568" spans="1:9" x14ac:dyDescent="0.3">
@@ -12997,11 +12997,11 @@
         <v>1736</v>
       </c>
       <c r="G568">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I568" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="569" spans="1:9" x14ac:dyDescent="0.3">
@@ -13039,11 +13039,11 @@
         <v>1741</v>
       </c>
       <c r="G570">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I570" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="571" spans="1:9" x14ac:dyDescent="0.3">
@@ -13417,7 +13417,7 @@
         <v>1809</v>
       </c>
       <c r="G588">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I588" s="6" t="str">
         <f t="shared" si="9"/>
@@ -13543,11 +13543,11 @@
         <v>1829</v>
       </c>
       <c r="G594">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I594" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="595" spans="1:9" x14ac:dyDescent="0.3">
@@ -13942,11 +13942,11 @@
         <v>1883</v>
       </c>
       <c r="G613">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I613" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="614" spans="1:9" x14ac:dyDescent="0.3">
@@ -14005,11 +14005,11 @@
         <v>1896</v>
       </c>
       <c r="G616">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I616" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="617" spans="1:9" x14ac:dyDescent="0.3">
@@ -14068,7 +14068,7 @@
         <v>1911</v>
       </c>
       <c r="G619">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I619" s="6" t="str">
         <f t="shared" si="9"/>
@@ -14089,7 +14089,7 @@
         <v>1912</v>
       </c>
       <c r="G620">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I620" s="6" t="str">
         <f t="shared" si="9"/>
@@ -14152,11 +14152,11 @@
         <v>1924</v>
       </c>
       <c r="G623">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I623" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="624" spans="1:9" x14ac:dyDescent="0.3">
@@ -14215,11 +14215,11 @@
         <v>1933</v>
       </c>
       <c r="G626">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I626" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="627" spans="1:9" x14ac:dyDescent="0.3">
@@ -14320,11 +14320,11 @@
         <v>1941</v>
       </c>
       <c r="G631">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I631" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="632" spans="1:9" x14ac:dyDescent="0.3">
@@ -14341,11 +14341,11 @@
         <v>1950</v>
       </c>
       <c r="G632">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I632" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="633" spans="1:9" x14ac:dyDescent="0.3">
@@ -14509,11 +14509,11 @@
         <v>1966</v>
       </c>
       <c r="G640">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I640" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="641" spans="1:9" x14ac:dyDescent="0.3">
@@ -14614,11 +14614,11 @@
         <v>1980</v>
       </c>
       <c r="G645">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I645" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="646" spans="1:9" x14ac:dyDescent="0.3">
@@ -14740,11 +14740,11 @@
         <v>2005</v>
       </c>
       <c r="G651">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I651" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="652" spans="1:9" x14ac:dyDescent="0.3">
@@ -14824,11 +14824,11 @@
         <v>2014</v>
       </c>
       <c r="G655">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I655" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="656" spans="1:9" x14ac:dyDescent="0.3">
@@ -14845,11 +14845,11 @@
         <v>2015</v>
       </c>
       <c r="G656">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I656" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="657" spans="1:9" x14ac:dyDescent="0.3">
@@ -14887,7 +14887,7 @@
         <v>2025</v>
       </c>
       <c r="G658">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I658" s="6" t="str">
         <f t="shared" si="10"/>
@@ -15181,11 +15181,11 @@
         <v>2073</v>
       </c>
       <c r="G672">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I672" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="673" spans="1:9" x14ac:dyDescent="0.3">
@@ -15349,11 +15349,11 @@
         <v>2119</v>
       </c>
       <c r="G680">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I680" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="681" spans="1:9" x14ac:dyDescent="0.3">
@@ -15454,11 +15454,11 @@
         <v>2138</v>
       </c>
       <c r="G685">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I685" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="686" spans="1:9" x14ac:dyDescent="0.3">
@@ -15496,11 +15496,11 @@
         <v>2153</v>
       </c>
       <c r="G687">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I687" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="688" spans="1:9" x14ac:dyDescent="0.3">
@@ -15580,11 +15580,11 @@
         <v>2162</v>
       </c>
       <c r="G691">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I691" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="692" spans="1:9" x14ac:dyDescent="0.3">
@@ -15601,11 +15601,11 @@
         <v>2163</v>
       </c>
       <c r="G692">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I692" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="693" spans="1:9" x14ac:dyDescent="0.3">
@@ -15622,7 +15622,7 @@
         <v>2164</v>
       </c>
       <c r="G693">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I693" s="6" t="str">
         <f t="shared" si="10"/>
@@ -15916,7 +15916,7 @@
         <v>2212</v>
       </c>
       <c r="G707">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I707" s="6" t="str">
         <f t="shared" ref="I707:I770" si="11">IF(B707=G707, "T", "F")</f>
@@ -16021,11 +16021,11 @@
         <v>2227</v>
       </c>
       <c r="G712">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I712" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="713" spans="1:9" x14ac:dyDescent="0.3">
@@ -16084,11 +16084,11 @@
         <v>2234</v>
       </c>
       <c r="G715">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I715" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="716" spans="1:9" x14ac:dyDescent="0.3">
@@ -16294,11 +16294,11 @@
         <v>2259</v>
       </c>
       <c r="G725">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I725" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="726" spans="1:9" x14ac:dyDescent="0.3">
@@ -16483,11 +16483,11 @@
         <v>2295</v>
       </c>
       <c r="G734">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I734" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="735" spans="1:9" x14ac:dyDescent="0.3">
@@ -16504,11 +16504,11 @@
         <v>2298</v>
       </c>
       <c r="G735">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I735" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="736" spans="1:9" x14ac:dyDescent="0.3">
@@ -16525,11 +16525,11 @@
         <v>2299</v>
       </c>
       <c r="G736">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I736" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="737" spans="1:9" x14ac:dyDescent="0.3">
@@ -16567,11 +16567,11 @@
         <v>2303</v>
       </c>
       <c r="G738">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I738" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="739" spans="1:9" x14ac:dyDescent="0.3">
@@ -16756,11 +16756,11 @@
         <v>2340</v>
       </c>
       <c r="G747">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I747" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="748" spans="1:9" x14ac:dyDescent="0.3">
@@ -16798,11 +16798,11 @@
         <v>2346</v>
       </c>
       <c r="G749">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I749" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="750" spans="1:9" x14ac:dyDescent="0.3">
@@ -16819,11 +16819,11 @@
         <v>2347</v>
       </c>
       <c r="G750">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I750" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="751" spans="1:9" x14ac:dyDescent="0.3">
@@ -16987,11 +16987,11 @@
         <v>2362</v>
       </c>
       <c r="G758">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I758" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="759" spans="1:9" x14ac:dyDescent="0.3">
@@ -17050,11 +17050,11 @@
         <v>2369</v>
       </c>
       <c r="G761">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I761" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="762" spans="1:9" x14ac:dyDescent="0.3">
@@ -17197,11 +17197,11 @@
         <v>2390</v>
       </c>
       <c r="G768">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I768" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="769" spans="1:9" x14ac:dyDescent="0.3">
@@ -17218,11 +17218,11 @@
         <v>2397</v>
       </c>
       <c r="G769">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I769" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="770" spans="1:9" x14ac:dyDescent="0.3">
@@ -17428,11 +17428,11 @@
         <v>2425</v>
       </c>
       <c r="G779">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I779" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="780" spans="1:9" x14ac:dyDescent="0.3">
@@ -17470,11 +17470,11 @@
         <v>2431</v>
       </c>
       <c r="G781">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I781" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="782" spans="1:9" x14ac:dyDescent="0.3">
@@ -17512,11 +17512,11 @@
         <v>2439</v>
       </c>
       <c r="G783">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I783" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="784" spans="1:9" x14ac:dyDescent="0.3">
@@ -17554,11 +17554,11 @@
         <v>2448</v>
       </c>
       <c r="G785">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I785" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="786" spans="1:9" x14ac:dyDescent="0.3">
@@ -17743,11 +17743,11 @@
         <v>2482</v>
       </c>
       <c r="G794">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I794" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="795" spans="1:9" x14ac:dyDescent="0.3">
@@ -17764,11 +17764,11 @@
         <v>2484</v>
       </c>
       <c r="G795">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I795" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="796" spans="1:9" x14ac:dyDescent="0.3">
@@ -18184,11 +18184,11 @@
         <v>2530</v>
       </c>
       <c r="G815">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I815" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="816" spans="1:9" x14ac:dyDescent="0.3">
@@ -18688,7 +18688,7 @@
         <v>2609</v>
       </c>
       <c r="G839">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I839" s="6" t="str">
         <f t="shared" si="13"/>
@@ -18856,11 +18856,11 @@
         <v>2639</v>
       </c>
       <c r="G847">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I847" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="848" spans="1:9" x14ac:dyDescent="0.3">
@@ -18919,11 +18919,11 @@
         <v>2648</v>
       </c>
       <c r="G850">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I850" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="851" spans="1:9" x14ac:dyDescent="0.3">
@@ -18940,11 +18940,11 @@
         <v>2650</v>
       </c>
       <c r="G851">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I851" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="852" spans="1:9" x14ac:dyDescent="0.3">
@@ -19003,11 +19003,11 @@
         <v>2661</v>
       </c>
       <c r="G854">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I854" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="855" spans="1:9" x14ac:dyDescent="0.3">
@@ -19318,7 +19318,7 @@
         <v>2702</v>
       </c>
       <c r="G869">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I869" s="6" t="str">
         <f t="shared" si="13"/>
@@ -19465,11 +19465,11 @@
         <v>2718</v>
       </c>
       <c r="G876">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I876" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="877" spans="1:9" x14ac:dyDescent="0.3">
@@ -19486,11 +19486,11 @@
         <v>2721</v>
       </c>
       <c r="G877">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I877" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="878" spans="1:9" x14ac:dyDescent="0.3">
@@ -19654,11 +19654,11 @@
         <v>2748</v>
       </c>
       <c r="G885">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I885" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="886" spans="1:9" x14ac:dyDescent="0.3">
@@ -20158,7 +20158,7 @@
         <v>2810</v>
       </c>
       <c r="G909">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I909" s="6" t="str">
         <f t="shared" si="14"/>
@@ -20347,11 +20347,11 @@
         <v>2830</v>
       </c>
       <c r="G918">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I918" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="919" spans="1:9" x14ac:dyDescent="0.3">
@@ -20515,7 +20515,7 @@
         <v>2852</v>
       </c>
       <c r="G926">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I926" s="6" t="str">
         <f t="shared" si="14"/>
@@ -20683,11 +20683,11 @@
         <v>2876</v>
       </c>
       <c r="G934">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I934" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="935" spans="1:9" x14ac:dyDescent="0.3">
@@ -20809,11 +20809,11 @@
         <v>2899</v>
       </c>
       <c r="G940">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I940" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="941" spans="1:9" x14ac:dyDescent="0.3">
@@ -20830,11 +20830,11 @@
         <v>2901</v>
       </c>
       <c r="G941">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I941" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="942" spans="1:9" x14ac:dyDescent="0.3">
@@ -20935,11 +20935,11 @@
         <v>2909</v>
       </c>
       <c r="G946">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I946" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="947" spans="1:9" x14ac:dyDescent="0.3">
@@ -21460,11 +21460,11 @@
         <v>2969</v>
       </c>
       <c r="G971">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I971" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="972" spans="1:9" x14ac:dyDescent="0.3">
@@ -21502,11 +21502,11 @@
         <v>2975</v>
       </c>
       <c r="G973">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I973" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="974" spans="1:9" x14ac:dyDescent="0.3">
@@ -21523,11 +21523,11 @@
         <v>2976</v>
       </c>
       <c r="G974">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I974" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="975" spans="1:9" x14ac:dyDescent="0.3">
@@ -21586,11 +21586,11 @@
         <v>2994</v>
       </c>
       <c r="G977">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I977" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="978" spans="1:9" x14ac:dyDescent="0.3">
@@ -21607,11 +21607,11 @@
         <v>2995</v>
       </c>
       <c r="G978">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I978" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="979" spans="1:9" x14ac:dyDescent="0.3">
@@ -21691,11 +21691,11 @@
         <v>3015</v>
       </c>
       <c r="G982">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I982" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="983" spans="1:9" x14ac:dyDescent="0.3">
@@ -21712,11 +21712,11 @@
         <v>3016</v>
       </c>
       <c r="G983">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I983" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="984" spans="1:9" x14ac:dyDescent="0.3">
@@ -21817,11 +21817,11 @@
         <v>3044</v>
       </c>
       <c r="G988">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I988" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="989" spans="1:9" x14ac:dyDescent="0.3">
@@ -21901,11 +21901,11 @@
         <v>3057</v>
       </c>
       <c r="G992">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I992" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="993" spans="1:9" x14ac:dyDescent="0.3">
@@ -22006,7 +22006,7 @@
         <v>3079</v>
       </c>
       <c r="G997">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I997" s="6" t="str">
         <f t="shared" si="15"/>

--- a/compareOP.xlsx
+++ b/compareOP.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DUT\Ki 2\Edge AI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DUT\Ki_2\Edge_AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8EDB4B5-321A-4460-8171-A431E2C19E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25DB256B-75F8-4D37-A945-D5EC04AB5334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{56603411-7B59-498E-88B9-7E9448248F05}"/>
   </bookViews>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="L2" s="4">
         <f>COUNTIF(I2:I1001, "T")</f>
-        <v>836</v>
+        <v>905</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="L3" s="4">
         <f>L2/1000*100</f>
-        <v>83.6</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -1135,7 +1135,7 @@
         <v>14</v>
       </c>
       <c r="G5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1363,11 +1363,11 @@
         <v>51</v>
       </c>
       <c r="G15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I15" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1384,11 +1384,11 @@
         <v>52</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I16" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="N16" s="3">
         <v>5</v>
@@ -1463,11 +1463,11 @@
         <v>59</v>
       </c>
       <c r="G19">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I19" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>T</v>
       </c>
       <c r="O19" s="10" t="s">
         <v>7</v>
@@ -1489,7 +1489,7 @@
         <v>63</v>
       </c>
       <c r="G20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I20" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1510,11 +1510,11 @@
         <v>67</v>
       </c>
       <c r="G21">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I21" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
@@ -1552,7 +1552,7 @@
         <v>70</v>
       </c>
       <c r="G23">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I23" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1636,11 +1636,11 @@
         <v>87</v>
       </c>
       <c r="G27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I27" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
@@ -1678,11 +1678,11 @@
         <v>93</v>
       </c>
       <c r="G29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I29" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
@@ -1867,7 +1867,7 @@
         <v>123</v>
       </c>
       <c r="G38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I38" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1993,7 +1993,7 @@
         <v>144</v>
       </c>
       <c r="G44">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I44" s="6" t="str">
         <f t="shared" si="0"/>
@@ -2161,11 +2161,11 @@
         <v>170</v>
       </c>
       <c r="G52">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I52" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
@@ -2224,11 +2224,11 @@
         <v>175</v>
       </c>
       <c r="G55">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I55" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
@@ -2329,11 +2329,11 @@
         <v>183</v>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I60" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
@@ -2476,11 +2476,11 @@
         <v>199</v>
       </c>
       <c r="G67">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I67" s="6" t="str">
         <f t="shared" ref="I67:I130" si="1">IF(B67=G67, "T", "F")</f>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
@@ -2539,7 +2539,7 @@
         <v>210</v>
       </c>
       <c r="G70">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I70" s="6" t="str">
         <f t="shared" si="1"/>
@@ -2854,11 +2854,11 @@
         <v>240</v>
       </c>
       <c r="G85">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I85" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
@@ -2938,11 +2938,11 @@
         <v>251</v>
       </c>
       <c r="G89">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I89" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.3">
@@ -3127,11 +3127,11 @@
         <v>270</v>
       </c>
       <c r="G98">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I98" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
@@ -3169,11 +3169,11 @@
         <v>276</v>
       </c>
       <c r="G100">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I100" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
@@ -3379,11 +3379,11 @@
         <v>299</v>
       </c>
       <c r="G110">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I110" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
@@ -3631,11 +3631,11 @@
         <v>340</v>
       </c>
       <c r="G122">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I122" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
@@ -3967,11 +3967,11 @@
         <v>387</v>
       </c>
       <c r="G138">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I138" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
@@ -4219,11 +4219,11 @@
         <v>423</v>
       </c>
       <c r="G150">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I150" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.3">
@@ -4240,7 +4240,7 @@
         <v>424</v>
       </c>
       <c r="G151">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I151" s="6" t="str">
         <f t="shared" si="2"/>
@@ -4345,7 +4345,7 @@
         <v>436</v>
       </c>
       <c r="G156">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I156" s="6" t="str">
         <f t="shared" si="2"/>
@@ -4408,7 +4408,7 @@
         <v>443</v>
       </c>
       <c r="G159">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I159" s="6" t="str">
         <f t="shared" si="2"/>
@@ -4429,7 +4429,7 @@
         <v>445</v>
       </c>
       <c r="G160">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I160" s="6" t="str">
         <f t="shared" si="2"/>
@@ -4555,7 +4555,7 @@
         <v>461</v>
       </c>
       <c r="G166">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I166" s="6" t="str">
         <f t="shared" si="2"/>
@@ -4681,11 +4681,11 @@
         <v>478</v>
       </c>
       <c r="G172">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I172" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.3">
@@ -4786,7 +4786,7 @@
         <v>495</v>
       </c>
       <c r="G177">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I177" s="6" t="str">
         <f t="shared" si="2"/>
@@ -4807,11 +4807,11 @@
         <v>498</v>
       </c>
       <c r="G178">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I178" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.3">
@@ -4849,11 +4849,11 @@
         <v>507</v>
       </c>
       <c r="G180">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I180" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.3">
@@ -5059,11 +5059,11 @@
         <v>535</v>
       </c>
       <c r="G190">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I190" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.3">
@@ -5143,11 +5143,11 @@
         <v>544</v>
       </c>
       <c r="G194">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I194" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.3">
@@ -5227,11 +5227,11 @@
         <v>554</v>
       </c>
       <c r="G198">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I198" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.3">
@@ -5248,11 +5248,11 @@
         <v>555</v>
       </c>
       <c r="G199">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I199" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.3">
@@ -5332,11 +5332,11 @@
         <v>565</v>
       </c>
       <c r="G203">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I203" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.3">
@@ -5353,11 +5353,11 @@
         <v>567</v>
       </c>
       <c r="G204">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I204" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.3">
@@ -5752,11 +5752,11 @@
         <v>620</v>
       </c>
       <c r="G223">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I223" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.3">
@@ -5773,11 +5773,11 @@
         <v>621</v>
       </c>
       <c r="G224">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I224" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.3">
@@ -5794,11 +5794,11 @@
         <v>626</v>
       </c>
       <c r="G225">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I225" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.3">
@@ -5962,11 +5962,11 @@
         <v>655</v>
       </c>
       <c r="G233">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I233" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.3">
@@ -6025,11 +6025,11 @@
         <v>670</v>
       </c>
       <c r="G236">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I236" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.3">
@@ -6130,11 +6130,11 @@
         <v>680</v>
       </c>
       <c r="G241">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I241" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.3">
@@ -6172,7 +6172,7 @@
         <v>685</v>
       </c>
       <c r="G243">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I243" s="6" t="str">
         <f t="shared" si="3"/>
@@ -6193,7 +6193,7 @@
         <v>691</v>
       </c>
       <c r="G244">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I244" s="6" t="str">
         <f t="shared" si="3"/>
@@ -6256,7 +6256,7 @@
         <v>700</v>
       </c>
       <c r="G247">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I247" s="6" t="str">
         <f t="shared" si="3"/>
@@ -6277,7 +6277,7 @@
         <v>705</v>
       </c>
       <c r="G248">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I248" s="6" t="str">
         <f t="shared" si="3"/>
@@ -6508,11 +6508,11 @@
         <v>755</v>
       </c>
       <c r="G259">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I259" s="6" t="str">
         <f t="shared" ref="I259:I322" si="4">IF(B259=G259, "T", "F")</f>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.3">
@@ -6739,11 +6739,11 @@
         <v>785</v>
       </c>
       <c r="G270">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I270" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.3">
@@ -7033,11 +7033,11 @@
         <v>812</v>
       </c>
       <c r="G284">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I284" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.3">
@@ -7327,11 +7327,11 @@
         <v>859</v>
       </c>
       <c r="G298">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I298" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.3">
@@ -7915,11 +7915,11 @@
         <v>952</v>
       </c>
       <c r="G326">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I326" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.3">
@@ -7936,11 +7936,11 @@
         <v>962</v>
       </c>
       <c r="G327">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I327" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.3">
@@ -8020,7 +8020,7 @@
         <v>978</v>
       </c>
       <c r="G331">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I331" s="6" t="str">
         <f t="shared" si="5"/>
@@ -8314,11 +8314,11 @@
         <v>1027</v>
       </c>
       <c r="G345">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I345" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.3">
@@ -8419,11 +8419,11 @@
         <v>1037</v>
       </c>
       <c r="G350">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I350" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.3">
@@ -8608,7 +8608,7 @@
         <v>1061</v>
       </c>
       <c r="G359">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I359" s="6" t="str">
         <f t="shared" si="5"/>
@@ -8734,11 +8734,11 @@
         <v>1078</v>
       </c>
       <c r="G365">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I365" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.3">
@@ -8839,11 +8839,11 @@
         <v>1091</v>
       </c>
       <c r="G370">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I370" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.3">
@@ -9154,11 +9154,11 @@
         <v>1128</v>
       </c>
       <c r="G385">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I385" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.3">
@@ -9217,11 +9217,11 @@
         <v>1135</v>
       </c>
       <c r="G388">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I388" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="389" spans="1:9" x14ac:dyDescent="0.3">
@@ -9469,11 +9469,11 @@
         <v>1188</v>
       </c>
       <c r="G400">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I400" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.3">
@@ -9490,11 +9490,11 @@
         <v>1195</v>
       </c>
       <c r="G401">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I401" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="402" spans="1:9" x14ac:dyDescent="0.3">
@@ -9511,7 +9511,7 @@
         <v>1196</v>
       </c>
       <c r="G402">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I402" s="6" t="str">
         <f t="shared" si="6"/>
@@ -9532,7 +9532,7 @@
         <v>1200</v>
       </c>
       <c r="G403">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I403" s="6" t="str">
         <f t="shared" si="6"/>
@@ -9658,11 +9658,11 @@
         <v>1213</v>
       </c>
       <c r="G409">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I409" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.3">
@@ -9679,11 +9679,11 @@
         <v>1216</v>
       </c>
       <c r="G410">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I410" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.3">
@@ -9847,11 +9847,11 @@
         <v>1235</v>
       </c>
       <c r="G418">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I418" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.3">
@@ -10120,11 +10120,11 @@
         <v>1270</v>
       </c>
       <c r="G431">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I431" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="432" spans="1:9" x14ac:dyDescent="0.3">
@@ -10204,11 +10204,11 @@
         <v>1286</v>
       </c>
       <c r="G435">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I435" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="436" spans="1:9" x14ac:dyDescent="0.3">
@@ -10372,11 +10372,11 @@
         <v>1309</v>
       </c>
       <c r="G443">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I443" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="444" spans="1:9" x14ac:dyDescent="0.3">
@@ -10435,7 +10435,7 @@
         <v>1320</v>
       </c>
       <c r="G446">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I446" s="6" t="str">
         <f t="shared" si="6"/>
@@ -10624,11 +10624,11 @@
         <v>1361</v>
       </c>
       <c r="G455">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I455" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="456" spans="1:9" x14ac:dyDescent="0.3">
@@ -10834,11 +10834,11 @@
         <v>1395</v>
       </c>
       <c r="G465">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I465" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="466" spans="1:9" x14ac:dyDescent="0.3">
@@ -10855,11 +10855,11 @@
         <v>1398</v>
       </c>
       <c r="G466">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I466" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="467" spans="1:9" x14ac:dyDescent="0.3">
@@ -10939,11 +10939,11 @@
         <v>1413</v>
       </c>
       <c r="G470">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I470" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="471" spans="1:9" x14ac:dyDescent="0.3">
@@ -11002,11 +11002,11 @@
         <v>1422</v>
       </c>
       <c r="G473">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I473" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="474" spans="1:9" x14ac:dyDescent="0.3">
@@ -11023,7 +11023,7 @@
         <v>1426</v>
       </c>
       <c r="G474">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I474" s="6" t="str">
         <f t="shared" si="7"/>
@@ -11212,11 +11212,11 @@
         <v>1461</v>
       </c>
       <c r="G483">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I483" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="484" spans="1:9" x14ac:dyDescent="0.3">
@@ -11296,7 +11296,7 @@
         <v>1472</v>
       </c>
       <c r="G487">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I487" s="6" t="str">
         <f t="shared" si="7"/>
@@ -11317,11 +11317,11 @@
         <v>1474</v>
       </c>
       <c r="G488">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I488" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="489" spans="1:9" x14ac:dyDescent="0.3">
@@ -11590,11 +11590,11 @@
         <v>1510</v>
       </c>
       <c r="G501">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I501" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="502" spans="1:9" x14ac:dyDescent="0.3">
@@ -11632,11 +11632,11 @@
         <v>1512</v>
       </c>
       <c r="G503">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I503" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="504" spans="1:9" x14ac:dyDescent="0.3">
@@ -11758,11 +11758,11 @@
         <v>1537</v>
       </c>
       <c r="G509">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I509" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="510" spans="1:9" x14ac:dyDescent="0.3">
@@ -11779,11 +11779,11 @@
         <v>1538</v>
       </c>
       <c r="G510">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I510" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="511" spans="1:9" x14ac:dyDescent="0.3">
@@ -11863,11 +11863,11 @@
         <v>1554</v>
       </c>
       <c r="G514">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I514" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="515" spans="1:9" x14ac:dyDescent="0.3">
@@ -11947,11 +11947,11 @@
         <v>1566</v>
       </c>
       <c r="G518">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I518" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="519" spans="1:9" x14ac:dyDescent="0.3">
@@ -12115,11 +12115,11 @@
         <v>1601</v>
       </c>
       <c r="G526">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I526" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="527" spans="1:9" x14ac:dyDescent="0.3">
@@ -12409,11 +12409,11 @@
         <v>1655</v>
       </c>
       <c r="G540">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I540" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="541" spans="1:9" x14ac:dyDescent="0.3">
@@ -12451,11 +12451,11 @@
         <v>1659</v>
       </c>
       <c r="G542">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I542" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="543" spans="1:9" x14ac:dyDescent="0.3">
@@ -12745,11 +12745,11 @@
         <v>1710</v>
       </c>
       <c r="G556">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I556" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="557" spans="1:9" x14ac:dyDescent="0.3">
@@ -12829,7 +12829,7 @@
         <v>1718</v>
       </c>
       <c r="G560">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I560" s="6" t="str">
         <f t="shared" si="8"/>
@@ -12892,11 +12892,11 @@
         <v>1725</v>
       </c>
       <c r="G563">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I563" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="564" spans="1:9" x14ac:dyDescent="0.3">
@@ -12934,11 +12934,11 @@
         <v>1730</v>
       </c>
       <c r="G565">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I565" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="566" spans="1:9" x14ac:dyDescent="0.3">
@@ -12955,11 +12955,11 @@
         <v>1731</v>
       </c>
       <c r="G566">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I566" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="567" spans="1:9" x14ac:dyDescent="0.3">
@@ -12976,11 +12976,11 @@
         <v>1735</v>
       </c>
       <c r="G567">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I567" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="568" spans="1:9" x14ac:dyDescent="0.3">
@@ -12997,11 +12997,11 @@
         <v>1736</v>
       </c>
       <c r="G568">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I568" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="569" spans="1:9" x14ac:dyDescent="0.3">
@@ -13039,7 +13039,7 @@
         <v>1741</v>
       </c>
       <c r="G570">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I570" s="6" t="str">
         <f t="shared" si="8"/>
@@ -13417,7 +13417,7 @@
         <v>1809</v>
       </c>
       <c r="G588">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I588" s="6" t="str">
         <f t="shared" si="9"/>
@@ -13459,11 +13459,11 @@
         <v>1814</v>
       </c>
       <c r="G590">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I590" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="591" spans="1:9" x14ac:dyDescent="0.3">
@@ -14068,11 +14068,11 @@
         <v>1911</v>
       </c>
       <c r="G619">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I619" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="620" spans="1:9" x14ac:dyDescent="0.3">
@@ -14089,7 +14089,7 @@
         <v>1912</v>
       </c>
       <c r="G620">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I620" s="6" t="str">
         <f t="shared" si="9"/>
@@ -14152,11 +14152,11 @@
         <v>1924</v>
       </c>
       <c r="G623">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I623" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="624" spans="1:9" x14ac:dyDescent="0.3">
@@ -14215,11 +14215,11 @@
         <v>1933</v>
       </c>
       <c r="G626">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I626" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="627" spans="1:9" x14ac:dyDescent="0.3">
@@ -14320,11 +14320,11 @@
         <v>1941</v>
       </c>
       <c r="G631">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I631" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="632" spans="1:9" x14ac:dyDescent="0.3">
@@ -14341,11 +14341,11 @@
         <v>1950</v>
       </c>
       <c r="G632">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I632" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="633" spans="1:9" x14ac:dyDescent="0.3">
@@ -14509,11 +14509,11 @@
         <v>1966</v>
       </c>
       <c r="G640">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I640" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="641" spans="1:9" x14ac:dyDescent="0.3">
@@ -14614,7 +14614,7 @@
         <v>1980</v>
       </c>
       <c r="G645">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I645" s="6" t="str">
         <f t="shared" si="10"/>
@@ -14740,11 +14740,11 @@
         <v>2005</v>
       </c>
       <c r="G651">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I651" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="652" spans="1:9" x14ac:dyDescent="0.3">
@@ -14824,11 +14824,11 @@
         <v>2014</v>
       </c>
       <c r="G655">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I655" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="656" spans="1:9" x14ac:dyDescent="0.3">
@@ -14845,11 +14845,11 @@
         <v>2015</v>
       </c>
       <c r="G656">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I656" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="657" spans="1:9" x14ac:dyDescent="0.3">
@@ -14908,11 +14908,11 @@
         <v>2028</v>
       </c>
       <c r="G659">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I659" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="660" spans="1:9" x14ac:dyDescent="0.3">
@@ -15181,11 +15181,11 @@
         <v>2073</v>
       </c>
       <c r="G672">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I672" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="673" spans="1:9" x14ac:dyDescent="0.3">
@@ -15244,11 +15244,11 @@
         <v>2086</v>
       </c>
       <c r="G675">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I675" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="676" spans="1:9" x14ac:dyDescent="0.3">
@@ -15349,7 +15349,7 @@
         <v>2119</v>
       </c>
       <c r="G680">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I680" s="6" t="str">
         <f t="shared" si="10"/>
@@ -15370,11 +15370,11 @@
         <v>2123</v>
       </c>
       <c r="G681">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I681" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="682" spans="1:9" x14ac:dyDescent="0.3">
@@ -15454,11 +15454,11 @@
         <v>2138</v>
       </c>
       <c r="G685">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I685" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="686" spans="1:9" x14ac:dyDescent="0.3">
@@ -15580,11 +15580,11 @@
         <v>2162</v>
       </c>
       <c r="G691">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I691" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="692" spans="1:9" x14ac:dyDescent="0.3">
@@ -15601,11 +15601,11 @@
         <v>2163</v>
       </c>
       <c r="G692">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I692" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="693" spans="1:9" x14ac:dyDescent="0.3">
@@ -15916,7 +15916,7 @@
         <v>2212</v>
       </c>
       <c r="G707">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I707" s="6" t="str">
         <f t="shared" ref="I707:I770" si="11">IF(B707=G707, "T", "F")</f>
@@ -16021,11 +16021,11 @@
         <v>2227</v>
       </c>
       <c r="G712">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I712" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="713" spans="1:9" x14ac:dyDescent="0.3">
@@ -16084,11 +16084,11 @@
         <v>2234</v>
       </c>
       <c r="G715">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I715" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="716" spans="1:9" x14ac:dyDescent="0.3">
@@ -16294,11 +16294,11 @@
         <v>2259</v>
       </c>
       <c r="G725">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I725" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="726" spans="1:9" x14ac:dyDescent="0.3">
@@ -16378,11 +16378,11 @@
         <v>2266</v>
       </c>
       <c r="G729">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I729" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="730" spans="1:9" x14ac:dyDescent="0.3">
@@ -16504,7 +16504,7 @@
         <v>2298</v>
       </c>
       <c r="G735">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I735" s="6" t="str">
         <f t="shared" si="11"/>
@@ -16525,11 +16525,11 @@
         <v>2299</v>
       </c>
       <c r="G736">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I736" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="737" spans="1:9" x14ac:dyDescent="0.3">
@@ -16567,11 +16567,11 @@
         <v>2303</v>
       </c>
       <c r="G738">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I738" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="739" spans="1:9" x14ac:dyDescent="0.3">
@@ -16651,11 +16651,11 @@
         <v>2312</v>
       </c>
       <c r="G742">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I742" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="743" spans="1:9" x14ac:dyDescent="0.3">
@@ -16756,11 +16756,11 @@
         <v>2340</v>
       </c>
       <c r="G747">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I747" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="748" spans="1:9" x14ac:dyDescent="0.3">
@@ -16798,11 +16798,11 @@
         <v>2346</v>
       </c>
       <c r="G749">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I749" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="750" spans="1:9" x14ac:dyDescent="0.3">
@@ -16819,11 +16819,11 @@
         <v>2347</v>
       </c>
       <c r="G750">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I750" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="751" spans="1:9" x14ac:dyDescent="0.3">
@@ -16987,11 +16987,11 @@
         <v>2362</v>
       </c>
       <c r="G758">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I758" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="759" spans="1:9" x14ac:dyDescent="0.3">
@@ -17008,11 +17008,11 @@
         <v>2364</v>
       </c>
       <c r="G759">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I759" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="760" spans="1:9" x14ac:dyDescent="0.3">
@@ -17050,7 +17050,7 @@
         <v>2369</v>
       </c>
       <c r="G761">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I761" s="6" t="str">
         <f t="shared" si="11"/>
@@ -17197,7 +17197,7 @@
         <v>2390</v>
       </c>
       <c r="G768">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I768" s="6" t="str">
         <f t="shared" si="11"/>
@@ -17218,11 +17218,11 @@
         <v>2397</v>
       </c>
       <c r="G769">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I769" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="770" spans="1:9" x14ac:dyDescent="0.3">
@@ -17428,11 +17428,11 @@
         <v>2425</v>
       </c>
       <c r="G779">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I779" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="780" spans="1:9" x14ac:dyDescent="0.3">
@@ -17470,11 +17470,11 @@
         <v>2431</v>
       </c>
       <c r="G781">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I781" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="782" spans="1:9" x14ac:dyDescent="0.3">
@@ -17512,7 +17512,7 @@
         <v>2439</v>
       </c>
       <c r="G783">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I783" s="6" t="str">
         <f t="shared" si="12"/>
@@ -17554,7 +17554,7 @@
         <v>2448</v>
       </c>
       <c r="G785">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I785" s="6" t="str">
         <f t="shared" si="12"/>
@@ -17743,7 +17743,7 @@
         <v>2482</v>
       </c>
       <c r="G794">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I794" s="6" t="str">
         <f t="shared" si="12"/>
@@ -17764,11 +17764,11 @@
         <v>2484</v>
       </c>
       <c r="G795">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I795" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="796" spans="1:9" x14ac:dyDescent="0.3">
@@ -18184,11 +18184,11 @@
         <v>2530</v>
       </c>
       <c r="G815">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I815" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="816" spans="1:9" x14ac:dyDescent="0.3">
@@ -18688,7 +18688,7 @@
         <v>2609</v>
       </c>
       <c r="G839">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I839" s="6" t="str">
         <f t="shared" si="13"/>
@@ -18856,11 +18856,11 @@
         <v>2639</v>
       </c>
       <c r="G847">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I847" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="848" spans="1:9" x14ac:dyDescent="0.3">
@@ -18919,11 +18919,11 @@
         <v>2648</v>
       </c>
       <c r="G850">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I850" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="851" spans="1:9" x14ac:dyDescent="0.3">
@@ -18940,11 +18940,11 @@
         <v>2650</v>
       </c>
       <c r="G851">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I851" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="852" spans="1:9" x14ac:dyDescent="0.3">
@@ -19003,11 +19003,11 @@
         <v>2661</v>
       </c>
       <c r="G854">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I854" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="855" spans="1:9" x14ac:dyDescent="0.3">
@@ -19465,11 +19465,11 @@
         <v>2718</v>
       </c>
       <c r="G876">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I876" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="877" spans="1:9" x14ac:dyDescent="0.3">
@@ -19486,11 +19486,11 @@
         <v>2721</v>
       </c>
       <c r="G877">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I877" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="878" spans="1:9" x14ac:dyDescent="0.3">
@@ -19528,11 +19528,11 @@
         <v>2725</v>
       </c>
       <c r="G879">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I879" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="880" spans="1:9" x14ac:dyDescent="0.3">
@@ -19654,11 +19654,11 @@
         <v>2748</v>
       </c>
       <c r="G885">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I885" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="886" spans="1:9" x14ac:dyDescent="0.3">
@@ -20158,11 +20158,11 @@
         <v>2810</v>
       </c>
       <c r="G909">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I909" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="910" spans="1:9" x14ac:dyDescent="0.3">
@@ -20347,7 +20347,7 @@
         <v>2830</v>
       </c>
       <c r="G918">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I918" s="6" t="str">
         <f t="shared" si="14"/>
@@ -20410,11 +20410,11 @@
         <v>2839</v>
       </c>
       <c r="G921">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I921" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="922" spans="1:9" x14ac:dyDescent="0.3">
@@ -20536,11 +20536,11 @@
         <v>2855</v>
       </c>
       <c r="G927">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I927" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="928" spans="1:9" x14ac:dyDescent="0.3">
@@ -20683,11 +20683,11 @@
         <v>2876</v>
       </c>
       <c r="G934">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I934" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="935" spans="1:9" x14ac:dyDescent="0.3">
@@ -20809,11 +20809,11 @@
         <v>2899</v>
       </c>
       <c r="G940">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I940" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="941" spans="1:9" x14ac:dyDescent="0.3">
@@ -20830,11 +20830,11 @@
         <v>2901</v>
       </c>
       <c r="G941">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I941" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="942" spans="1:9" x14ac:dyDescent="0.3">
@@ -20935,11 +20935,11 @@
         <v>2909</v>
       </c>
       <c r="G946">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I946" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="947" spans="1:9" x14ac:dyDescent="0.3">
@@ -21460,11 +21460,11 @@
         <v>2969</v>
       </c>
       <c r="G971">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I971" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="972" spans="1:9" x14ac:dyDescent="0.3">
@@ -21523,7 +21523,7 @@
         <v>2976</v>
       </c>
       <c r="G974">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I974" s="6" t="str">
         <f t="shared" si="15"/>
@@ -21586,7 +21586,7 @@
         <v>2994</v>
       </c>
       <c r="G977">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I977" s="6" t="str">
         <f t="shared" si="15"/>
@@ -21607,11 +21607,11 @@
         <v>2995</v>
       </c>
       <c r="G978">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I978" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="979" spans="1:9" x14ac:dyDescent="0.3">
@@ -21691,11 +21691,11 @@
         <v>3015</v>
       </c>
       <c r="G982">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I982" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="983" spans="1:9" x14ac:dyDescent="0.3">
@@ -21712,11 +21712,11 @@
         <v>3016</v>
       </c>
       <c r="G983">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I983" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="984" spans="1:9" x14ac:dyDescent="0.3">
@@ -21817,7 +21817,7 @@
         <v>3044</v>
       </c>
       <c r="G988">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I988" s="6" t="str">
         <f t="shared" si="15"/>
@@ -21901,7 +21901,7 @@
         <v>3057</v>
       </c>
       <c r="G992">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I992" s="6" t="str">
         <f t="shared" si="15"/>
@@ -21964,11 +21964,11 @@
         <v>3075</v>
       </c>
       <c r="G995">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I995" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="996" spans="1:9" x14ac:dyDescent="0.3">
@@ -22006,7 +22006,7 @@
         <v>3079</v>
       </c>
       <c r="G997">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I997" s="6" t="str">
         <f t="shared" si="15"/>

--- a/compareOP.xlsx
+++ b/compareOP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DUT\Ki_2\Edge_AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25DB256B-75F8-4D37-A945-D5EC04AB5334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D4AFA7F-7CFC-4B7D-8D34-1B0A47A28CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{56603411-7B59-498E-88B9-7E9448248F05}"/>
   </bookViews>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="L2" s="4">
         <f>COUNTIF(I2:I1001, "T")</f>
-        <v>905</v>
+        <v>942</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="L3" s="4">
         <f>L2/1000*100</f>
-        <v>90.5</v>
+        <v>94.199999999999989</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -1135,7 +1135,7 @@
         <v>14</v>
       </c>
       <c r="G5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I5" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1384,11 +1384,11 @@
         <v>52</v>
       </c>
       <c r="G16">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I16" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>T</v>
       </c>
       <c r="N16" s="3">
         <v>5</v>
@@ -1489,7 +1489,7 @@
         <v>63</v>
       </c>
       <c r="G20">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I20" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1552,7 +1552,7 @@
         <v>70</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I23" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1993,11 +1993,11 @@
         <v>144</v>
       </c>
       <c r="G44">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I44" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
@@ -2539,11 +2539,11 @@
         <v>210</v>
       </c>
       <c r="G70">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I70" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
@@ -2854,11 +2854,11 @@
         <v>240</v>
       </c>
       <c r="G85">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I85" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
@@ -3211,11 +3211,11 @@
         <v>279</v>
       </c>
       <c r="G102">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I102" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
@@ -3232,11 +3232,11 @@
         <v>282</v>
       </c>
       <c r="G103">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I103" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
@@ -3379,11 +3379,11 @@
         <v>299</v>
       </c>
       <c r="G110">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I110" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
@@ -3547,11 +3547,11 @@
         <v>324</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I118" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
@@ -3631,11 +3631,11 @@
         <v>340</v>
       </c>
       <c r="G122">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I122" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
@@ -4135,7 +4135,7 @@
         <v>415</v>
       </c>
       <c r="G146">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I146" s="6" t="str">
         <f t="shared" si="2"/>
@@ -4240,7 +4240,7 @@
         <v>424</v>
       </c>
       <c r="G151">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I151" s="6" t="str">
         <f t="shared" si="2"/>
@@ -4345,11 +4345,11 @@
         <v>436</v>
       </c>
       <c r="G156">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I156" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.3">
@@ -4408,11 +4408,11 @@
         <v>443</v>
       </c>
       <c r="G159">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I159" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
@@ -4429,11 +4429,11 @@
         <v>445</v>
       </c>
       <c r="G160">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I160" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.3">
@@ -4555,11 +4555,11 @@
         <v>461</v>
       </c>
       <c r="G166">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I166" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
@@ -4681,11 +4681,11 @@
         <v>478</v>
       </c>
       <c r="G172">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I172" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.3">
@@ -4786,7 +4786,7 @@
         <v>495</v>
       </c>
       <c r="G177">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I177" s="6" t="str">
         <f t="shared" si="2"/>
@@ -4807,11 +4807,11 @@
         <v>498</v>
       </c>
       <c r="G178">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I178" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.3">
@@ -4828,11 +4828,11 @@
         <v>506</v>
       </c>
       <c r="G179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I179" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
@@ -4891,11 +4891,11 @@
         <v>509</v>
       </c>
       <c r="G182">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I182" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.3">
@@ -5248,11 +5248,11 @@
         <v>555</v>
       </c>
       <c r="G199">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I199" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.3">
@@ -5773,11 +5773,11 @@
         <v>621</v>
       </c>
       <c r="G224">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I224" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.3">
@@ -5899,11 +5899,11 @@
         <v>647</v>
       </c>
       <c r="G230">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I230" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.3">
@@ -5920,7 +5920,7 @@
         <v>650</v>
       </c>
       <c r="G231">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I231" s="6" t="str">
         <f t="shared" si="3"/>
@@ -6088,11 +6088,11 @@
         <v>678</v>
       </c>
       <c r="G239">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I239" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.3">
@@ -6130,11 +6130,11 @@
         <v>680</v>
       </c>
       <c r="G241">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I241" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.3">
@@ -6256,11 +6256,11 @@
         <v>700</v>
       </c>
       <c r="G247">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I247" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.3">
@@ -6277,11 +6277,11 @@
         <v>705</v>
       </c>
       <c r="G248">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I248" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.3">
@@ -6382,11 +6382,11 @@
         <v>736</v>
       </c>
       <c r="G253">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I253" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.3">
@@ -6739,11 +6739,11 @@
         <v>785</v>
       </c>
       <c r="G270">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I270" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.3">
@@ -7033,11 +7033,11 @@
         <v>812</v>
       </c>
       <c r="G284">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I284" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.3">
@@ -7852,11 +7852,11 @@
         <v>944</v>
       </c>
       <c r="G323">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I323" s="6" t="str">
         <f t="shared" ref="I323:I386" si="5">IF(B323=G323, "T", "F")</f>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.3">
@@ -8020,7 +8020,7 @@
         <v>978</v>
       </c>
       <c r="G331">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I331" s="6" t="str">
         <f t="shared" si="5"/>
@@ -8419,11 +8419,11 @@
         <v>1037</v>
       </c>
       <c r="G350">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I350" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.3">
@@ -8608,11 +8608,11 @@
         <v>1061</v>
       </c>
       <c r="G359">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I359" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.3">
@@ -9028,11 +9028,11 @@
         <v>1113</v>
       </c>
       <c r="G379">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I379" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="380" spans="1:9" x14ac:dyDescent="0.3">
@@ -9301,11 +9301,11 @@
         <v>1159</v>
       </c>
       <c r="G392">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I392" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.3">
@@ -9490,7 +9490,7 @@
         <v>1195</v>
       </c>
       <c r="G401">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I401" s="6" t="str">
         <f t="shared" si="6"/>
@@ -9511,11 +9511,11 @@
         <v>1196</v>
       </c>
       <c r="G402">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I402" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.3">
@@ -9847,11 +9847,11 @@
         <v>1235</v>
       </c>
       <c r="G418">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I418" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.3">
@@ -10309,11 +10309,11 @@
         <v>1299</v>
       </c>
       <c r="G440">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I440" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="441" spans="1:9" x14ac:dyDescent="0.3">
@@ -10435,11 +10435,11 @@
         <v>1320</v>
       </c>
       <c r="G446">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I446" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="447" spans="1:9" x14ac:dyDescent="0.3">
@@ -10624,7 +10624,7 @@
         <v>1361</v>
       </c>
       <c r="G455">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I455" s="6" t="str">
         <f t="shared" si="7"/>
@@ -10834,11 +10834,11 @@
         <v>1395</v>
       </c>
       <c r="G465">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I465" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="466" spans="1:9" x14ac:dyDescent="0.3">
@@ -10897,11 +10897,11 @@
         <v>1407</v>
       </c>
       <c r="G468">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I468" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="469" spans="1:9" x14ac:dyDescent="0.3">
@@ -11212,11 +11212,11 @@
         <v>1461</v>
       </c>
       <c r="G483">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I483" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="484" spans="1:9" x14ac:dyDescent="0.3">
@@ -11317,7 +11317,7 @@
         <v>1474</v>
       </c>
       <c r="G488">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I488" s="6" t="str">
         <f t="shared" si="7"/>
@@ -11401,11 +11401,11 @@
         <v>1483</v>
       </c>
       <c r="G492">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I492" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="493" spans="1:9" x14ac:dyDescent="0.3">
@@ -11632,7 +11632,7 @@
         <v>1512</v>
       </c>
       <c r="G503">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I503" s="6" t="str">
         <f t="shared" si="7"/>
@@ -11758,11 +11758,11 @@
         <v>1537</v>
       </c>
       <c r="G509">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I509" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="510" spans="1:9" x14ac:dyDescent="0.3">
@@ -11947,7 +11947,7 @@
         <v>1566</v>
       </c>
       <c r="G518">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I518" s="6" t="str">
         <f t="shared" si="8"/>
@@ -12115,11 +12115,11 @@
         <v>1601</v>
       </c>
       <c r="G526">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I526" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="527" spans="1:9" x14ac:dyDescent="0.3">
@@ -12745,11 +12745,11 @@
         <v>1710</v>
       </c>
       <c r="G556">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I556" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="557" spans="1:9" x14ac:dyDescent="0.3">
@@ -12787,11 +12787,11 @@
         <v>1713</v>
       </c>
       <c r="G558">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I558" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="559" spans="1:9" x14ac:dyDescent="0.3">
@@ -12829,11 +12829,11 @@
         <v>1718</v>
       </c>
       <c r="G560">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I560" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="561" spans="1:9" x14ac:dyDescent="0.3">
@@ -13039,7 +13039,7 @@
         <v>1741</v>
       </c>
       <c r="G570">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I570" s="6" t="str">
         <f t="shared" si="8"/>
@@ -13417,11 +13417,11 @@
         <v>1809</v>
       </c>
       <c r="G588">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I588" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="589" spans="1:9" x14ac:dyDescent="0.3">
@@ -13459,11 +13459,11 @@
         <v>1814</v>
       </c>
       <c r="G590">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I590" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="591" spans="1:9" x14ac:dyDescent="0.3">
@@ -13543,11 +13543,11 @@
         <v>1829</v>
       </c>
       <c r="G594">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I594" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="595" spans="1:9" x14ac:dyDescent="0.3">
@@ -13942,11 +13942,11 @@
         <v>1883</v>
       </c>
       <c r="G613">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I613" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="614" spans="1:9" x14ac:dyDescent="0.3">
@@ -14005,11 +14005,11 @@
         <v>1896</v>
       </c>
       <c r="G616">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I616" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="617" spans="1:9" x14ac:dyDescent="0.3">
@@ -14068,11 +14068,11 @@
         <v>1911</v>
       </c>
       <c r="G619">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I619" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="620" spans="1:9" x14ac:dyDescent="0.3">
@@ -14089,11 +14089,11 @@
         <v>1912</v>
       </c>
       <c r="G620">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I620" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="621" spans="1:9" x14ac:dyDescent="0.3">
@@ -14614,11 +14614,11 @@
         <v>1980</v>
       </c>
       <c r="G645">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I645" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="646" spans="1:9" x14ac:dyDescent="0.3">
@@ -15076,11 +15076,11 @@
         <v>2051</v>
       </c>
       <c r="G667">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I667" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="668" spans="1:9" x14ac:dyDescent="0.3">
@@ -15244,11 +15244,11 @@
         <v>2086</v>
       </c>
       <c r="G675">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I675" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="676" spans="1:9" x14ac:dyDescent="0.3">
@@ -15349,11 +15349,11 @@
         <v>2119</v>
       </c>
       <c r="G680">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I680" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="681" spans="1:9" x14ac:dyDescent="0.3">
@@ -15370,11 +15370,11 @@
         <v>2123</v>
       </c>
       <c r="G681">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I681" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="682" spans="1:9" x14ac:dyDescent="0.3">
@@ -15874,11 +15874,11 @@
         <v>2208</v>
       </c>
       <c r="G705">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I705" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="706" spans="1:9" x14ac:dyDescent="0.3">
@@ -15916,7 +15916,7 @@
         <v>2212</v>
       </c>
       <c r="G707">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I707" s="6" t="str">
         <f t="shared" ref="I707:I770" si="11">IF(B707=G707, "T", "F")</f>
@@ -16378,11 +16378,11 @@
         <v>2266</v>
       </c>
       <c r="G729">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I729" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="730" spans="1:9" x14ac:dyDescent="0.3">
@@ -16651,11 +16651,11 @@
         <v>2312</v>
       </c>
       <c r="G742">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I742" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="743" spans="1:9" x14ac:dyDescent="0.3">
@@ -16882,11 +16882,11 @@
         <v>2354</v>
       </c>
       <c r="G753">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I753" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="754" spans="1:9" x14ac:dyDescent="0.3">
@@ -17008,11 +17008,11 @@
         <v>2364</v>
       </c>
       <c r="G759">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I759" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="760" spans="1:9" x14ac:dyDescent="0.3">
@@ -17050,11 +17050,11 @@
         <v>2369</v>
       </c>
       <c r="G761">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I761" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="762" spans="1:9" x14ac:dyDescent="0.3">
@@ -17197,11 +17197,11 @@
         <v>2390</v>
       </c>
       <c r="G768">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I768" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="769" spans="1:9" x14ac:dyDescent="0.3">
@@ -17512,11 +17512,11 @@
         <v>2439</v>
       </c>
       <c r="G783">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I783" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="784" spans="1:9" x14ac:dyDescent="0.3">
@@ -17743,11 +17743,11 @@
         <v>2482</v>
       </c>
       <c r="G794">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I794" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="795" spans="1:9" x14ac:dyDescent="0.3">
@@ -18688,11 +18688,11 @@
         <v>2609</v>
       </c>
       <c r="G839">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I839" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="840" spans="1:9" x14ac:dyDescent="0.3">
@@ -18940,11 +18940,11 @@
         <v>2650</v>
       </c>
       <c r="G851">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I851" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="852" spans="1:9" x14ac:dyDescent="0.3">
@@ -19528,11 +19528,11 @@
         <v>2725</v>
       </c>
       <c r="G879">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I879" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="880" spans="1:9" x14ac:dyDescent="0.3">
@@ -20347,7 +20347,7 @@
         <v>2830</v>
       </c>
       <c r="G918">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I918" s="6" t="str">
         <f t="shared" si="14"/>
@@ -20410,11 +20410,11 @@
         <v>2839</v>
       </c>
       <c r="G921">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I921" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="922" spans="1:9" x14ac:dyDescent="0.3">
@@ -20536,11 +20536,11 @@
         <v>2855</v>
       </c>
       <c r="G927">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I927" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="928" spans="1:9" x14ac:dyDescent="0.3">
@@ -21502,11 +21502,11 @@
         <v>2975</v>
       </c>
       <c r="G973">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I973" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="974" spans="1:9" x14ac:dyDescent="0.3">
@@ -21523,11 +21523,11 @@
         <v>2976</v>
       </c>
       <c r="G974">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I974" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="975" spans="1:9" x14ac:dyDescent="0.3">
@@ -21586,7 +21586,7 @@
         <v>2994</v>
       </c>
       <c r="G977">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I977" s="6" t="str">
         <f t="shared" si="15"/>
@@ -21628,11 +21628,11 @@
         <v>3008</v>
       </c>
       <c r="G979">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I979" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="980" spans="1:9" x14ac:dyDescent="0.3">
@@ -21817,11 +21817,11 @@
         <v>3044</v>
       </c>
       <c r="G988">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I988" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="989" spans="1:9" x14ac:dyDescent="0.3">
@@ -21901,11 +21901,11 @@
         <v>3057</v>
       </c>
       <c r="G992">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I992" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="993" spans="1:9" x14ac:dyDescent="0.3">
@@ -21964,11 +21964,11 @@
         <v>3075</v>
       </c>
       <c r="G995">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I995" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="996" spans="1:9" x14ac:dyDescent="0.3">
@@ -22006,7 +22006,7 @@
         <v>3079</v>
       </c>
       <c r="G997">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I997" s="6" t="str">
         <f t="shared" si="15"/>

--- a/compareOP.xlsx
+++ b/compareOP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DUT\Ki_2\Edge_AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58363DCC-4293-43AB-9161-D6F1708343D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E80FC8-4267-4355-B75D-E933E567E4CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{56603411-7B59-498E-88B9-7E9448248F05}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="6">
   <si>
     <t>Id</t>
   </si>
@@ -37,6 +37,12 @@
   </si>
   <si>
     <t>Pct</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>X</t>
   </si>
 </sst>
 </file>
@@ -122,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -145,13 +151,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -957,6 +966,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="6"/>
+    <col min="4" max="4" width="8.88671875" style="6"/>
     <col min="6" max="7" width="8.88671875" style="6"/>
     <col min="9" max="9" width="8.88671875" style="6"/>
   </cols>
@@ -984,7 +994,9 @@
       <c r="B2">
         <v>4</v>
       </c>
-      <c r="C2" s="6"/>
+      <c r="C2" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F2">
         <v>0</v>
       </c>
@@ -1010,7 +1022,9 @@
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" s="6"/>
+      <c r="C3" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F3">
         <v>7</v>
       </c>
@@ -1036,7 +1050,9 @@
       <c r="B4">
         <v>0</v>
       </c>
-      <c r="C4" s="6"/>
+      <c r="C4" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F4">
         <v>8</v>
       </c>
@@ -1055,7 +1071,9 @@
       <c r="B5">
         <v>2</v>
       </c>
-      <c r="C5" s="6"/>
+      <c r="C5" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F5">
         <v>12</v>
       </c>
@@ -1074,7 +1092,9 @@
       <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" s="6"/>
+      <c r="C6" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F6">
         <v>13</v>
       </c>
@@ -1093,8 +1113,10 @@
       <c r="B7">
         <v>6</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="9"/>
+      <c r="C7" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="8"/>
       <c r="F7">
         <v>14</v>
       </c>
@@ -1113,7 +1135,9 @@
       <c r="B8">
         <v>4</v>
       </c>
-      <c r="C8" s="6"/>
+      <c r="C8" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F8">
         <v>18</v>
       </c>
@@ -1132,7 +1156,9 @@
       <c r="B9">
         <v>2</v>
       </c>
-      <c r="C9" s="6"/>
+      <c r="C9" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F9">
         <v>20</v>
       </c>
@@ -1166,7 +1192,9 @@
       <c r="B10">
         <v>1</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F10">
         <v>22</v>
       </c>
@@ -1185,7 +1213,9 @@
       <c r="B11">
         <v>4</v>
       </c>
-      <c r="C11" s="6"/>
+      <c r="C11" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F11">
         <v>23</v>
       </c>
@@ -1204,7 +1234,9 @@
       <c r="B12">
         <v>4</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F12">
         <v>25</v>
       </c>
@@ -1223,7 +1255,9 @@
       <c r="B13">
         <v>2</v>
       </c>
-      <c r="C13" s="6"/>
+      <c r="C13" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F13">
         <v>29</v>
       </c>
@@ -1242,7 +1276,9 @@
       <c r="B14">
         <v>7</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F14">
         <v>30</v>
       </c>
@@ -1261,7 +1297,9 @@
       <c r="B15">
         <v>2</v>
       </c>
-      <c r="C15" s="6"/>
+      <c r="C15" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F15">
         <v>32</v>
       </c>
@@ -1280,7 +1318,12 @@
       <c r="B16">
         <v>1</v>
       </c>
-      <c r="C16" s="6"/>
+      <c r="C16" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="6">
+        <v>2</v>
+      </c>
       <c r="F16">
         <v>43</v>
       </c>
@@ -1314,7 +1357,9 @@
       <c r="B17">
         <v>7</v>
       </c>
-      <c r="C17" s="6"/>
+      <c r="C17" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F17">
         <v>44</v>
       </c>
@@ -1334,7 +1379,9 @@
       <c r="B18">
         <v>1</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F18">
         <v>45</v>
       </c>
@@ -1346,27 +1393,30 @@
         <v>T</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A19">
+    <row r="19" spans="1:20" s="9" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="9">
         <v>48</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="9">
         <v>3</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="F19">
+      <c r="C19" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="10"/>
+      <c r="F19" s="9">
         <v>48</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="9">
         <v>7</v>
       </c>
-      <c r="I19" s="6" t="str">
+      <c r="I19" s="10" t="str">
         <f t="shared" si="0"/>
         <v>F</v>
       </c>
-      <c r="O19" s="10"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="12"/>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20">
@@ -1375,7 +1425,9 @@
       <c r="B20">
         <v>1</v>
       </c>
-      <c r="C20" s="6"/>
+      <c r="C20" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F20">
         <v>49</v>
       </c>
@@ -1394,7 +1446,9 @@
       <c r="B21">
         <v>7</v>
       </c>
-      <c r="C21" s="6"/>
+      <c r="C21" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F21">
         <v>51</v>
       </c>
@@ -1413,7 +1467,9 @@
       <c r="B22">
         <v>2</v>
       </c>
-      <c r="C22" s="6"/>
+      <c r="C22" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F22">
         <v>52</v>
       </c>
@@ -1432,7 +1488,9 @@
       <c r="B23">
         <v>1</v>
       </c>
-      <c r="C23" s="6"/>
+      <c r="C23" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F23">
         <v>56</v>
       </c>
@@ -1451,7 +1509,9 @@
       <c r="B24">
         <v>2</v>
       </c>
-      <c r="C24" s="6"/>
+      <c r="C24" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F24">
         <v>57</v>
       </c>
@@ -1470,7 +1530,9 @@
       <c r="B25">
         <v>1</v>
       </c>
-      <c r="C25" s="6"/>
+      <c r="C25" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F25">
         <v>59</v>
       </c>
@@ -1489,7 +1551,9 @@
       <c r="B26">
         <v>6</v>
       </c>
-      <c r="C26" s="6"/>
+      <c r="C26" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F26">
         <v>63</v>
       </c>
@@ -1546,7 +1610,9 @@
       <c r="B29">
         <v>5</v>
       </c>
-      <c r="C29" s="6"/>
+      <c r="C29" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F29">
         <v>69</v>
       </c>
@@ -1565,7 +1631,9 @@
       <c r="B30">
         <v>6</v>
       </c>
-      <c r="C30" s="6"/>
+      <c r="C30" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F30">
         <v>70</v>
       </c>
@@ -1584,7 +1652,9 @@
       <c r="B31">
         <v>4</v>
       </c>
-      <c r="C31" s="6"/>
+      <c r="C31" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F31">
         <v>71</v>
       </c>
@@ -1603,7 +1673,9 @@
       <c r="B32">
         <v>2</v>
       </c>
-      <c r="C32" s="6"/>
+      <c r="C32" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F32">
         <v>73</v>
       </c>
@@ -1622,7 +1694,9 @@
       <c r="B33">
         <v>6</v>
       </c>
-      <c r="C33" s="6"/>
+      <c r="C33" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F33">
         <v>76</v>
       </c>
@@ -1641,7 +1715,9 @@
       <c r="B34">
         <v>3</v>
       </c>
-      <c r="C34" s="6"/>
+      <c r="C34" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F34">
         <v>78</v>
       </c>
@@ -1660,7 +1736,9 @@
       <c r="B35">
         <v>9</v>
       </c>
-      <c r="C35" s="6"/>
+      <c r="C35" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F35">
         <v>80</v>
       </c>
@@ -1679,7 +1757,9 @@
       <c r="B36">
         <v>2</v>
       </c>
-      <c r="C36" s="6"/>
+      <c r="C36" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="F36">
         <v>83</v>
       </c>
@@ -1698,7 +1778,12 @@
       <c r="B37">
         <v>9</v>
       </c>
-      <c r="C37" s="6"/>
+      <c r="C37" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="6">
+        <v>3</v>
+      </c>
       <c r="F37">
         <v>84</v>
       </c>

--- a/compareOP.xlsx
+++ b/compareOP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DUT\Ki_2\Edge_AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E80FC8-4267-4355-B75D-E933E567E4CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{165622EA-66A6-4044-95BD-133930B0398A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{56603411-7B59-498E-88B9-7E9448248F05}"/>
   </bookViews>
@@ -1001,18 +1001,18 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I2" s="6" t="str">
         <f>IF(B2=G2, "T", "F")</f>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="L2" s="4">
         <f>COUNTIF(I2:I1001, "T")</f>
-        <v>748</v>
+        <v>771</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="L3" s="4">
         <f>L2/1000*100</f>
-        <v>74.8</v>
+        <v>77.100000000000009</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -1078,7 +1078,7 @@
         <v>12</v>
       </c>
       <c r="G5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I5" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1121,7 +1121,7 @@
         <v>14</v>
       </c>
       <c r="G7">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I7" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1328,11 +1328,11 @@
         <v>43</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>T</v>
       </c>
       <c r="N16" s="3">
         <v>5</v>
@@ -1404,15 +1404,15 @@
         <v>4</v>
       </c>
       <c r="D19" s="10"/>
-      <c r="F19" s="9">
+      <c r="F19">
         <v>48</v>
       </c>
-      <c r="G19" s="9">
-        <v>7</v>
+      <c r="G19">
+        <v>3</v>
       </c>
       <c r="I19" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>T</v>
       </c>
       <c r="O19" s="11"/>
       <c r="P19" s="12"/>
@@ -1495,11 +1495,11 @@
         <v>56</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
@@ -1577,11 +1577,11 @@
         <v>65</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
@@ -1596,11 +1596,11 @@
         <v>67</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
@@ -1845,7 +1845,7 @@
         <v>88</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I40" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1940,11 +1940,11 @@
         <v>100</v>
       </c>
       <c r="G45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I45" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
@@ -2054,11 +2054,11 @@
         <v>111</v>
       </c>
       <c r="G51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I51" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
@@ -2073,11 +2073,11 @@
         <v>115</v>
       </c>
       <c r="G52">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I52" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
@@ -2206,11 +2206,11 @@
         <v>132</v>
       </c>
       <c r="G59">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I59" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
@@ -2244,7 +2244,7 @@
         <v>135</v>
       </c>
       <c r="G61">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I61" s="6" t="str">
         <f t="shared" si="0"/>
@@ -2301,7 +2301,7 @@
         <v>141</v>
       </c>
       <c r="G64">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I64" s="6" t="str">
         <f t="shared" si="0"/>
@@ -2339,11 +2339,11 @@
         <v>144</v>
       </c>
       <c r="G66">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I66" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
@@ -2358,11 +2358,11 @@
         <v>149</v>
       </c>
       <c r="G67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I67" s="6" t="str">
         <f t="shared" ref="I67:I130" si="1">IF(B67=G67, "T", "F")</f>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
@@ -2396,11 +2396,11 @@
         <v>152</v>
       </c>
       <c r="G69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I69" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
@@ -2415,7 +2415,7 @@
         <v>155</v>
       </c>
       <c r="G70">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I70" s="6" t="str">
         <f t="shared" si="1"/>
@@ -2453,7 +2453,7 @@
         <v>157</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I72" s="6" t="str">
         <f t="shared" si="1"/>
@@ -2529,11 +2529,11 @@
         <v>166</v>
       </c>
       <c r="G76">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I76" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
@@ -2567,7 +2567,7 @@
         <v>170</v>
       </c>
       <c r="G78">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I78" s="6" t="str">
         <f t="shared" si="1"/>
@@ -2700,11 +2700,11 @@
         <v>179</v>
       </c>
       <c r="G85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I85" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
@@ -2890,11 +2890,11 @@
         <v>198</v>
       </c>
       <c r="G95">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I95" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
@@ -2985,7 +2985,7 @@
         <v>208</v>
       </c>
       <c r="G100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I100" s="6" t="str">
         <f t="shared" si="1"/>
@@ -3080,11 +3080,11 @@
         <v>213</v>
       </c>
       <c r="G105">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I105" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
@@ -3099,7 +3099,7 @@
         <v>218</v>
       </c>
       <c r="G106">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I106" s="6" t="str">
         <f t="shared" si="1"/>
@@ -3118,7 +3118,7 @@
         <v>219</v>
       </c>
       <c r="G107">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I107" s="6" t="str">
         <f t="shared" si="1"/>
@@ -3137,7 +3137,7 @@
         <v>220</v>
       </c>
       <c r="G108">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I108" s="6" t="str">
         <f t="shared" si="1"/>
@@ -3156,11 +3156,11 @@
         <v>221</v>
       </c>
       <c r="G109">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I109" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
@@ -3232,7 +3232,7 @@
         <v>229</v>
       </c>
       <c r="G113">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I113" s="6" t="str">
         <f t="shared" si="1"/>
@@ -3289,11 +3289,11 @@
         <v>233</v>
       </c>
       <c r="G116">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I116" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
@@ -3365,11 +3365,11 @@
         <v>240</v>
       </c>
       <c r="G120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I120" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
@@ -3517,11 +3517,11 @@
         <v>257</v>
       </c>
       <c r="G128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I128" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
@@ -3574,11 +3574,11 @@
         <v>263</v>
       </c>
       <c r="G131">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I131" s="6" t="str">
         <f t="shared" ref="I131:I194" si="2">IF(B131=G131, "T", "F")</f>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
@@ -3669,7 +3669,7 @@
         <v>273</v>
       </c>
       <c r="G136">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I136" s="6" t="str">
         <f t="shared" si="2"/>
@@ -3688,11 +3688,11 @@
         <v>275</v>
       </c>
       <c r="G137">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I137" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.3">
@@ -3745,11 +3745,11 @@
         <v>278</v>
       </c>
       <c r="G140">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I140" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.3">
@@ -3840,11 +3840,11 @@
         <v>286</v>
       </c>
       <c r="G145">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I145" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.3">
@@ -3878,7 +3878,7 @@
         <v>288</v>
       </c>
       <c r="G147">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I147" s="6" t="str">
         <f t="shared" si="2"/>
@@ -3916,7 +3916,7 @@
         <v>290</v>
       </c>
       <c r="G149">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I149" s="6" t="str">
         <f t="shared" si="2"/>
@@ -3954,7 +3954,7 @@
         <v>294</v>
       </c>
       <c r="G151">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I151" s="6" t="str">
         <f t="shared" si="2"/>
@@ -3992,7 +3992,7 @@
         <v>297</v>
       </c>
       <c r="G153">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I153" s="6" t="str">
         <f t="shared" si="2"/>
@@ -4087,7 +4087,7 @@
         <v>304</v>
       </c>
       <c r="G158">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I158" s="6" t="str">
         <f t="shared" si="2"/>
@@ -4125,11 +4125,11 @@
         <v>306</v>
       </c>
       <c r="G160">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I160" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.3">
@@ -4182,11 +4182,11 @@
         <v>309</v>
       </c>
       <c r="G163">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I163" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
@@ -4220,7 +4220,7 @@
         <v>313</v>
       </c>
       <c r="G165">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I165" s="6" t="str">
         <f t="shared" si="2"/>
@@ -4372,11 +4372,11 @@
         <v>325</v>
       </c>
       <c r="G173">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I173" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.3">
@@ -4391,11 +4391,11 @@
         <v>331</v>
       </c>
       <c r="G174">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I174" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.3">
@@ -4410,7 +4410,7 @@
         <v>332</v>
       </c>
       <c r="G175">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I175" s="6" t="str">
         <f t="shared" si="2"/>
@@ -4429,11 +4429,11 @@
         <v>340</v>
       </c>
       <c r="G176">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I176" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.3">
@@ -4467,11 +4467,11 @@
         <v>343</v>
       </c>
       <c r="G178">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I178" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.3">
@@ -4638,11 +4638,11 @@
         <v>353</v>
       </c>
       <c r="G187">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I187" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.3">
@@ -4809,11 +4809,11 @@
         <v>370</v>
       </c>
       <c r="G196">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I196" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.3">
@@ -4866,7 +4866,7 @@
         <v>380</v>
       </c>
       <c r="G199">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I199" s="6" t="str">
         <f t="shared" si="3"/>
@@ -4885,11 +4885,11 @@
         <v>381</v>
       </c>
       <c r="G200">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I200" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.3">
@@ -5037,7 +5037,7 @@
         <v>406</v>
       </c>
       <c r="G208">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I208" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5056,7 +5056,7 @@
         <v>407</v>
       </c>
       <c r="G209">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I209" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5113,11 +5113,11 @@
         <v>410</v>
       </c>
       <c r="G212">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I212" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.3">
@@ -5132,11 +5132,11 @@
         <v>411</v>
       </c>
       <c r="G213">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I213" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.3">
@@ -5246,7 +5246,7 @@
         <v>422</v>
       </c>
       <c r="G219">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I219" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5284,7 +5284,7 @@
         <v>424</v>
       </c>
       <c r="G221">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I221" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5417,11 +5417,11 @@
         <v>433</v>
       </c>
       <c r="G228">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I228" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.3">
@@ -5436,11 +5436,11 @@
         <v>435</v>
       </c>
       <c r="G229">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I229" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.3">
@@ -5474,7 +5474,7 @@
         <v>438</v>
       </c>
       <c r="G231">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I231" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5550,7 +5550,7 @@
         <v>444</v>
       </c>
       <c r="G235">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I235" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5569,7 +5569,7 @@
         <v>445</v>
       </c>
       <c r="G236">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I236" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5683,11 +5683,11 @@
         <v>458</v>
       </c>
       <c r="G242">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I242" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.3">
@@ -5778,11 +5778,11 @@
         <v>464</v>
       </c>
       <c r="G247">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I247" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.3">
@@ -5816,11 +5816,11 @@
         <v>472</v>
       </c>
       <c r="G249">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I249" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.3">
@@ -5854,7 +5854,7 @@
         <v>479</v>
       </c>
       <c r="G251">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I251" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5873,11 +5873,11 @@
         <v>480</v>
       </c>
       <c r="G252">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I252" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.3">
@@ -6063,11 +6063,11 @@
         <v>498</v>
       </c>
       <c r="G262">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I262" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.3">
@@ -6101,11 +6101,11 @@
         <v>503</v>
       </c>
       <c r="G264">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I264" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.3">
@@ -6177,11 +6177,11 @@
         <v>509</v>
       </c>
       <c r="G268">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I268" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.3">
@@ -6196,7 +6196,7 @@
         <v>511</v>
       </c>
       <c r="G269">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I269" s="6" t="str">
         <f t="shared" si="4"/>
@@ -6405,11 +6405,11 @@
         <v>532</v>
       </c>
       <c r="G280">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I280" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.3">
@@ -6462,11 +6462,11 @@
         <v>535</v>
       </c>
       <c r="G283">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I283" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.3">
@@ -6595,11 +6595,11 @@
         <v>549</v>
       </c>
       <c r="G290">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I290" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.3">
@@ -6709,11 +6709,11 @@
         <v>557</v>
       </c>
       <c r="G296">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I296" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.3">
@@ -6804,7 +6804,7 @@
         <v>567</v>
       </c>
       <c r="G301">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I301" s="6" t="str">
         <f t="shared" si="4"/>
@@ -6880,11 +6880,11 @@
         <v>572</v>
       </c>
       <c r="G305">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I305" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.3">
@@ -6956,11 +6956,11 @@
         <v>582</v>
       </c>
       <c r="G309">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I309" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.3">
@@ -7032,7 +7032,7 @@
         <v>590</v>
       </c>
       <c r="G313">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I313" s="6" t="str">
         <f t="shared" si="4"/>
@@ -7108,11 +7108,11 @@
         <v>597</v>
       </c>
       <c r="G317">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I317" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.3">
@@ -7488,7 +7488,7 @@
         <v>636</v>
       </c>
       <c r="G337">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I337" s="6" t="str">
         <f t="shared" si="5"/>
@@ -7526,7 +7526,7 @@
         <v>642</v>
       </c>
       <c r="G339">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I339" s="6" t="str">
         <f t="shared" si="5"/>
@@ -7583,7 +7583,7 @@
         <v>647</v>
       </c>
       <c r="G342">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I342" s="6" t="str">
         <f t="shared" si="5"/>
@@ -7659,7 +7659,7 @@
         <v>654</v>
       </c>
       <c r="G346">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I346" s="6" t="str">
         <f t="shared" si="5"/>
@@ -7678,7 +7678,7 @@
         <v>655</v>
       </c>
       <c r="G347">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I347" s="6" t="str">
         <f t="shared" si="5"/>
@@ -7754,7 +7754,7 @@
         <v>668</v>
       </c>
       <c r="G351">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I351" s="6" t="str">
         <f t="shared" si="5"/>
@@ -7792,7 +7792,7 @@
         <v>672</v>
       </c>
       <c r="G353">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I353" s="6" t="str">
         <f t="shared" si="5"/>
@@ -7830,7 +7830,7 @@
         <v>676</v>
       </c>
       <c r="G355">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I355" s="6" t="str">
         <f t="shared" si="5"/>
@@ -7849,11 +7849,11 @@
         <v>677</v>
       </c>
       <c r="G356">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I356" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.3">
@@ -7925,7 +7925,7 @@
         <v>682</v>
       </c>
       <c r="G360">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I360" s="6" t="str">
         <f t="shared" si="5"/>
@@ -8096,7 +8096,7 @@
         <v>700</v>
       </c>
       <c r="G369">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I369" s="6" t="str">
         <f t="shared" si="5"/>
@@ -8134,11 +8134,11 @@
         <v>707</v>
       </c>
       <c r="G371">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I371" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.3">
@@ -8172,11 +8172,11 @@
         <v>715</v>
       </c>
       <c r="G373">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I373" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.3">
@@ -8305,11 +8305,11 @@
         <v>736</v>
       </c>
       <c r="G380">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I380" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="381" spans="1:9" x14ac:dyDescent="0.3">
@@ -8419,11 +8419,11 @@
         <v>749</v>
       </c>
       <c r="G386">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I386" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="387" spans="1:9" x14ac:dyDescent="0.3">
@@ -8533,11 +8533,11 @@
         <v>761</v>
       </c>
       <c r="G392">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I392" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.3">
@@ -8590,7 +8590,7 @@
         <v>767</v>
       </c>
       <c r="G395">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I395" s="6" t="str">
         <f t="shared" si="6"/>
@@ -8685,7 +8685,7 @@
         <v>782</v>
       </c>
       <c r="G400">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I400" s="6" t="str">
         <f t="shared" si="6"/>
@@ -8723,11 +8723,11 @@
         <v>785</v>
       </c>
       <c r="G402">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I402" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.3">
@@ -8894,11 +8894,11 @@
         <v>800</v>
       </c>
       <c r="G411">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I411" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.3">
@@ -8989,7 +8989,7 @@
         <v>807</v>
       </c>
       <c r="G416">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I416" s="6" t="str">
         <f t="shared" si="6"/>
@@ -9084,11 +9084,11 @@
         <v>812</v>
       </c>
       <c r="G421">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I421" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="422" spans="1:9" x14ac:dyDescent="0.3">
@@ -9122,11 +9122,11 @@
         <v>819</v>
       </c>
       <c r="G423">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I423" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="424" spans="1:9" x14ac:dyDescent="0.3">
@@ -9141,11 +9141,11 @@
         <v>821</v>
       </c>
       <c r="G424">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I424" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="425" spans="1:9" x14ac:dyDescent="0.3">
@@ -9179,11 +9179,11 @@
         <v>831</v>
       </c>
       <c r="G426">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I426" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="427" spans="1:9" x14ac:dyDescent="0.3">
@@ -9217,11 +9217,11 @@
         <v>836</v>
       </c>
       <c r="G428">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I428" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.3">
@@ -9350,7 +9350,7 @@
         <v>844</v>
       </c>
       <c r="G435">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I435" s="6" t="str">
         <f t="shared" si="6"/>
@@ -9369,11 +9369,11 @@
         <v>845</v>
       </c>
       <c r="G436">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I436" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="437" spans="1:9" x14ac:dyDescent="0.3">
@@ -9407,11 +9407,11 @@
         <v>855</v>
       </c>
       <c r="G438">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I438" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="439" spans="1:9" x14ac:dyDescent="0.3">
@@ -9540,11 +9540,11 @@
         <v>864</v>
       </c>
       <c r="G445">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I445" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="446" spans="1:9" x14ac:dyDescent="0.3">
@@ -9597,7 +9597,7 @@
         <v>869</v>
       </c>
       <c r="G448">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I448" s="6" t="str">
         <f t="shared" si="6"/>
@@ -9673,11 +9673,11 @@
         <v>879</v>
       </c>
       <c r="G452">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I452" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="453" spans="1:9" x14ac:dyDescent="0.3">
@@ -9692,11 +9692,11 @@
         <v>881</v>
       </c>
       <c r="G453">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I453" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="454" spans="1:9" x14ac:dyDescent="0.3">
@@ -9768,11 +9768,11 @@
         <v>887</v>
       </c>
       <c r="G457">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I457" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="458" spans="1:9" x14ac:dyDescent="0.3">
@@ -9844,7 +9844,7 @@
         <v>891</v>
       </c>
       <c r="G461">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I461" s="6" t="str">
         <f t="shared" si="7"/>
@@ -9882,7 +9882,7 @@
         <v>898</v>
       </c>
       <c r="G463">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I463" s="6" t="str">
         <f t="shared" si="7"/>
@@ -9939,11 +9939,11 @@
         <v>903</v>
       </c>
       <c r="G466">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I466" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="467" spans="1:9" x14ac:dyDescent="0.3">
@@ -9958,11 +9958,11 @@
         <v>906</v>
       </c>
       <c r="G467">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I467" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="468" spans="1:9" x14ac:dyDescent="0.3">
@@ -9996,11 +9996,11 @@
         <v>908</v>
       </c>
       <c r="G469">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I469" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="470" spans="1:9" x14ac:dyDescent="0.3">
@@ -10034,11 +10034,11 @@
         <v>911</v>
       </c>
       <c r="G471">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I471" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="472" spans="1:9" x14ac:dyDescent="0.3">
@@ -10148,7 +10148,7 @@
         <v>926</v>
       </c>
       <c r="G477">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I477" s="6" t="str">
         <f t="shared" si="7"/>
@@ -10547,11 +10547,11 @@
         <v>969</v>
       </c>
       <c r="G498">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I498" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="499" spans="1:9" x14ac:dyDescent="0.3">
@@ -10585,7 +10585,7 @@
         <v>973</v>
       </c>
       <c r="G500">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I500" s="6" t="str">
         <f t="shared" si="7"/>
@@ -10680,11 +10680,11 @@
         <v>988</v>
       </c>
       <c r="G505">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I505" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="506" spans="1:9" x14ac:dyDescent="0.3">
@@ -10908,7 +10908,7 @@
         <v>1011</v>
       </c>
       <c r="G517">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I517" s="6" t="str">
         <f t="shared" si="8"/>
@@ -10946,11 +10946,11 @@
         <v>1017</v>
       </c>
       <c r="G519">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I519" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="520" spans="1:9" x14ac:dyDescent="0.3">
@@ -11041,7 +11041,7 @@
         <v>1027</v>
       </c>
       <c r="G524">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I524" s="6" t="str">
         <f t="shared" si="8"/>
@@ -11383,11 +11383,11 @@
         <v>1058</v>
       </c>
       <c r="G542">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I542" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="543" spans="1:9" x14ac:dyDescent="0.3">
@@ -11402,11 +11402,11 @@
         <v>1061</v>
       </c>
       <c r="G543">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I543" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="544" spans="1:9" x14ac:dyDescent="0.3">
@@ -11573,7 +11573,7 @@
         <v>1083</v>
       </c>
       <c r="G552">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I552" s="6" t="str">
         <f t="shared" si="8"/>
@@ -11668,7 +11668,7 @@
         <v>1090</v>
       </c>
       <c r="G557">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I557" s="6" t="str">
         <f t="shared" si="8"/>
@@ -11706,11 +11706,11 @@
         <v>1093</v>
       </c>
       <c r="G559">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I559" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="560" spans="1:9" x14ac:dyDescent="0.3">
@@ -11725,7 +11725,7 @@
         <v>1094</v>
       </c>
       <c r="G560">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I560" s="6" t="str">
         <f t="shared" si="8"/>
@@ -11782,11 +11782,11 @@
         <v>1098</v>
       </c>
       <c r="G563">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I563" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="564" spans="1:9" x14ac:dyDescent="0.3">
@@ -11858,11 +11858,11 @@
         <v>1103</v>
       </c>
       <c r="G567">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I567" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="568" spans="1:9" x14ac:dyDescent="0.3">
@@ -11934,7 +11934,7 @@
         <v>1113</v>
       </c>
       <c r="G571">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I571" s="6" t="str">
         <f t="shared" si="8"/>
@@ -12029,11 +12029,11 @@
         <v>1124</v>
       </c>
       <c r="G576">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I576" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="577" spans="1:9" x14ac:dyDescent="0.3">
@@ -12067,11 +12067,11 @@
         <v>1127</v>
       </c>
       <c r="G578">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I578" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="579" spans="1:9" x14ac:dyDescent="0.3">
@@ -12257,7 +12257,7 @@
         <v>1159</v>
       </c>
       <c r="G588">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I588" s="6" t="str">
         <f t="shared" si="9"/>
@@ -12314,11 +12314,11 @@
         <v>1173</v>
       </c>
       <c r="G591">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I591" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="592" spans="1:9" x14ac:dyDescent="0.3">
@@ -12352,11 +12352,11 @@
         <v>1177</v>
       </c>
       <c r="G593">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I593" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="594" spans="1:9" x14ac:dyDescent="0.3">
@@ -12523,11 +12523,11 @@
         <v>1192</v>
       </c>
       <c r="G602">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I602" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="603" spans="1:9" x14ac:dyDescent="0.3">
@@ -12561,7 +12561,7 @@
         <v>1196</v>
       </c>
       <c r="G604">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I604" s="6" t="str">
         <f t="shared" si="9"/>
@@ -12580,11 +12580,11 @@
         <v>1200</v>
       </c>
       <c r="G605">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I605" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="606" spans="1:9" x14ac:dyDescent="0.3">
@@ -12694,11 +12694,11 @@
         <v>1211</v>
       </c>
       <c r="G611">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I611" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="612" spans="1:9" x14ac:dyDescent="0.3">
@@ -12732,11 +12732,11 @@
         <v>1216</v>
       </c>
       <c r="G613">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I613" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="614" spans="1:9" x14ac:dyDescent="0.3">
@@ -12770,11 +12770,11 @@
         <v>1221</v>
       </c>
       <c r="G615">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I615" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="616" spans="1:9" x14ac:dyDescent="0.3">
@@ -12827,7 +12827,7 @@
         <v>1226</v>
       </c>
       <c r="G618">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I618" s="6" t="str">
         <f t="shared" si="9"/>
@@ -12884,11 +12884,11 @@
         <v>1230</v>
       </c>
       <c r="G621">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I621" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="622" spans="1:9" x14ac:dyDescent="0.3">
@@ -13017,11 +13017,11 @@
         <v>1239</v>
       </c>
       <c r="G628">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I628" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="629" spans="1:9" x14ac:dyDescent="0.3">
@@ -13112,11 +13112,11 @@
         <v>1251</v>
       </c>
       <c r="G633">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I633" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="634" spans="1:9" x14ac:dyDescent="0.3">
@@ -13264,7 +13264,7 @@
         <v>1265</v>
       </c>
       <c r="G641">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I641" s="6" t="str">
         <f t="shared" si="9"/>
@@ -13283,11 +13283,11 @@
         <v>1268</v>
       </c>
       <c r="G642">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I642" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="643" spans="1:9" x14ac:dyDescent="0.3">
@@ -13416,11 +13416,11 @@
         <v>1281</v>
       </c>
       <c r="G649">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I649" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="650" spans="1:9" x14ac:dyDescent="0.3">
@@ -13473,11 +13473,11 @@
         <v>1286</v>
       </c>
       <c r="G652">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I652" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="653" spans="1:9" x14ac:dyDescent="0.3">
@@ -13492,7 +13492,7 @@
         <v>1288</v>
       </c>
       <c r="G653">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I653" s="6" t="str">
         <f t="shared" si="10"/>
@@ -13511,11 +13511,11 @@
         <v>1289</v>
       </c>
       <c r="G654">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I654" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="655" spans="1:9" x14ac:dyDescent="0.3">
@@ -13606,11 +13606,11 @@
         <v>1299</v>
       </c>
       <c r="G659">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I659" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="660" spans="1:9" x14ac:dyDescent="0.3">
@@ -13644,11 +13644,11 @@
         <v>1307</v>
       </c>
       <c r="G661">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I661" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="662" spans="1:9" x14ac:dyDescent="0.3">
@@ -13758,7 +13758,7 @@
         <v>1321</v>
       </c>
       <c r="G667">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I667" s="6" t="str">
         <f t="shared" si="10"/>
@@ -13777,7 +13777,7 @@
         <v>1322</v>
       </c>
       <c r="G668">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I668" s="6" t="str">
         <f t="shared" si="10"/>
@@ -13834,7 +13834,7 @@
         <v>1330</v>
       </c>
       <c r="G671">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I671" s="6" t="str">
         <f t="shared" si="10"/>
@@ -13853,7 +13853,7 @@
         <v>1334</v>
       </c>
       <c r="G672">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I672" s="6" t="str">
         <f t="shared" si="10"/>
@@ -13872,7 +13872,7 @@
         <v>1336</v>
       </c>
       <c r="G673">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I673" s="6" t="str">
         <f t="shared" si="10"/>
@@ -13891,11 +13891,11 @@
         <v>1337</v>
       </c>
       <c r="G674">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I674" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="675" spans="1:9" x14ac:dyDescent="0.3">
@@ -14138,11 +14138,11 @@
         <v>1360</v>
       </c>
       <c r="G687">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I687" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="688" spans="1:9" x14ac:dyDescent="0.3">
@@ -14157,11 +14157,11 @@
         <v>1361</v>
       </c>
       <c r="G688">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I688" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="689" spans="1:9" x14ac:dyDescent="0.3">
@@ -14195,11 +14195,11 @@
         <v>1364</v>
       </c>
       <c r="G690">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I690" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="691" spans="1:9" x14ac:dyDescent="0.3">
@@ -14271,7 +14271,7 @@
         <v>1373</v>
       </c>
       <c r="G694">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I694" s="6" t="str">
         <f t="shared" si="10"/>
@@ -14309,7 +14309,7 @@
         <v>1375</v>
       </c>
       <c r="G696">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I696" s="6" t="str">
         <f t="shared" si="10"/>
@@ -14328,11 +14328,11 @@
         <v>1376</v>
       </c>
       <c r="G697">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I697" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="698" spans="1:9" x14ac:dyDescent="0.3">
@@ -14423,11 +14423,11 @@
         <v>1391</v>
       </c>
       <c r="G702">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I702" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="703" spans="1:9" x14ac:dyDescent="0.3">
@@ -14442,11 +14442,11 @@
         <v>1392</v>
       </c>
       <c r="G703">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I703" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="704" spans="1:9" x14ac:dyDescent="0.3">
@@ -14480,11 +14480,11 @@
         <v>1395</v>
       </c>
       <c r="G705">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I705" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="706" spans="1:9" x14ac:dyDescent="0.3">
@@ -14556,11 +14556,11 @@
         <v>1402</v>
       </c>
       <c r="G709">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I709" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="710" spans="1:9" x14ac:dyDescent="0.3">
@@ -14613,7 +14613,7 @@
         <v>1407</v>
       </c>
       <c r="G712">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I712" s="6" t="str">
         <f t="shared" si="11"/>
@@ -14822,11 +14822,11 @@
         <v>1426</v>
       </c>
       <c r="G723">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I723" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="724" spans="1:9" x14ac:dyDescent="0.3">
@@ -14898,11 +14898,11 @@
         <v>1432</v>
       </c>
       <c r="G727">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I727" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="728" spans="1:9" x14ac:dyDescent="0.3">
@@ -14955,7 +14955,7 @@
         <v>1437</v>
       </c>
       <c r="G730">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I730" s="6" t="str">
         <f t="shared" si="11"/>
@@ -15164,11 +15164,11 @@
         <v>1457</v>
       </c>
       <c r="G741">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I741" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="742" spans="1:9" x14ac:dyDescent="0.3">
@@ -15297,11 +15297,11 @@
         <v>1472</v>
       </c>
       <c r="G748">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I748" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="749" spans="1:9" x14ac:dyDescent="0.3">
@@ -15316,11 +15316,11 @@
         <v>1474</v>
       </c>
       <c r="G749">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I749" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="750" spans="1:9" x14ac:dyDescent="0.3">
@@ -15487,7 +15487,7 @@
         <v>1494</v>
       </c>
       <c r="G758">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I758" s="6" t="str">
         <f t="shared" si="11"/>
@@ -15506,7 +15506,7 @@
         <v>1497</v>
       </c>
       <c r="G759">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I759" s="6" t="str">
         <f t="shared" si="11"/>
@@ -15544,11 +15544,11 @@
         <v>1502</v>
       </c>
       <c r="G761">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I761" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="762" spans="1:9" x14ac:dyDescent="0.3">
@@ -15639,7 +15639,7 @@
         <v>1509</v>
       </c>
       <c r="G766">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I766" s="6" t="str">
         <f t="shared" si="11"/>
@@ -15696,11 +15696,11 @@
         <v>1512</v>
       </c>
       <c r="G769">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I769" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="770" spans="1:9" x14ac:dyDescent="0.3">
@@ -15734,7 +15734,7 @@
         <v>1518</v>
       </c>
       <c r="G771">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I771" s="6" t="str">
         <f t="shared" ref="I771:I834" si="12">IF(B771=G771, "T", "F")</f>
@@ -15848,7 +15848,7 @@
         <v>1538</v>
       </c>
       <c r="G777">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I777" s="6" t="str">
         <f t="shared" si="12"/>
@@ -15981,11 +15981,11 @@
         <v>1554</v>
       </c>
       <c r="G784">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I784" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="785" spans="1:9" x14ac:dyDescent="0.3">
@@ -16133,11 +16133,11 @@
         <v>1566</v>
       </c>
       <c r="G792">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I792" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="793" spans="1:9" x14ac:dyDescent="0.3">
@@ -16304,7 +16304,7 @@
         <v>1582</v>
       </c>
       <c r="G801">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I801" s="6" t="str">
         <f t="shared" si="12"/>
@@ -16323,7 +16323,7 @@
         <v>1583</v>
       </c>
       <c r="G802">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I802" s="6" t="str">
         <f t="shared" si="12"/>
@@ -16399,11 +16399,11 @@
         <v>1588</v>
       </c>
       <c r="G806">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I806" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="807" spans="1:9" x14ac:dyDescent="0.3">
@@ -16627,11 +16627,11 @@
         <v>1611</v>
       </c>
       <c r="G818">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I818" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="819" spans="1:9" x14ac:dyDescent="0.3">
@@ -16684,11 +16684,11 @@
         <v>1614</v>
       </c>
       <c r="G821">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I821" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="822" spans="1:9" x14ac:dyDescent="0.3">
@@ -16722,11 +16722,11 @@
         <v>1618</v>
       </c>
       <c r="G823">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I823" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="824" spans="1:9" x14ac:dyDescent="0.3">
@@ -16969,11 +16969,11 @@
         <v>1655</v>
       </c>
       <c r="G836">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I836" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="837" spans="1:9" x14ac:dyDescent="0.3">
@@ -17140,7 +17140,7 @@
         <v>1674</v>
       </c>
       <c r="G845">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I845" s="6" t="str">
         <f t="shared" si="13"/>
@@ -17159,11 +17159,11 @@
         <v>1675</v>
       </c>
       <c r="G846">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I846" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="847" spans="1:9" x14ac:dyDescent="0.3">
@@ -17273,11 +17273,11 @@
         <v>1690</v>
       </c>
       <c r="G852">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I852" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="853" spans="1:9" x14ac:dyDescent="0.3">
@@ -17425,7 +17425,7 @@
         <v>1710</v>
       </c>
       <c r="G860">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I860" s="6" t="str">
         <f t="shared" si="13"/>
@@ -17444,11 +17444,11 @@
         <v>1711</v>
       </c>
       <c r="G861">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I861" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="862" spans="1:9" x14ac:dyDescent="0.3">
@@ -17539,7 +17539,7 @@
         <v>1718</v>
       </c>
       <c r="G866">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I866" s="6" t="str">
         <f t="shared" si="13"/>
@@ -17596,7 +17596,7 @@
         <v>1723</v>
       </c>
       <c r="G869">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I869" s="6" t="str">
         <f t="shared" si="13"/>
@@ -17634,11 +17634,11 @@
         <v>1727</v>
       </c>
       <c r="G871">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I871" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="872" spans="1:9" x14ac:dyDescent="0.3">
@@ -17691,7 +17691,7 @@
         <v>1731</v>
       </c>
       <c r="G874">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I874" s="6" t="str">
         <f t="shared" si="13"/>
@@ -17748,11 +17748,11 @@
         <v>1736</v>
       </c>
       <c r="G877">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I877" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="878" spans="1:9" x14ac:dyDescent="0.3">
@@ -17824,7 +17824,7 @@
         <v>1740</v>
       </c>
       <c r="G881">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I881" s="6" t="str">
         <f t="shared" si="13"/>
@@ -17843,11 +17843,11 @@
         <v>1741</v>
       </c>
       <c r="G882">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I882" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="883" spans="1:9" x14ac:dyDescent="0.3">
@@ -18071,7 +18071,7 @@
         <v>1765</v>
       </c>
       <c r="G894">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I894" s="6" t="str">
         <f t="shared" si="13"/>
@@ -18337,7 +18337,7 @@
         <v>1795</v>
       </c>
       <c r="G908">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I908" s="6" t="str">
         <f t="shared" si="14"/>
@@ -18375,11 +18375,11 @@
         <v>1800</v>
       </c>
       <c r="G910">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I910" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="911" spans="1:9" x14ac:dyDescent="0.3">
@@ -18432,7 +18432,7 @@
         <v>1805</v>
       </c>
       <c r="G913">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I913" s="6" t="str">
         <f t="shared" si="14"/>
@@ -18451,11 +18451,11 @@
         <v>1808</v>
       </c>
       <c r="G914">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I914" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="915" spans="1:9" x14ac:dyDescent="0.3">
@@ -18527,7 +18527,7 @@
         <v>1814</v>
       </c>
       <c r="G918">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I918" s="6" t="str">
         <f t="shared" si="14"/>
@@ -18546,11 +18546,11 @@
         <v>1815</v>
       </c>
       <c r="G919">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I919" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="920" spans="1:9" x14ac:dyDescent="0.3">
@@ -18584,7 +18584,7 @@
         <v>1818</v>
       </c>
       <c r="G921">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I921" s="6" t="str">
         <f t="shared" si="14"/>
@@ -18717,7 +18717,7 @@
         <v>1837</v>
       </c>
       <c r="G928">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I928" s="6" t="str">
         <f t="shared" si="14"/>
@@ -18736,11 +18736,11 @@
         <v>1839</v>
       </c>
       <c r="G929">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I929" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="930" spans="1:9" x14ac:dyDescent="0.3">
@@ -18812,7 +18812,7 @@
         <v>1845</v>
       </c>
       <c r="G933">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I933" s="6" t="str">
         <f t="shared" si="14"/>
@@ -18850,11 +18850,11 @@
         <v>1847</v>
       </c>
       <c r="G935">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I935" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="936" spans="1:9" x14ac:dyDescent="0.3">
@@ -18907,7 +18907,7 @@
         <v>1860</v>
       </c>
       <c r="G938">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I938" s="6" t="str">
         <f t="shared" si="14"/>
@@ -19021,7 +19021,7 @@
         <v>1868</v>
       </c>
       <c r="G944">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I944" s="6" t="str">
         <f t="shared" si="14"/>
@@ -19040,7 +19040,7 @@
         <v>1869</v>
       </c>
       <c r="G945">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I945" s="6" t="str">
         <f t="shared" si="14"/>
@@ -19097,11 +19097,11 @@
         <v>1877</v>
       </c>
       <c r="G948">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I948" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="949" spans="1:9" x14ac:dyDescent="0.3">
@@ -19211,11 +19211,11 @@
         <v>1896</v>
       </c>
       <c r="G954">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I954" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="955" spans="1:9" x14ac:dyDescent="0.3">
@@ -19230,11 +19230,11 @@
         <v>1898</v>
       </c>
       <c r="G955">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I955" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="956" spans="1:9" x14ac:dyDescent="0.3">
@@ -19325,11 +19325,11 @@
         <v>1911</v>
       </c>
       <c r="G960">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I960" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="961" spans="1:9" x14ac:dyDescent="0.3">
@@ -19667,11 +19667,11 @@
         <v>1941</v>
       </c>
       <c r="G978">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I978" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="979" spans="1:9" x14ac:dyDescent="0.3">
@@ -19686,11 +19686,11 @@
         <v>1945</v>
       </c>
       <c r="G979">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I979" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="980" spans="1:9" x14ac:dyDescent="0.3">
@@ -19724,11 +19724,11 @@
         <v>1948</v>
       </c>
       <c r="G981">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I981" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="982" spans="1:9" x14ac:dyDescent="0.3">
@@ -19819,11 +19819,11 @@
         <v>1953</v>
       </c>
       <c r="G986">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I986" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="987" spans="1:9" x14ac:dyDescent="0.3">
@@ -19876,11 +19876,11 @@
         <v>1957</v>
       </c>
       <c r="G989">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I989" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="990" spans="1:9" x14ac:dyDescent="0.3">
@@ -19971,7 +19971,7 @@
         <v>1965</v>
       </c>
       <c r="G994">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I994" s="6" t="str">
         <f t="shared" si="15"/>
@@ -20047,7 +20047,7 @@
         <v>1972</v>
       </c>
       <c r="G998">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I998" s="6" t="str">
         <f t="shared" si="15"/>
@@ -20066,11 +20066,11 @@
         <v>1973</v>
       </c>
       <c r="G999">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I999" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="1000" spans="1:9" x14ac:dyDescent="0.3">
@@ -20104,7 +20104,7 @@
         <v>1978</v>
       </c>
       <c r="G1001">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I1001" s="6" t="str">
         <f t="shared" si="15"/>
@@ -20150,7 +20150,7 @@
         <v>1985</v>
       </c>
       <c r="G1004">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1005" spans="1:9" x14ac:dyDescent="0.3">
@@ -20178,7 +20178,7 @@
         <v>1991</v>
       </c>
       <c r="G1006">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1007" spans="1:9" x14ac:dyDescent="0.3">
@@ -20206,7 +20206,7 @@
         <v>1993</v>
       </c>
       <c r="G1008">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1009" spans="1:7" x14ac:dyDescent="0.3">
@@ -20248,7 +20248,7 @@
         <v>2005</v>
       </c>
       <c r="G1011">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1012" spans="1:7" x14ac:dyDescent="0.3">
@@ -20276,7 +20276,7 @@
         <v>2008</v>
       </c>
       <c r="G1013">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1014" spans="1:7" x14ac:dyDescent="0.3">
@@ -20360,7 +20360,7 @@
         <v>2018</v>
       </c>
       <c r="G1019">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1020" spans="1:7" x14ac:dyDescent="0.3">
@@ -20444,7 +20444,7 @@
         <v>2028</v>
       </c>
       <c r="G1025">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1026" spans="1:7" x14ac:dyDescent="0.3">
@@ -20500,7 +20500,7 @@
         <v>2032</v>
       </c>
       <c r="G1029">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1030" spans="1:7" x14ac:dyDescent="0.3">
@@ -20668,7 +20668,7 @@
         <v>2066</v>
       </c>
       <c r="G1041">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1042" spans="1:7" x14ac:dyDescent="0.3">
@@ -20682,7 +20682,7 @@
         <v>2073</v>
       </c>
       <c r="G1042">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1043" spans="1:7" x14ac:dyDescent="0.3">
@@ -20752,7 +20752,7 @@
         <v>2086</v>
       </c>
       <c r="G1047">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1048" spans="1:7" x14ac:dyDescent="0.3">
@@ -20766,7 +20766,7 @@
         <v>2087</v>
       </c>
       <c r="G1048">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1049" spans="1:7" x14ac:dyDescent="0.3">
@@ -20794,7 +20794,7 @@
         <v>2091</v>
       </c>
       <c r="G1050">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1051" spans="1:7" x14ac:dyDescent="0.3">
@@ -20864,7 +20864,7 @@
         <v>2102</v>
       </c>
       <c r="G1055">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1056" spans="1:7" x14ac:dyDescent="0.3">
@@ -20892,7 +20892,7 @@
         <v>2104</v>
       </c>
       <c r="G1057">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1058" spans="1:7" x14ac:dyDescent="0.3">
@@ -20906,7 +20906,7 @@
         <v>2107</v>
       </c>
       <c r="G1058">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1059" spans="1:7" x14ac:dyDescent="0.3">
@@ -20948,7 +20948,7 @@
         <v>2113</v>
       </c>
       <c r="G1061">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1062" spans="1:7" x14ac:dyDescent="0.3">
@@ -20962,7 +20962,7 @@
         <v>2115</v>
       </c>
       <c r="G1062">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1063" spans="1:7" x14ac:dyDescent="0.3">
@@ -21172,7 +21172,7 @@
         <v>2155</v>
       </c>
       <c r="G1077">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1078" spans="1:7" x14ac:dyDescent="0.3">
@@ -21228,7 +21228,7 @@
         <v>2163</v>
       </c>
       <c r="G1081">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1082" spans="1:7" x14ac:dyDescent="0.3">
@@ -21284,7 +21284,7 @@
         <v>2171</v>
       </c>
       <c r="G1085">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1086" spans="1:7" x14ac:dyDescent="0.3">
@@ -21298,7 +21298,7 @@
         <v>2174</v>
       </c>
       <c r="G1086">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1087" spans="1:7" x14ac:dyDescent="0.3">
@@ -21354,7 +21354,7 @@
         <v>2183</v>
       </c>
       <c r="G1090">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1091" spans="1:7" x14ac:dyDescent="0.3">
@@ -21382,7 +21382,7 @@
         <v>2189</v>
       </c>
       <c r="G1092">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1093" spans="1:7" x14ac:dyDescent="0.3">
@@ -21536,7 +21536,7 @@
         <v>2211</v>
       </c>
       <c r="G1103">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1104" spans="1:7" x14ac:dyDescent="0.3">
@@ -21606,7 +21606,7 @@
         <v>2218</v>
       </c>
       <c r="G1108">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1109" spans="1:7" x14ac:dyDescent="0.3">
@@ -22026,7 +22026,7 @@
         <v>2273</v>
       </c>
       <c r="G1138">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1139" spans="1:7" x14ac:dyDescent="0.3">
@@ -22096,7 +22096,7 @@
         <v>2281</v>
       </c>
       <c r="G1143">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1144" spans="1:7" x14ac:dyDescent="0.3">
@@ -22110,7 +22110,7 @@
         <v>2282</v>
       </c>
       <c r="G1144">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1145" spans="1:7" x14ac:dyDescent="0.3">
@@ -22208,7 +22208,7 @@
         <v>2295</v>
       </c>
       <c r="G1151">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1152" spans="1:7" x14ac:dyDescent="0.3">
@@ -22278,7 +22278,7 @@
         <v>2304</v>
       </c>
       <c r="G1156">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1157" spans="1:7" x14ac:dyDescent="0.3">
@@ -22306,7 +22306,7 @@
         <v>2308</v>
       </c>
       <c r="G1158">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1159" spans="1:7" x14ac:dyDescent="0.3">
@@ -22348,7 +22348,7 @@
         <v>2318</v>
       </c>
       <c r="G1161">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1162" spans="1:7" x14ac:dyDescent="0.3">
@@ -22404,7 +22404,7 @@
         <v>2328</v>
       </c>
       <c r="G1165">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1166" spans="1:7" x14ac:dyDescent="0.3">
@@ -22572,7 +22572,7 @@
         <v>2350</v>
       </c>
       <c r="G1177">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1178" spans="1:7" x14ac:dyDescent="0.3">
@@ -22586,7 +22586,7 @@
         <v>2354</v>
       </c>
       <c r="G1178">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1179" spans="1:7" x14ac:dyDescent="0.3">
@@ -22600,7 +22600,7 @@
         <v>2355</v>
       </c>
       <c r="G1179">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1180" spans="1:7" x14ac:dyDescent="0.3">
@@ -22642,7 +22642,7 @@
         <v>2358</v>
       </c>
       <c r="G1182">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1183" spans="1:7" x14ac:dyDescent="0.3">
@@ -22684,7 +22684,7 @@
         <v>2364</v>
       </c>
       <c r="G1185">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1186" spans="1:7" x14ac:dyDescent="0.3">
@@ -22754,7 +22754,7 @@
         <v>2377</v>
       </c>
       <c r="G1190">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1191" spans="1:7" x14ac:dyDescent="0.3">
@@ -23146,7 +23146,7 @@
         <v>2431</v>
       </c>
       <c r="G1218">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1219" spans="1:7" x14ac:dyDescent="0.3">
@@ -23230,7 +23230,7 @@
         <v>2447</v>
       </c>
       <c r="G1224">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1225" spans="1:7" x14ac:dyDescent="0.3">
@@ -23244,7 +23244,7 @@
         <v>2448</v>
       </c>
       <c r="G1225">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1226" spans="1:7" x14ac:dyDescent="0.3">
@@ -23286,7 +23286,7 @@
         <v>2460</v>
       </c>
       <c r="G1228">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1229" spans="1:7" x14ac:dyDescent="0.3">
@@ -23314,7 +23314,7 @@
         <v>2464</v>
       </c>
       <c r="G1230">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1231" spans="1:7" x14ac:dyDescent="0.3">
@@ -23342,7 +23342,7 @@
         <v>2466</v>
       </c>
       <c r="G1232">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1233" spans="1:7" x14ac:dyDescent="0.3">
@@ -23384,7 +23384,7 @@
         <v>2472</v>
       </c>
       <c r="G1235">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1236" spans="1:7" x14ac:dyDescent="0.3">
@@ -23426,7 +23426,7 @@
         <v>2478</v>
       </c>
       <c r="G1238">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1239" spans="1:7" x14ac:dyDescent="0.3">
@@ -23552,7 +23552,7 @@
         <v>2494</v>
       </c>
       <c r="G1247">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1248" spans="1:7" x14ac:dyDescent="0.3">
@@ -23566,7 +23566,7 @@
         <v>2496</v>
       </c>
       <c r="G1248">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1249" spans="1:7" x14ac:dyDescent="0.3">
@@ -23580,7 +23580,7 @@
         <v>2498</v>
       </c>
       <c r="G1249">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1250" spans="1:7" x14ac:dyDescent="0.3">
@@ -23734,7 +23734,7 @@
         <v>2519</v>
       </c>
       <c r="G1260">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1261" spans="1:7" x14ac:dyDescent="0.3">
@@ -23818,7 +23818,7 @@
         <v>2529</v>
       </c>
       <c r="G1266">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1267" spans="1:7" x14ac:dyDescent="0.3">
@@ -23874,7 +23874,7 @@
         <v>2542</v>
       </c>
       <c r="G1270">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1271" spans="1:7" x14ac:dyDescent="0.3">
@@ -23902,7 +23902,7 @@
         <v>2545</v>
       </c>
       <c r="G1272">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1273" spans="1:7" x14ac:dyDescent="0.3">
@@ -23930,7 +23930,7 @@
         <v>2548</v>
       </c>
       <c r="G1274">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1275" spans="1:7" x14ac:dyDescent="0.3">
@@ -23972,7 +23972,7 @@
         <v>2554</v>
       </c>
       <c r="G1277">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1278" spans="1:7" x14ac:dyDescent="0.3">
@@ -24056,7 +24056,7 @@
         <v>2575</v>
       </c>
       <c r="G1283">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1284" spans="1:7" x14ac:dyDescent="0.3">
@@ -24084,7 +24084,7 @@
         <v>2580</v>
       </c>
       <c r="G1285">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1286" spans="1:7" x14ac:dyDescent="0.3">
@@ -24168,7 +24168,7 @@
         <v>2593</v>
       </c>
       <c r="G1291">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1292" spans="1:7" x14ac:dyDescent="0.3">
@@ -24210,7 +24210,7 @@
         <v>2601</v>
       </c>
       <c r="G1294">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1295" spans="1:7" x14ac:dyDescent="0.3">
@@ -24294,7 +24294,7 @@
         <v>2609</v>
       </c>
       <c r="G1300">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1301" spans="1:7" x14ac:dyDescent="0.3">
@@ -24336,7 +24336,7 @@
         <v>2618</v>
       </c>
       <c r="G1303">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1304" spans="1:7" x14ac:dyDescent="0.3">
@@ -24504,7 +24504,7 @@
         <v>2641</v>
       </c>
       <c r="G1315">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1316" spans="1:7" x14ac:dyDescent="0.3">
@@ -24630,7 +24630,7 @@
         <v>2655</v>
       </c>
       <c r="G1324">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1325" spans="1:7" x14ac:dyDescent="0.3">
@@ -24714,7 +24714,7 @@
         <v>2669</v>
       </c>
       <c r="G1330">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1331" spans="1:7" x14ac:dyDescent="0.3">
@@ -24742,7 +24742,7 @@
         <v>2671</v>
       </c>
       <c r="G1332">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1333" spans="1:7" x14ac:dyDescent="0.3">
@@ -24784,7 +24784,7 @@
         <v>2677</v>
       </c>
       <c r="G1335">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1336" spans="1:7" x14ac:dyDescent="0.3">
@@ -24812,7 +24812,7 @@
         <v>2679</v>
       </c>
       <c r="G1337">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1338" spans="1:7" x14ac:dyDescent="0.3">
@@ -24826,7 +24826,7 @@
         <v>2681</v>
       </c>
       <c r="G1338">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1339" spans="1:7" x14ac:dyDescent="0.3">
@@ -24854,7 +24854,7 @@
         <v>2683</v>
       </c>
       <c r="G1340">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1341" spans="1:7" x14ac:dyDescent="0.3">
@@ -24924,7 +24924,7 @@
         <v>2699</v>
       </c>
       <c r="G1345">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1346" spans="1:7" x14ac:dyDescent="0.3">
@@ -24980,7 +24980,7 @@
         <v>2706</v>
       </c>
       <c r="G1349">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1350" spans="1:7" x14ac:dyDescent="0.3">
@@ -25050,7 +25050,7 @@
         <v>2714</v>
       </c>
       <c r="G1354">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1355" spans="1:7" x14ac:dyDescent="0.3">
@@ -25078,7 +25078,7 @@
         <v>2718</v>
       </c>
       <c r="G1356">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1357" spans="1:7" x14ac:dyDescent="0.3">
@@ -25134,7 +25134,7 @@
         <v>2725</v>
       </c>
       <c r="G1360">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1361" spans="1:7" x14ac:dyDescent="0.3">
@@ -25176,7 +25176,7 @@
         <v>2728</v>
       </c>
       <c r="G1363">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1364" spans="1:7" x14ac:dyDescent="0.3">
@@ -25190,7 +25190,7 @@
         <v>2730</v>
       </c>
       <c r="G1364">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1365" spans="1:7" x14ac:dyDescent="0.3">
@@ -25218,7 +25218,7 @@
         <v>2739</v>
       </c>
       <c r="G1366">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1367" spans="1:7" x14ac:dyDescent="0.3">
@@ -25260,7 +25260,7 @@
         <v>2744</v>
       </c>
       <c r="G1369">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1370" spans="1:7" x14ac:dyDescent="0.3">
@@ -25302,7 +25302,7 @@
         <v>2748</v>
       </c>
       <c r="G1372">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1373" spans="1:7" x14ac:dyDescent="0.3">
@@ -25344,7 +25344,7 @@
         <v>2753</v>
       </c>
       <c r="G1375">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1376" spans="1:7" x14ac:dyDescent="0.3">
@@ -25358,7 +25358,7 @@
         <v>2755</v>
       </c>
       <c r="G1376">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1377" spans="1:7" x14ac:dyDescent="0.3">
@@ -25386,7 +25386,7 @@
         <v>2759</v>
       </c>
       <c r="G1378">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1379" spans="1:7" x14ac:dyDescent="0.3">
@@ -25540,7 +25540,7 @@
         <v>2775</v>
       </c>
       <c r="G1389">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1390" spans="1:7" x14ac:dyDescent="0.3">
@@ -25708,7 +25708,7 @@
         <v>2795</v>
       </c>
       <c r="G1401">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1402" spans="1:7" x14ac:dyDescent="0.3">
@@ -25764,7 +25764,7 @@
         <v>2802</v>
       </c>
       <c r="G1405">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1406" spans="1:7" x14ac:dyDescent="0.3">
@@ -25778,7 +25778,7 @@
         <v>2803</v>
       </c>
       <c r="G1406">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1407" spans="1:7" x14ac:dyDescent="0.3">
@@ -25806,7 +25806,7 @@
         <v>2806</v>
       </c>
       <c r="G1408">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1409" spans="1:7" x14ac:dyDescent="0.3">
@@ -25834,7 +25834,7 @@
         <v>2808</v>
       </c>
       <c r="G1410">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1411" spans="1:7" x14ac:dyDescent="0.3">
@@ -25876,7 +25876,7 @@
         <v>2813</v>
       </c>
       <c r="G1413">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1414" spans="1:7" x14ac:dyDescent="0.3">
@@ -25890,7 +25890,7 @@
         <v>2817</v>
       </c>
       <c r="G1414">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1415" spans="1:7" x14ac:dyDescent="0.3">
@@ -26002,7 +26002,7 @@
         <v>2829</v>
       </c>
       <c r="G1422">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1423" spans="1:7" x14ac:dyDescent="0.3">
@@ -26016,7 +26016,7 @@
         <v>2830</v>
       </c>
       <c r="G1423">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1424" spans="1:7" x14ac:dyDescent="0.3">
@@ -26030,7 +26030,7 @@
         <v>2835</v>
       </c>
       <c r="G1424">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1425" spans="1:7" x14ac:dyDescent="0.3">
@@ -26044,7 +26044,7 @@
         <v>2838</v>
       </c>
       <c r="G1425">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1426" spans="1:7" x14ac:dyDescent="0.3">
@@ -26058,7 +26058,7 @@
         <v>2839</v>
       </c>
       <c r="G1426">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1427" spans="1:7" x14ac:dyDescent="0.3">
@@ -26114,7 +26114,7 @@
         <v>2849</v>
       </c>
       <c r="G1430">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1431" spans="1:7" x14ac:dyDescent="0.3">
@@ -26142,7 +26142,7 @@
         <v>2851</v>
       </c>
       <c r="G1432">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1433" spans="1:7" x14ac:dyDescent="0.3">
@@ -26198,7 +26198,7 @@
         <v>2858</v>
       </c>
       <c r="G1436">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1437" spans="1:7" x14ac:dyDescent="0.3">
@@ -26268,7 +26268,7 @@
         <v>2870</v>
       </c>
       <c r="G1441">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1442" spans="1:7" x14ac:dyDescent="0.3">
@@ -26324,7 +26324,7 @@
         <v>2878</v>
       </c>
       <c r="G1445">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1446" spans="1:7" x14ac:dyDescent="0.3">
@@ -26338,7 +26338,7 @@
         <v>2881</v>
       </c>
       <c r="G1446">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1447" spans="1:7" x14ac:dyDescent="0.3">
@@ -26352,7 +26352,7 @@
         <v>2882</v>
       </c>
       <c r="G1447">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1448" spans="1:7" x14ac:dyDescent="0.3">
@@ -26436,7 +26436,7 @@
         <v>2901</v>
       </c>
       <c r="G1453">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1454" spans="1:7" x14ac:dyDescent="0.3">
@@ -26520,7 +26520,7 @@
         <v>2910</v>
       </c>
       <c r="G1459">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1460" spans="1:7" x14ac:dyDescent="0.3">
@@ -26576,7 +26576,7 @@
         <v>2918</v>
       </c>
       <c r="G1463">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1464" spans="1:7" x14ac:dyDescent="0.3">
@@ -26618,7 +26618,7 @@
         <v>2923</v>
       </c>
       <c r="G1466">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1467" spans="1:7" x14ac:dyDescent="0.3">
@@ -26688,7 +26688,7 @@
         <v>2935</v>
       </c>
       <c r="G1471">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1472" spans="1:7" x14ac:dyDescent="0.3">
@@ -26716,7 +26716,7 @@
         <v>2940</v>
       </c>
       <c r="G1473">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1474" spans="1:7" x14ac:dyDescent="0.3">
@@ -26730,7 +26730,7 @@
         <v>2943</v>
       </c>
       <c r="G1474">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1475" spans="1:7" x14ac:dyDescent="0.3">
@@ -26758,7 +26758,7 @@
         <v>2948</v>
       </c>
       <c r="G1476">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1477" spans="1:7" x14ac:dyDescent="0.3">
@@ -26772,7 +26772,7 @@
         <v>2949</v>
       </c>
       <c r="G1477">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1478" spans="1:7" x14ac:dyDescent="0.3">
@@ -26786,7 +26786,7 @@
         <v>2950</v>
       </c>
       <c r="G1478">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1479" spans="1:7" x14ac:dyDescent="0.3">
@@ -26828,7 +26828,7 @@
         <v>2957</v>
       </c>
       <c r="G1481">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1482" spans="1:7" x14ac:dyDescent="0.3">
@@ -26898,7 +26898,7 @@
         <v>2967</v>
       </c>
       <c r="G1486">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1487" spans="1:7" x14ac:dyDescent="0.3">
@@ -26982,7 +26982,7 @@
         <v>2979</v>
       </c>
       <c r="G1492">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1493" spans="1:7" x14ac:dyDescent="0.3">
@@ -27094,7 +27094,7 @@
         <v>2994</v>
       </c>
       <c r="G1500">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1501" spans="1:7" x14ac:dyDescent="0.3">
@@ -27136,7 +27136,7 @@
         <v>3000</v>
       </c>
       <c r="G1503">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1504" spans="1:7" x14ac:dyDescent="0.3">
@@ -27192,7 +27192,7 @@
         <v>3015</v>
       </c>
       <c r="G1507">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1508" spans="1:7" x14ac:dyDescent="0.3">
@@ -27234,7 +27234,7 @@
         <v>3021</v>
       </c>
       <c r="G1510">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1511" spans="1:7" x14ac:dyDescent="0.3">
@@ -27332,7 +27332,7 @@
         <v>3036</v>
       </c>
       <c r="G1517">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1518" spans="1:7" x14ac:dyDescent="0.3">
@@ -27346,7 +27346,7 @@
         <v>3037</v>
       </c>
       <c r="G1518">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1519" spans="1:7" x14ac:dyDescent="0.3">
@@ -27388,7 +27388,7 @@
         <v>3044</v>
       </c>
       <c r="G1521">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1522" spans="1:7" x14ac:dyDescent="0.3">
@@ -27402,7 +27402,7 @@
         <v>3045</v>
       </c>
       <c r="G1522">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1523" spans="1:7" x14ac:dyDescent="0.3">
@@ -27430,7 +27430,7 @@
         <v>3047</v>
       </c>
       <c r="G1524">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1525" spans="1:7" x14ac:dyDescent="0.3">
@@ -27444,7 +27444,7 @@
         <v>3049</v>
       </c>
       <c r="G1525">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1526" spans="1:7" x14ac:dyDescent="0.3">
@@ -27472,7 +27472,7 @@
         <v>3055</v>
       </c>
       <c r="G1527">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1528" spans="1:7" x14ac:dyDescent="0.3">
@@ -27486,7 +27486,7 @@
         <v>3057</v>
       </c>
       <c r="G1528">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1529" spans="1:7" x14ac:dyDescent="0.3">
@@ -27640,7 +27640,7 @@
         <v>3079</v>
       </c>
       <c r="G1539">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1540" spans="1:7" x14ac:dyDescent="0.3">
@@ -27682,7 +27682,7 @@
         <v>3083</v>
       </c>
       <c r="G1542">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1543" spans="1:7" x14ac:dyDescent="0.3">
@@ -27738,7 +27738,7 @@
         <v>3089</v>
       </c>
       <c r="G1546">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/compareOP.xlsx
+++ b/compareOP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DUT\Ki_2\Edge_AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{165622EA-66A6-4044-95BD-133930B0398A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46B265C-6CA4-45B3-90F6-AA3327A06C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{56603411-7B59-498E-88B9-7E9448248F05}"/>
   </bookViews>
@@ -1001,18 +1001,18 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2" s="6" t="str">
         <f>IF(B2=G2, "T", "F")</f>
-        <v>F</v>
+        <v>T</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="L2" s="4">
         <f>COUNTIF(I2:I1001, "T")</f>
-        <v>771</v>
+        <v>794</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="L3" s="4">
         <f>L2/1000*100</f>
-        <v>77.100000000000009</v>
+        <v>79.400000000000006</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -1596,11 +1596,11 @@
         <v>67</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
@@ -1845,7 +1845,7 @@
         <v>88</v>
       </c>
       <c r="G40">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I40" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1940,11 +1940,11 @@
         <v>100</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I45" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
@@ -2054,7 +2054,7 @@
         <v>111</v>
       </c>
       <c r="G51">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I51" s="6" t="str">
         <f t="shared" si="0"/>
@@ -2358,11 +2358,11 @@
         <v>149</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I67" s="6" t="str">
         <f t="shared" ref="I67:I130" si="1">IF(B67=G67, "T", "F")</f>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
@@ -2472,11 +2472,11 @@
         <v>158</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I73" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
@@ -2529,11 +2529,11 @@
         <v>166</v>
       </c>
       <c r="G76">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I76" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
@@ -2567,11 +2567,11 @@
         <v>170</v>
       </c>
       <c r="G78">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I78" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
@@ -2700,11 +2700,11 @@
         <v>179</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
@@ -2776,11 +2776,11 @@
         <v>188</v>
       </c>
       <c r="G89">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I89" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.3">
@@ -2890,11 +2890,11 @@
         <v>198</v>
       </c>
       <c r="G95">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I95" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
@@ -2985,7 +2985,7 @@
         <v>208</v>
       </c>
       <c r="G100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I100" s="6" t="str">
         <f t="shared" si="1"/>
@@ -3080,11 +3080,11 @@
         <v>213</v>
       </c>
       <c r="G105">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I105" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
@@ -3118,11 +3118,11 @@
         <v>219</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I107" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
@@ -3232,7 +3232,7 @@
         <v>229</v>
       </c>
       <c r="G113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I113" s="6" t="str">
         <f t="shared" si="1"/>
@@ -3289,11 +3289,11 @@
         <v>233</v>
       </c>
       <c r="G116">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I116" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
@@ -3517,11 +3517,11 @@
         <v>257</v>
       </c>
       <c r="G128">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I128" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
@@ -3574,11 +3574,11 @@
         <v>263</v>
       </c>
       <c r="G131">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I131" s="6" t="str">
         <f t="shared" ref="I131:I194" si="2">IF(B131=G131, "T", "F")</f>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
@@ -3688,11 +3688,11 @@
         <v>275</v>
       </c>
       <c r="G137">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I137" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.3">
@@ -3707,11 +3707,11 @@
         <v>276</v>
       </c>
       <c r="G138">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I138" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
@@ -3745,11 +3745,11 @@
         <v>278</v>
       </c>
       <c r="G140">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I140" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.3">
@@ -3840,11 +3840,11 @@
         <v>286</v>
       </c>
       <c r="G145">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I145" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.3">
@@ -3878,11 +3878,11 @@
         <v>288</v>
       </c>
       <c r="G147">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I147" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
@@ -3916,7 +3916,7 @@
         <v>290</v>
       </c>
       <c r="G149">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I149" s="6" t="str">
         <f t="shared" si="2"/>
@@ -3954,7 +3954,7 @@
         <v>294</v>
       </c>
       <c r="G151">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I151" s="6" t="str">
         <f t="shared" si="2"/>
@@ -3992,7 +3992,7 @@
         <v>297</v>
       </c>
       <c r="G153">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I153" s="6" t="str">
         <f t="shared" si="2"/>
@@ -4087,7 +4087,7 @@
         <v>304</v>
       </c>
       <c r="G158">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I158" s="6" t="str">
         <f t="shared" si="2"/>
@@ -4182,11 +4182,11 @@
         <v>309</v>
       </c>
       <c r="G163">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I163" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
@@ -4220,7 +4220,7 @@
         <v>313</v>
       </c>
       <c r="G165">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I165" s="6" t="str">
         <f t="shared" si="2"/>
@@ -4277,11 +4277,11 @@
         <v>316</v>
       </c>
       <c r="G168">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I168" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.3">
@@ -4391,11 +4391,11 @@
         <v>331</v>
       </c>
       <c r="G174">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I174" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.3">
@@ -4410,7 +4410,7 @@
         <v>332</v>
       </c>
       <c r="G175">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I175" s="6" t="str">
         <f t="shared" si="2"/>
@@ -4600,11 +4600,11 @@
         <v>351</v>
       </c>
       <c r="G185">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I185" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.3">
@@ -4638,11 +4638,11 @@
         <v>353</v>
       </c>
       <c r="G187">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I187" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.3">
@@ -4809,7 +4809,7 @@
         <v>370</v>
       </c>
       <c r="G196">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I196" s="6" t="str">
         <f t="shared" si="3"/>
@@ -4866,11 +4866,11 @@
         <v>380</v>
       </c>
       <c r="G199">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I199" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.3">
@@ -4980,11 +4980,11 @@
         <v>393</v>
       </c>
       <c r="G205">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I205" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.3">
@@ -5056,7 +5056,7 @@
         <v>407</v>
       </c>
       <c r="G209">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I209" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5246,7 +5246,7 @@
         <v>422</v>
       </c>
       <c r="G219">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I219" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5284,11 +5284,11 @@
         <v>424</v>
       </c>
       <c r="G221">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I221" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.3">
@@ -5303,11 +5303,11 @@
         <v>425</v>
       </c>
       <c r="G222">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I222" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.3">
@@ -5379,11 +5379,11 @@
         <v>430</v>
       </c>
       <c r="G226">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I226" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.3">
@@ -5417,7 +5417,7 @@
         <v>433</v>
       </c>
       <c r="G228">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I228" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5474,7 +5474,7 @@
         <v>438</v>
       </c>
       <c r="G231">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I231" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5569,7 +5569,7 @@
         <v>445</v>
       </c>
       <c r="G236">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I236" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5683,11 +5683,11 @@
         <v>458</v>
       </c>
       <c r="G242">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I242" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.3">
@@ -5816,11 +5816,11 @@
         <v>472</v>
       </c>
       <c r="G249">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I249" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.3">
@@ -5854,11 +5854,11 @@
         <v>479</v>
       </c>
       <c r="G251">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I251" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.3">
@@ -5987,11 +5987,11 @@
         <v>491</v>
       </c>
       <c r="G258">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I258" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.3">
@@ -6006,11 +6006,11 @@
         <v>494</v>
       </c>
       <c r="G259">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I259" s="6" t="str">
         <f t="shared" ref="I259:I322" si="4">IF(B259=G259, "T", "F")</f>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.3">
@@ -6101,7 +6101,7 @@
         <v>503</v>
       </c>
       <c r="G264">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I264" s="6" t="str">
         <f t="shared" si="4"/>
@@ -6177,11 +6177,11 @@
         <v>509</v>
       </c>
       <c r="G268">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I268" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.3">
@@ -6196,7 +6196,7 @@
         <v>511</v>
       </c>
       <c r="G269">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I269" s="6" t="str">
         <f t="shared" si="4"/>
@@ -6405,11 +6405,11 @@
         <v>532</v>
       </c>
       <c r="G280">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I280" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.3">
@@ -6462,11 +6462,11 @@
         <v>535</v>
       </c>
       <c r="G283">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I283" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.3">
@@ -6538,11 +6538,11 @@
         <v>544</v>
       </c>
       <c r="G287">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I287" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.3">
@@ -6709,11 +6709,11 @@
         <v>557</v>
       </c>
       <c r="G296">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I296" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.3">
@@ -6728,11 +6728,11 @@
         <v>560</v>
       </c>
       <c r="G297">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I297" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.3">
@@ -6785,11 +6785,11 @@
         <v>565</v>
       </c>
       <c r="G300">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I300" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.3">
@@ -6956,11 +6956,11 @@
         <v>582</v>
       </c>
       <c r="G309">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I309" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.3">
@@ -7032,7 +7032,7 @@
         <v>590</v>
       </c>
       <c r="G313">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I313" s="6" t="str">
         <f t="shared" si="4"/>
@@ -7108,11 +7108,11 @@
         <v>597</v>
       </c>
       <c r="G317">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I317" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.3">
@@ -7374,11 +7374,11 @@
         <v>620</v>
       </c>
       <c r="G331">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I331" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.3">
@@ -7488,11 +7488,11 @@
         <v>636</v>
       </c>
       <c r="G337">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I337" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.3">
@@ -7526,7 +7526,7 @@
         <v>642</v>
       </c>
       <c r="G339">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I339" s="6" t="str">
         <f t="shared" si="5"/>
@@ -7564,11 +7564,11 @@
         <v>644</v>
       </c>
       <c r="G341">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I341" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.3">
@@ -7602,11 +7602,11 @@
         <v>649</v>
       </c>
       <c r="G343">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I343" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.3">
@@ -7659,7 +7659,7 @@
         <v>654</v>
       </c>
       <c r="G346">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I346" s="6" t="str">
         <f t="shared" si="5"/>
@@ -7678,7 +7678,7 @@
         <v>655</v>
       </c>
       <c r="G347">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I347" s="6" t="str">
         <f t="shared" si="5"/>
@@ -7754,7 +7754,7 @@
         <v>668</v>
       </c>
       <c r="G351">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I351" s="6" t="str">
         <f t="shared" si="5"/>
@@ -7792,11 +7792,11 @@
         <v>672</v>
       </c>
       <c r="G353">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I353" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.3">
@@ -7830,11 +7830,11 @@
         <v>676</v>
       </c>
       <c r="G355">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I355" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.3">
@@ -7944,7 +7944,7 @@
         <v>685</v>
       </c>
       <c r="G361">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I361" s="6" t="str">
         <f t="shared" si="5"/>
@@ -8191,11 +8191,11 @@
         <v>718</v>
       </c>
       <c r="G374">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I374" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.3">
@@ -8248,7 +8248,7 @@
         <v>729</v>
       </c>
       <c r="G377">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I377" s="6" t="str">
         <f t="shared" si="5"/>
@@ -8533,11 +8533,11 @@
         <v>761</v>
       </c>
       <c r="G392">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I392" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.3">
@@ -8552,7 +8552,7 @@
         <v>764</v>
       </c>
       <c r="G393">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I393" s="6" t="str">
         <f t="shared" si="6"/>
@@ -8761,7 +8761,7 @@
         <v>787</v>
       </c>
       <c r="G404">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I404" s="6" t="str">
         <f t="shared" si="6"/>
@@ -8894,11 +8894,11 @@
         <v>800</v>
       </c>
       <c r="G411">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I411" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.3">
@@ -8970,11 +8970,11 @@
         <v>805</v>
       </c>
       <c r="G415">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I415" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.3">
@@ -8989,7 +8989,7 @@
         <v>807</v>
       </c>
       <c r="G416">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I416" s="6" t="str">
         <f t="shared" si="6"/>
@@ -9084,11 +9084,11 @@
         <v>812</v>
       </c>
       <c r="G421">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I421" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="422" spans="1:9" x14ac:dyDescent="0.3">
@@ -9141,11 +9141,11 @@
         <v>821</v>
       </c>
       <c r="G424">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I424" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="425" spans="1:9" x14ac:dyDescent="0.3">
@@ -9217,11 +9217,11 @@
         <v>836</v>
       </c>
       <c r="G428">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I428" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.3">
@@ -9331,11 +9331,11 @@
         <v>843</v>
       </c>
       <c r="G434">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I434" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="435" spans="1:9" x14ac:dyDescent="0.3">
@@ -9350,11 +9350,11 @@
         <v>844</v>
       </c>
       <c r="G435">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I435" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="436" spans="1:9" x14ac:dyDescent="0.3">
@@ -9616,11 +9616,11 @@
         <v>871</v>
       </c>
       <c r="G449">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I449" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="450" spans="1:9" x14ac:dyDescent="0.3">
@@ -9673,11 +9673,11 @@
         <v>879</v>
       </c>
       <c r="G452">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I452" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="453" spans="1:9" x14ac:dyDescent="0.3">
@@ -9768,11 +9768,11 @@
         <v>887</v>
       </c>
       <c r="G457">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I457" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="458" spans="1:9" x14ac:dyDescent="0.3">
@@ -9844,7 +9844,7 @@
         <v>891</v>
       </c>
       <c r="G461">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I461" s="6" t="str">
         <f t="shared" si="7"/>
@@ -9882,7 +9882,7 @@
         <v>898</v>
       </c>
       <c r="G463">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I463" s="6" t="str">
         <f t="shared" si="7"/>
@@ -9958,11 +9958,11 @@
         <v>906</v>
       </c>
       <c r="G467">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I467" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="468" spans="1:9" x14ac:dyDescent="0.3">
@@ -10148,11 +10148,11 @@
         <v>926</v>
       </c>
       <c r="G477">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I477" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="478" spans="1:9" x14ac:dyDescent="0.3">
@@ -10205,7 +10205,7 @@
         <v>930</v>
       </c>
       <c r="G480">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I480" s="6" t="str">
         <f t="shared" si="7"/>
@@ -10585,7 +10585,7 @@
         <v>973</v>
       </c>
       <c r="G500">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I500" s="6" t="str">
         <f t="shared" si="7"/>
@@ -10718,7 +10718,7 @@
         <v>993</v>
       </c>
       <c r="G507">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I507" s="6" t="str">
         <f t="shared" si="7"/>
@@ -10775,11 +10775,11 @@
         <v>1000</v>
       </c>
       <c r="G510">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I510" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="511" spans="1:9" x14ac:dyDescent="0.3">
@@ -10946,11 +10946,11 @@
         <v>1017</v>
       </c>
       <c r="G519">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I519" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="520" spans="1:9" x14ac:dyDescent="0.3">
@@ -11288,11 +11288,11 @@
         <v>1053</v>
       </c>
       <c r="G537">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I537" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="538" spans="1:9" x14ac:dyDescent="0.3">
@@ -11383,7 +11383,7 @@
         <v>1058</v>
       </c>
       <c r="G542">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I542" s="6" t="str">
         <f t="shared" si="8"/>
@@ -11649,7 +11649,7 @@
         <v>1089</v>
       </c>
       <c r="G556">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I556" s="6" t="str">
         <f t="shared" si="8"/>
@@ -11915,7 +11915,7 @@
         <v>1110</v>
       </c>
       <c r="G570">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I570" s="6" t="str">
         <f t="shared" si="8"/>
@@ -11934,11 +11934,11 @@
         <v>1113</v>
       </c>
       <c r="G571">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I571" s="6" t="str">
         <f t="shared" si="8"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="572" spans="1:9" x14ac:dyDescent="0.3">
@@ -12029,7 +12029,7 @@
         <v>1124</v>
       </c>
       <c r="G576">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I576" s="6" t="str">
         <f t="shared" si="8"/>
@@ -12181,11 +12181,11 @@
         <v>1146</v>
       </c>
       <c r="G584">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I584" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="585" spans="1:9" x14ac:dyDescent="0.3">
@@ -12314,11 +12314,11 @@
         <v>1173</v>
       </c>
       <c r="G591">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I591" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="592" spans="1:9" x14ac:dyDescent="0.3">
@@ -12352,11 +12352,11 @@
         <v>1177</v>
       </c>
       <c r="G593">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I593" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="594" spans="1:9" x14ac:dyDescent="0.3">
@@ -12390,11 +12390,11 @@
         <v>1179</v>
       </c>
       <c r="G595">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I595" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="596" spans="1:9" x14ac:dyDescent="0.3">
@@ -12409,11 +12409,11 @@
         <v>1185</v>
       </c>
       <c r="G596">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I596" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="597" spans="1:9" x14ac:dyDescent="0.3">
@@ -12561,11 +12561,11 @@
         <v>1196</v>
       </c>
       <c r="G604">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I604" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="605" spans="1:9" x14ac:dyDescent="0.3">
@@ -12732,11 +12732,11 @@
         <v>1216</v>
       </c>
       <c r="G613">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I613" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="614" spans="1:9" x14ac:dyDescent="0.3">
@@ -12884,7 +12884,7 @@
         <v>1230</v>
       </c>
       <c r="G621">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I621" s="6" t="str">
         <f t="shared" si="9"/>
@@ -12903,11 +12903,11 @@
         <v>1231</v>
       </c>
       <c r="G622">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I622" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="623" spans="1:9" x14ac:dyDescent="0.3">
@@ -13017,11 +13017,11 @@
         <v>1239</v>
       </c>
       <c r="G628">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I628" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="629" spans="1:9" x14ac:dyDescent="0.3">
@@ -13093,11 +13093,11 @@
         <v>1247</v>
       </c>
       <c r="G632">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I632" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="633" spans="1:9" x14ac:dyDescent="0.3">
@@ -13264,7 +13264,7 @@
         <v>1265</v>
       </c>
       <c r="G641">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I641" s="6" t="str">
         <f t="shared" si="9"/>
@@ -13378,11 +13378,11 @@
         <v>1273</v>
       </c>
       <c r="G647">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I647" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="648" spans="1:9" x14ac:dyDescent="0.3">
@@ -13416,11 +13416,11 @@
         <v>1281</v>
       </c>
       <c r="G649">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I649" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="650" spans="1:9" x14ac:dyDescent="0.3">
@@ -13511,11 +13511,11 @@
         <v>1289</v>
       </c>
       <c r="G654">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I654" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="655" spans="1:9" x14ac:dyDescent="0.3">
@@ -13644,7 +13644,7 @@
         <v>1307</v>
       </c>
       <c r="G661">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I661" s="6" t="str">
         <f t="shared" si="10"/>
@@ -13663,11 +13663,11 @@
         <v>1309</v>
       </c>
       <c r="G662">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I662" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="663" spans="1:9" x14ac:dyDescent="0.3">
@@ -13758,7 +13758,7 @@
         <v>1321</v>
       </c>
       <c r="G667">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I667" s="6" t="str">
         <f t="shared" si="10"/>
@@ -13777,11 +13777,11 @@
         <v>1322</v>
       </c>
       <c r="G668">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I668" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="669" spans="1:9" x14ac:dyDescent="0.3">
@@ -13853,7 +13853,7 @@
         <v>1334</v>
       </c>
       <c r="G672">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I672" s="6" t="str">
         <f t="shared" si="10"/>
@@ -13891,11 +13891,11 @@
         <v>1337</v>
       </c>
       <c r="G674">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I674" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="675" spans="1:9" x14ac:dyDescent="0.3">
@@ -14195,11 +14195,11 @@
         <v>1364</v>
       </c>
       <c r="G690">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I690" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="691" spans="1:9" x14ac:dyDescent="0.3">
@@ -14328,11 +14328,11 @@
         <v>1376</v>
       </c>
       <c r="G697">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I697" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="698" spans="1:9" x14ac:dyDescent="0.3">
@@ -14423,11 +14423,11 @@
         <v>1391</v>
       </c>
       <c r="G702">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I702" s="6" t="str">
         <f t="shared" si="10"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="703" spans="1:9" x14ac:dyDescent="0.3">
@@ -14575,7 +14575,7 @@
         <v>1405</v>
       </c>
       <c r="G710">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I710" s="6" t="str">
         <f t="shared" si="11"/>
@@ -14613,11 +14613,11 @@
         <v>1407</v>
       </c>
       <c r="G712">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I712" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="713" spans="1:9" x14ac:dyDescent="0.3">
@@ -14784,11 +14784,11 @@
         <v>1423</v>
       </c>
       <c r="G721">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I721" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="722" spans="1:9" x14ac:dyDescent="0.3">
@@ -14822,11 +14822,11 @@
         <v>1426</v>
       </c>
       <c r="G723">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I723" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="724" spans="1:9" x14ac:dyDescent="0.3">
@@ -14898,11 +14898,11 @@
         <v>1432</v>
       </c>
       <c r="G727">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I727" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="728" spans="1:9" x14ac:dyDescent="0.3">
@@ -14955,11 +14955,11 @@
         <v>1437</v>
       </c>
       <c r="G730">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I730" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="731" spans="1:9" x14ac:dyDescent="0.3">
@@ -15050,7 +15050,7 @@
         <v>1450</v>
       </c>
       <c r="G735">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I735" s="6" t="str">
         <f t="shared" si="11"/>
@@ -15297,11 +15297,11 @@
         <v>1472</v>
       </c>
       <c r="G748">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I748" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="749" spans="1:9" x14ac:dyDescent="0.3">
@@ -15430,11 +15430,11 @@
         <v>1487</v>
       </c>
       <c r="G755">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I755" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="756" spans="1:9" x14ac:dyDescent="0.3">
@@ -15487,11 +15487,11 @@
         <v>1494</v>
       </c>
       <c r="G758">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I758" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="759" spans="1:9" x14ac:dyDescent="0.3">
@@ -15506,7 +15506,7 @@
         <v>1497</v>
       </c>
       <c r="G759">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I759" s="6" t="str">
         <f t="shared" si="11"/>
@@ -15639,7 +15639,7 @@
         <v>1509</v>
       </c>
       <c r="G766">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I766" s="6" t="str">
         <f t="shared" si="11"/>
@@ -15734,7 +15734,7 @@
         <v>1518</v>
       </c>
       <c r="G771">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I771" s="6" t="str">
         <f t="shared" ref="I771:I834" si="12">IF(B771=G771, "T", "F")</f>
@@ -15829,7 +15829,7 @@
         <v>1537</v>
       </c>
       <c r="G776">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I776" s="6" t="str">
         <f t="shared" si="12"/>
@@ -15848,7 +15848,7 @@
         <v>1538</v>
       </c>
       <c r="G777">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I777" s="6" t="str">
         <f t="shared" si="12"/>
@@ -16076,7 +16076,7 @@
         <v>1562</v>
       </c>
       <c r="G789">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I789" s="6" t="str">
         <f t="shared" si="12"/>
@@ -16095,11 +16095,11 @@
         <v>1563</v>
       </c>
       <c r="G790">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I790" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="791" spans="1:9" x14ac:dyDescent="0.3">
@@ -16133,11 +16133,11 @@
         <v>1566</v>
       </c>
       <c r="G792">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I792" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="793" spans="1:9" x14ac:dyDescent="0.3">
@@ -16323,7 +16323,7 @@
         <v>1583</v>
       </c>
       <c r="G802">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I802" s="6" t="str">
         <f t="shared" si="12"/>
@@ -16399,11 +16399,11 @@
         <v>1588</v>
       </c>
       <c r="G806">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I806" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="807" spans="1:9" x14ac:dyDescent="0.3">
@@ -16456,11 +16456,11 @@
         <v>1593</v>
       </c>
       <c r="G809">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I809" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="810" spans="1:9" x14ac:dyDescent="0.3">
@@ -16665,7 +16665,7 @@
         <v>1613</v>
       </c>
       <c r="G820">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I820" s="6" t="str">
         <f t="shared" si="12"/>
@@ -16684,11 +16684,11 @@
         <v>1614</v>
       </c>
       <c r="G821">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I821" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="822" spans="1:9" x14ac:dyDescent="0.3">
@@ -16722,11 +16722,11 @@
         <v>1618</v>
       </c>
       <c r="G823">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I823" s="6" t="str">
         <f t="shared" si="12"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="824" spans="1:9" x14ac:dyDescent="0.3">
@@ -16950,11 +16950,11 @@
         <v>1653</v>
       </c>
       <c r="G835">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I835" s="6" t="str">
         <f t="shared" ref="I835:I898" si="13">IF(B835=G835, "T", "F")</f>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="836" spans="1:9" x14ac:dyDescent="0.3">
@@ -17140,11 +17140,11 @@
         <v>1674</v>
       </c>
       <c r="G845">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I845" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="846" spans="1:9" x14ac:dyDescent="0.3">
@@ -17159,11 +17159,11 @@
         <v>1675</v>
       </c>
       <c r="G846">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I846" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="847" spans="1:9" x14ac:dyDescent="0.3">
@@ -17235,11 +17235,11 @@
         <v>1688</v>
       </c>
       <c r="G850">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I850" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="851" spans="1:9" x14ac:dyDescent="0.3">
@@ -17273,11 +17273,11 @@
         <v>1690</v>
       </c>
       <c r="G852">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I852" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="853" spans="1:9" x14ac:dyDescent="0.3">
@@ -17406,11 +17406,11 @@
         <v>1709</v>
       </c>
       <c r="G859">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I859" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="860" spans="1:9" x14ac:dyDescent="0.3">
@@ -17425,7 +17425,7 @@
         <v>1710</v>
       </c>
       <c r="G860">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I860" s="6" t="str">
         <f t="shared" si="13"/>
@@ -17539,11 +17539,11 @@
         <v>1718</v>
       </c>
       <c r="G866">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I866" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="867" spans="1:9" x14ac:dyDescent="0.3">
@@ -18071,7 +18071,7 @@
         <v>1765</v>
       </c>
       <c r="G894">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I894" s="6" t="str">
         <f t="shared" si="13"/>
@@ -18166,11 +18166,11 @@
         <v>1775</v>
       </c>
       <c r="G899">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I899" s="6" t="str">
         <f t="shared" ref="I899:I962" si="14">IF(B899=G899, "T", "F")</f>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="900" spans="1:9" x14ac:dyDescent="0.3">
@@ -18375,11 +18375,11 @@
         <v>1800</v>
       </c>
       <c r="G910">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I910" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="911" spans="1:9" x14ac:dyDescent="0.3">
@@ -18527,11 +18527,11 @@
         <v>1814</v>
       </c>
       <c r="G918">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I918" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="919" spans="1:9" x14ac:dyDescent="0.3">
@@ -18717,7 +18717,7 @@
         <v>1837</v>
       </c>
       <c r="G928">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I928" s="6" t="str">
         <f t="shared" si="14"/>
@@ -18755,7 +18755,7 @@
         <v>1840</v>
       </c>
       <c r="G930">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I930" s="6" t="str">
         <f t="shared" si="14"/>
@@ -18907,7 +18907,7 @@
         <v>1860</v>
       </c>
       <c r="G938">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I938" s="6" t="str">
         <f t="shared" si="14"/>
@@ -19021,7 +19021,7 @@
         <v>1868</v>
       </c>
       <c r="G944">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I944" s="6" t="str">
         <f t="shared" si="14"/>
@@ -19040,11 +19040,11 @@
         <v>1869</v>
       </c>
       <c r="G945">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I945" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="946" spans="1:9" x14ac:dyDescent="0.3">
@@ -19097,11 +19097,11 @@
         <v>1877</v>
       </c>
       <c r="G948">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I948" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="949" spans="1:9" x14ac:dyDescent="0.3">
@@ -19154,11 +19154,11 @@
         <v>1883</v>
       </c>
       <c r="G951">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I951" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="952" spans="1:9" x14ac:dyDescent="0.3">
@@ -19211,11 +19211,11 @@
         <v>1896</v>
       </c>
       <c r="G954">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I954" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="955" spans="1:9" x14ac:dyDescent="0.3">
@@ -19230,11 +19230,11 @@
         <v>1898</v>
       </c>
       <c r="G955">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I955" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="956" spans="1:9" x14ac:dyDescent="0.3">
@@ -19249,11 +19249,11 @@
         <v>1902</v>
       </c>
       <c r="G956">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I956" s="6" t="str">
         <f t="shared" si="14"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="957" spans="1:9" x14ac:dyDescent="0.3">
@@ -19439,11 +19439,11 @@
         <v>1921</v>
       </c>
       <c r="G966">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I966" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="967" spans="1:9" x14ac:dyDescent="0.3">
@@ -19534,11 +19534,11 @@
         <v>1929</v>
       </c>
       <c r="G971">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I971" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="972" spans="1:9" x14ac:dyDescent="0.3">
@@ -19686,11 +19686,11 @@
         <v>1945</v>
       </c>
       <c r="G979">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I979" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>T</v>
+        <v>F</v>
       </c>
     </row>
     <row r="980" spans="1:9" x14ac:dyDescent="0.3">
@@ -19724,11 +19724,11 @@
         <v>1948</v>
       </c>
       <c r="G981">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I981" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="982" spans="1:9" x14ac:dyDescent="0.3">
@@ -19800,7 +19800,7 @@
         <v>1952</v>
       </c>
       <c r="G985">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I985" s="6" t="str">
         <f t="shared" si="15"/>
@@ -20066,11 +20066,11 @@
         <v>1973</v>
       </c>
       <c r="G999">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I999" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="1000" spans="1:9" x14ac:dyDescent="0.3">
@@ -20104,11 +20104,11 @@
         <v>1978</v>
       </c>
       <c r="G1001">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I1001" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
     <row r="1002" spans="1:9" x14ac:dyDescent="0.3">
@@ -20150,7 +20150,7 @@
         <v>1985</v>
       </c>
       <c r="G1004">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1005" spans="1:9" x14ac:dyDescent="0.3">
@@ -20178,7 +20178,7 @@
         <v>1991</v>
       </c>
       <c r="G1006">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1007" spans="1:9" x14ac:dyDescent="0.3">
@@ -20192,7 +20192,7 @@
         <v>1992</v>
       </c>
       <c r="G1007">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1008" spans="1:9" x14ac:dyDescent="0.3">
@@ -20206,7 +20206,7 @@
         <v>1993</v>
       </c>
       <c r="G1008">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1009" spans="1:7" x14ac:dyDescent="0.3">
@@ -20388,7 +20388,7 @@
         <v>2022</v>
       </c>
       <c r="G1021">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1022" spans="1:7" x14ac:dyDescent="0.3">
@@ -20500,7 +20500,7 @@
         <v>2032</v>
       </c>
       <c r="G1029">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1030" spans="1:7" x14ac:dyDescent="0.3">
@@ -20668,7 +20668,7 @@
         <v>2066</v>
       </c>
       <c r="G1041">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1042" spans="1:7" x14ac:dyDescent="0.3">
@@ -20850,7 +20850,7 @@
         <v>2098</v>
       </c>
       <c r="G1054">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1055" spans="1:7" x14ac:dyDescent="0.3">
@@ -20906,7 +20906,7 @@
         <v>2107</v>
       </c>
       <c r="G1058">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1059" spans="1:7" x14ac:dyDescent="0.3">
@@ -20948,7 +20948,7 @@
         <v>2113</v>
       </c>
       <c r="G1061">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1062" spans="1:7" x14ac:dyDescent="0.3">
@@ -21172,7 +21172,7 @@
         <v>2155</v>
       </c>
       <c r="G1077">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1078" spans="1:7" x14ac:dyDescent="0.3">
@@ -21228,7 +21228,7 @@
         <v>2163</v>
       </c>
       <c r="G1081">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1082" spans="1:7" x14ac:dyDescent="0.3">
@@ -21298,7 +21298,7 @@
         <v>2174</v>
       </c>
       <c r="G1086">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1087" spans="1:7" x14ac:dyDescent="0.3">
@@ -21494,7 +21494,7 @@
         <v>2208</v>
       </c>
       <c r="G1100">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1101" spans="1:7" x14ac:dyDescent="0.3">
@@ -21536,7 +21536,7 @@
         <v>2211</v>
       </c>
       <c r="G1103">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1104" spans="1:7" x14ac:dyDescent="0.3">
@@ -21592,7 +21592,7 @@
         <v>2216</v>
       </c>
       <c r="G1107">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1108" spans="1:7" x14ac:dyDescent="0.3">
@@ -21606,7 +21606,7 @@
         <v>2218</v>
       </c>
       <c r="G1108">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1109" spans="1:7" x14ac:dyDescent="0.3">
@@ -21620,7 +21620,7 @@
         <v>2219</v>
       </c>
       <c r="G1109">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1110" spans="1:7" x14ac:dyDescent="0.3">
@@ -22026,7 +22026,7 @@
         <v>2273</v>
       </c>
       <c r="G1138">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1139" spans="1:7" x14ac:dyDescent="0.3">
@@ -22096,7 +22096,7 @@
         <v>2281</v>
       </c>
       <c r="G1143">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1144" spans="1:7" x14ac:dyDescent="0.3">
@@ -22208,7 +22208,7 @@
         <v>2295</v>
       </c>
       <c r="G1151">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1152" spans="1:7" x14ac:dyDescent="0.3">
@@ -22348,7 +22348,7 @@
         <v>2318</v>
       </c>
       <c r="G1161">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1162" spans="1:7" x14ac:dyDescent="0.3">
@@ -22404,7 +22404,7 @@
         <v>2328</v>
       </c>
       <c r="G1165">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1166" spans="1:7" x14ac:dyDescent="0.3">
@@ -22460,7 +22460,7 @@
         <v>2339</v>
       </c>
       <c r="G1169">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1170" spans="1:7" x14ac:dyDescent="0.3">
@@ -22586,7 +22586,7 @@
         <v>2354</v>
       </c>
       <c r="G1178">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1179" spans="1:7" x14ac:dyDescent="0.3">
@@ -22712,7 +22712,7 @@
         <v>2367</v>
       </c>
       <c r="G1187">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1188" spans="1:7" x14ac:dyDescent="0.3">
@@ -22754,7 +22754,7 @@
         <v>2377</v>
       </c>
       <c r="G1190">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1191" spans="1:7" x14ac:dyDescent="0.3">
@@ -22978,7 +22978,7 @@
         <v>2406</v>
       </c>
       <c r="G1206">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1207" spans="1:7" x14ac:dyDescent="0.3">
@@ -23146,7 +23146,7 @@
         <v>2431</v>
       </c>
       <c r="G1218">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1219" spans="1:7" x14ac:dyDescent="0.3">
@@ -23286,7 +23286,7 @@
         <v>2460</v>
       </c>
       <c r="G1228">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1229" spans="1:7" x14ac:dyDescent="0.3">
@@ -23314,7 +23314,7 @@
         <v>2464</v>
       </c>
       <c r="G1230">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1231" spans="1:7" x14ac:dyDescent="0.3">
@@ -23342,7 +23342,7 @@
         <v>2466</v>
       </c>
       <c r="G1232">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1233" spans="1:7" x14ac:dyDescent="0.3">
@@ -23384,7 +23384,7 @@
         <v>2472</v>
       </c>
       <c r="G1235">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1236" spans="1:7" x14ac:dyDescent="0.3">
@@ -23538,7 +23538,7 @@
         <v>2493</v>
       </c>
       <c r="G1246">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1247" spans="1:7" x14ac:dyDescent="0.3">
@@ -23552,7 +23552,7 @@
         <v>2494</v>
       </c>
       <c r="G1247">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1248" spans="1:7" x14ac:dyDescent="0.3">
@@ -23580,7 +23580,7 @@
         <v>2498</v>
       </c>
       <c r="G1249">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1250" spans="1:7" x14ac:dyDescent="0.3">
@@ -23790,7 +23790,7 @@
         <v>2527</v>
       </c>
       <c r="G1264">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1265" spans="1:7" x14ac:dyDescent="0.3">
@@ -23818,7 +23818,7 @@
         <v>2529</v>
       </c>
       <c r="G1266">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1267" spans="1:7" x14ac:dyDescent="0.3">
@@ -23874,7 +23874,7 @@
         <v>2542</v>
       </c>
       <c r="G1270">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1271" spans="1:7" x14ac:dyDescent="0.3">
@@ -23888,7 +23888,7 @@
         <v>2543</v>
       </c>
       <c r="G1271">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1272" spans="1:7" x14ac:dyDescent="0.3">
@@ -23902,7 +23902,7 @@
         <v>2545</v>
       </c>
       <c r="G1272">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1273" spans="1:7" x14ac:dyDescent="0.3">
@@ -24028,7 +24028,7 @@
         <v>2570</v>
       </c>
       <c r="G1281">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1282" spans="1:7" x14ac:dyDescent="0.3">
@@ -24056,7 +24056,7 @@
         <v>2575</v>
       </c>
       <c r="G1283">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1284" spans="1:7" x14ac:dyDescent="0.3">
@@ -24294,7 +24294,7 @@
         <v>2609</v>
       </c>
       <c r="G1300">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1301" spans="1:7" x14ac:dyDescent="0.3">
@@ -24336,7 +24336,7 @@
         <v>2618</v>
       </c>
       <c r="G1303">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1304" spans="1:7" x14ac:dyDescent="0.3">
@@ -24392,7 +24392,7 @@
         <v>2629</v>
       </c>
       <c r="G1307">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1308" spans="1:7" x14ac:dyDescent="0.3">
@@ -24588,7 +24588,7 @@
         <v>2648</v>
       </c>
       <c r="G1321">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1322" spans="1:7" x14ac:dyDescent="0.3">
@@ -24630,7 +24630,7 @@
         <v>2655</v>
       </c>
       <c r="G1324">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1325" spans="1:7" x14ac:dyDescent="0.3">
@@ -24742,7 +24742,7 @@
         <v>2671</v>
       </c>
       <c r="G1332">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1333" spans="1:7" x14ac:dyDescent="0.3">
@@ -24784,7 +24784,7 @@
         <v>2677</v>
       </c>
       <c r="G1335">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1336" spans="1:7" x14ac:dyDescent="0.3">
@@ -24812,7 +24812,7 @@
         <v>2679</v>
       </c>
       <c r="G1337">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1338" spans="1:7" x14ac:dyDescent="0.3">
@@ -24826,7 +24826,7 @@
         <v>2681</v>
       </c>
       <c r="G1338">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1339" spans="1:7" x14ac:dyDescent="0.3">
@@ -24854,7 +24854,7 @@
         <v>2683</v>
       </c>
       <c r="G1340">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1341" spans="1:7" x14ac:dyDescent="0.3">
@@ -24924,7 +24924,7 @@
         <v>2699</v>
       </c>
       <c r="G1345">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1346" spans="1:7" x14ac:dyDescent="0.3">
@@ -25050,7 +25050,7 @@
         <v>2714</v>
       </c>
       <c r="G1354">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1355" spans="1:7" x14ac:dyDescent="0.3">
@@ -25078,7 +25078,7 @@
         <v>2718</v>
       </c>
       <c r="G1356">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1357" spans="1:7" x14ac:dyDescent="0.3">
@@ -25190,7 +25190,7 @@
         <v>2730</v>
       </c>
       <c r="G1364">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1365" spans="1:7" x14ac:dyDescent="0.3">
@@ -25232,7 +25232,7 @@
         <v>2740</v>
       </c>
       <c r="G1367">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1368" spans="1:7" x14ac:dyDescent="0.3">
@@ -25302,7 +25302,7 @@
         <v>2748</v>
       </c>
       <c r="G1372">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1373" spans="1:7" x14ac:dyDescent="0.3">
@@ -25358,7 +25358,7 @@
         <v>2755</v>
       </c>
       <c r="G1376">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1377" spans="1:7" x14ac:dyDescent="0.3">
@@ -25386,7 +25386,7 @@
         <v>2759</v>
       </c>
       <c r="G1378">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1379" spans="1:7" x14ac:dyDescent="0.3">
@@ -25470,7 +25470,7 @@
         <v>2768</v>
       </c>
       <c r="G1384">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1385" spans="1:7" x14ac:dyDescent="0.3">
@@ -25512,7 +25512,7 @@
         <v>2771</v>
       </c>
       <c r="G1387">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1388" spans="1:7" x14ac:dyDescent="0.3">
@@ -25610,7 +25610,7 @@
         <v>2785</v>
       </c>
       <c r="G1394">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1395" spans="1:7" x14ac:dyDescent="0.3">
@@ -25736,7 +25736,7 @@
         <v>2800</v>
       </c>
       <c r="G1403">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1404" spans="1:7" x14ac:dyDescent="0.3">
@@ -25778,7 +25778,7 @@
         <v>2803</v>
       </c>
       <c r="G1406">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1407" spans="1:7" x14ac:dyDescent="0.3">
@@ -25806,7 +25806,7 @@
         <v>2806</v>
       </c>
       <c r="G1408">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1409" spans="1:7" x14ac:dyDescent="0.3">
@@ -25834,7 +25834,7 @@
         <v>2808</v>
       </c>
       <c r="G1410">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1411" spans="1:7" x14ac:dyDescent="0.3">
@@ -25876,7 +25876,7 @@
         <v>2813</v>
       </c>
       <c r="G1413">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1414" spans="1:7" x14ac:dyDescent="0.3">
@@ -25890,7 +25890,7 @@
         <v>2817</v>
       </c>
       <c r="G1414">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1415" spans="1:7" x14ac:dyDescent="0.3">
@@ -25960,7 +25960,7 @@
         <v>2826</v>
       </c>
       <c r="G1419">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1420" spans="1:7" x14ac:dyDescent="0.3">
@@ -26002,7 +26002,7 @@
         <v>2829</v>
       </c>
       <c r="G1422">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1423" spans="1:7" x14ac:dyDescent="0.3">
@@ -26030,7 +26030,7 @@
         <v>2835</v>
       </c>
       <c r="G1424">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1425" spans="1:7" x14ac:dyDescent="0.3">
@@ -26044,7 +26044,7 @@
         <v>2838</v>
       </c>
       <c r="G1425">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1426" spans="1:7" x14ac:dyDescent="0.3">
@@ -26114,7 +26114,7 @@
         <v>2849</v>
       </c>
       <c r="G1430">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1431" spans="1:7" x14ac:dyDescent="0.3">
@@ -26142,7 +26142,7 @@
         <v>2851</v>
       </c>
       <c r="G1432">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1433" spans="1:7" x14ac:dyDescent="0.3">
@@ -26212,7 +26212,7 @@
         <v>2861</v>
       </c>
       <c r="G1437">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1438" spans="1:7" x14ac:dyDescent="0.3">
@@ -26268,7 +26268,7 @@
         <v>2870</v>
       </c>
       <c r="G1441">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1442" spans="1:7" x14ac:dyDescent="0.3">
@@ -26310,7 +26310,7 @@
         <v>2876</v>
       </c>
       <c r="G1444">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1445" spans="1:7" x14ac:dyDescent="0.3">
@@ -26352,7 +26352,7 @@
         <v>2882</v>
       </c>
       <c r="G1447">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1448" spans="1:7" x14ac:dyDescent="0.3">
@@ -26436,7 +26436,7 @@
         <v>2901</v>
       </c>
       <c r="G1453">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1454" spans="1:7" x14ac:dyDescent="0.3">
@@ -26520,7 +26520,7 @@
         <v>2910</v>
       </c>
       <c r="G1459">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1460" spans="1:7" x14ac:dyDescent="0.3">
@@ -26618,7 +26618,7 @@
         <v>2923</v>
       </c>
       <c r="G1466">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1467" spans="1:7" x14ac:dyDescent="0.3">
@@ -26688,7 +26688,7 @@
         <v>2935</v>
       </c>
       <c r="G1471">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1472" spans="1:7" x14ac:dyDescent="0.3">
@@ -26716,7 +26716,7 @@
         <v>2940</v>
       </c>
       <c r="G1473">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1474" spans="1:7" x14ac:dyDescent="0.3">
@@ -26758,7 +26758,7 @@
         <v>2948</v>
       </c>
       <c r="G1476">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1477" spans="1:7" x14ac:dyDescent="0.3">
@@ -26786,7 +26786,7 @@
         <v>2950</v>
       </c>
       <c r="G1478">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1479" spans="1:7" x14ac:dyDescent="0.3">
@@ -26828,7 +26828,7 @@
         <v>2957</v>
       </c>
       <c r="G1481">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1482" spans="1:7" x14ac:dyDescent="0.3">
@@ -26898,7 +26898,7 @@
         <v>2967</v>
       </c>
       <c r="G1486">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1487" spans="1:7" x14ac:dyDescent="0.3">
@@ -26982,7 +26982,7 @@
         <v>2979</v>
       </c>
       <c r="G1492">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1493" spans="1:7" x14ac:dyDescent="0.3">
@@ -27080,7 +27080,7 @@
         <v>2992</v>
       </c>
       <c r="G1499">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1500" spans="1:7" x14ac:dyDescent="0.3">
@@ -27234,7 +27234,7 @@
         <v>3021</v>
       </c>
       <c r="G1510">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1511" spans="1:7" x14ac:dyDescent="0.3">
@@ -27388,7 +27388,7 @@
         <v>3044</v>
       </c>
       <c r="G1521">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1522" spans="1:7" x14ac:dyDescent="0.3">
@@ -27430,7 +27430,7 @@
         <v>3047</v>
       </c>
       <c r="G1524">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1525" spans="1:7" x14ac:dyDescent="0.3">
@@ -27444,7 +27444,7 @@
         <v>3049</v>
       </c>
       <c r="G1525">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1526" spans="1:7" x14ac:dyDescent="0.3">
@@ -27556,7 +27556,7 @@
         <v>3069</v>
       </c>
       <c r="G1533">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1534" spans="1:7" x14ac:dyDescent="0.3">
@@ -27738,7 +27738,7 @@
         <v>3089</v>
       </c>
       <c r="G1546">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
